--- a/Files Data.xlsx
+++ b/Files Data.xlsx
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
@@ -93,14 +93,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
@@ -470,14 +467,14 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E479"/>
+  <dimension ref="A1:E483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="59.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="42.86214285714286" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.71928571428571" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.71928571428571" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -507,7 +504,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
+    <row r="2" ht="19.5" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>البداية</t>
@@ -528,7 +525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1">
+    <row r="3" ht="19.5" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>لحن تين اوؤشت</t>
@@ -549,7 +546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1">
+    <row r="4" ht="19.5" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>لحن شيري ماريا</t>
@@ -570,7 +567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
+    <row r="5" ht="19.5" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>بدء قداس الكلمة</t>
@@ -591,7 +588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1">
+    <row r="6" ht="19.5" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>مزامير الساعة الثالثة</t>
@@ -612,7 +609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>انجيل الساعة الثالثة</t>
@@ -633,7 +630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1">
+    <row r="8" ht="19.5" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>قطع الساعة الثالثة</t>
@@ -654,7 +651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1">
+    <row r="9" ht="19.5" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>مزامير الساعة السادسة</t>
@@ -675,7 +672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>انجيل الساعة السادسة</t>
@@ -696,7 +693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>قطع الساعة السادسة</t>
@@ -717,7 +714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1">
+    <row r="12" ht="19.5" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>مزامير الساعة التاسعة</t>
@@ -738,7 +735,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1">
+    <row r="13" ht="19.5" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>انجيل الساعة التاسعة</t>
@@ -759,7 +756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>قطع الساعة التاسعة</t>
@@ -780,7 +777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1">
+    <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>مزامير الغروب و النوم</t>
@@ -801,7 +798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1">
+    <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>انجيل الغروب</t>
@@ -822,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1">
+    <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>قطع الغروب</t>
@@ -5382,12 +5379,12 @@
     <row r="234" ht="18.75" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>فاي اريه بي اوو</t>
+          <t>مرد الانجيل</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>{B7D98377-B994-4654-B49C-DE10E0DDE4F1}</t>
+          <t>{06D592C8-05BF-4B7C-86F7-FDAB3FAB5FB1}</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -5403,12 +5400,12 @@
     <row r="235" ht="18.75" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>مرد الانجيل</t>
+          <t>ربع للعذراء</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>{06D592C8-05BF-4B7C-86F7-FDAB3FAB5FB1}</t>
+          <t>{ECE652ED-1345-4C6D-B92D-5996CFA27AEE}</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -5424,12 +5421,12 @@
     <row r="236" ht="18.75" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ربع للعذراء</t>
+          <t>ربع للملاك ميخائيل</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>{ECE652ED-1345-4C6D-B92D-5996CFA27AEE}</t>
+          <t>{9EF543FB-A75B-4171-B358-2EB549C98411}</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -5445,12 +5442,12 @@
     <row r="237" ht="18.75" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ربع للملاك ميخائيل</t>
+          <t>ربع للملاك غبريال</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>{9EF543FB-A75B-4171-B358-2EB549C98411}</t>
+          <t>{D291E41B-2C53-4536-8FD1-348E9CDB2155}</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -5466,12 +5463,12 @@
     <row r="238" ht="18.75" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ربع للملاك غبريال</t>
+          <t>ربع ليوحنا المعمدان</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>{D291E41B-2C53-4536-8FD1-348E9CDB2155}</t>
+          <t>{1D7510AE-6E2C-4BA3-9D81-3EBDFCD8956C}</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -5487,12 +5484,12 @@
     <row r="239" ht="18.75" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ربع ليوحنا المعمدان</t>
+          <t>ربع للرسل</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>{1D7510AE-6E2C-4BA3-9D81-3EBDFCD8956C}</t>
+          <t>{F5AB11D4-D7D2-4DA3-A830-32BA45BCB16D}</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -5508,12 +5505,12 @@
     <row r="240" ht="18.75" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ربع للرسل</t>
+          <t>ربع للرسولين بطرس و بولس</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>{F5AB11D4-D7D2-4DA3-A830-32BA45BCB16D}</t>
+          <t>{7279EB5A-C32A-41F8-80D7-A33740EC7C09}</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -5529,12 +5526,12 @@
     <row r="241" ht="18.75" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ربع للرسولين بطرس و بولس</t>
+          <t>ربع للأنبا لعازر</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>{7279EB5A-C32A-41F8-80D7-A33740EC7C09}</t>
+          <t>{9DA6B68C-98B8-40DA-9117-200EB52E30AB}</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -5550,12 +5547,12 @@
     <row r="242" ht="18.75" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ربع للأنبا لعازر</t>
+          <t>فاي اريه بي اوو</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>{9DA6B68C-98B8-40DA-9117-200EB52E30AB}</t>
+          <t>{B7D98377-B994-4654-B49C-DE10E0DDE4F1}</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -8784,250 +8781,250 @@
     <row r="396" ht="18.75" customHeight="1">
       <c r="A396" t="inlineStr">
         <is>
-          <t>قسمة للإبن سنوى (أيها الكائن الذى كان)</t>
+          <t>قسمة للآب تُقال في كل وقت (اللهم أبا ربنا وإلهنا)</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>{F90E4B14-C4FF-486F-98C1-ADA99A89A302}</t>
+          <t>{DD47AADF-BF21-418D-A69D-BADB48E42804}</t>
         </is>
       </c>
       <c r="C396" t="n">
         <v>2821</v>
       </c>
       <c r="D396" t="n">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="E396" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="397" ht="18.75" customHeight="1">
       <c r="A397" t="inlineStr">
         <is>
-          <t>قسمة للإبن سنوى (أنت هو كلمة الآب)</t>
+          <t>قسمة للإبن سنوى (أيها الكائن الذى كان)</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>{F2499A0D-A0A3-42EB-A437-5664CF9EB56C}</t>
+          <t>{F90E4B14-C4FF-486F-98C1-ADA99A89A302}</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="D397" t="n">
-        <v>2837</v>
+        <v>2843</v>
       </c>
       <c r="E397" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="398" ht="18.75" customHeight="1">
       <c r="A398" t="inlineStr">
         <is>
-          <t>قسمة للإبن لأى وقت (أيها الإبن الإله الكلمة)</t>
+          <t>قسمة للإبن سنوى (أنت هو كلمة الآب)</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>{027EC456-759E-4983-982E-8E661C082017}</t>
+          <t>{F2499A0D-A0A3-42EB-A437-5664CF9EB56C}</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2838</v>
+        <v>2844</v>
       </c>
       <c r="D398" t="n">
         <v>2848</v>
       </c>
       <c r="E398" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399" ht="18.75" customHeight="1">
       <c r="A399" t="inlineStr">
         <is>
-          <t>قسمة للابن سنوي (يا مخلصي هذه هي الرأس)</t>
+          <t>قسمة للإبن لأى وقت (أيها الإبن الإله الكلمة)</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>{1BA28636-E0D3-4C62-9A88-2EC8CD89FCDF}</t>
+          <t>{027EC456-759E-4983-982E-8E661C082017}</t>
         </is>
       </c>
       <c r="C399" t="n">
         <v>2849</v>
       </c>
       <c r="D399" t="n">
-        <v>2854</v>
+        <v>2859</v>
       </c>
       <c r="E399" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="400" ht="18.75" customHeight="1">
       <c r="A400" t="inlineStr">
         <is>
-          <t>قسمة للابن تقال في أي وقت (لمجد صورة جوهريتك نخضع)</t>
+          <t>قسمة للابن سنوي (يا مخلصي هذه هي الرأس)</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>{9C7B0DA2-DB0E-4576-B2DF-875A87310C06}</t>
+          <t>{1BA28636-E0D3-4C62-9A88-2EC8CD89FCDF}</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2855</v>
+        <v>2860</v>
       </c>
       <c r="D400" t="n">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="E400" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="401" ht="18.75" customHeight="1">
       <c r="A401" t="inlineStr">
         <is>
-          <t>قسمة النيروز (لنسبح الله تسبيحا جديدا)</t>
+          <t>قسمة للابن تقال في أي وقت (لمجد صورة جوهريتك نخضع)</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>{8CC6F153-C335-4534-8CF6-42E3774875A6}</t>
+          <t>{9C7B0DA2-DB0E-4576-B2DF-875A87310C06}</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="D401" t="n">
-        <v>2872</v>
+        <v>2875</v>
       </c>
       <c r="E401" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="402" ht="18.75" customHeight="1">
       <c r="A402" t="inlineStr">
         <is>
-          <t>قسمة عيد الصليب (ايها المسيح الهنا الابن الكلمة)</t>
+          <t>قسمة النيروز (لنسبح الله تسبيحا جديدا)</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>{3DF2ADE7-6EAF-4FD9-8250-7048D4114339}</t>
+          <t>{8CC6F153-C335-4534-8CF6-42E3774875A6}</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2873</v>
+        <v>2876</v>
       </c>
       <c r="D402" t="n">
         <v>2883</v>
       </c>
       <c r="E402" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="403" ht="18.75" customHeight="1">
       <c r="A403" t="inlineStr">
         <is>
-          <t>قسمة للآب في صوم الميلاد وعيد الميلاد وسنوى (أيها السيد الرب إلهنا)</t>
+          <t>قسمة عيد الصليب (ايها المسيح الهنا الابن الكلمة)</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>{C2F28915-B86E-4596-8EB2-7455EF4E91BD}</t>
+          <t>{3DF2ADE7-6EAF-4FD9-8250-7048D4114339}</t>
         </is>
       </c>
       <c r="C403" t="n">
         <v>2884</v>
       </c>
       <c r="D403" t="n">
-        <v>2888</v>
+        <v>2894</v>
       </c>
       <c r="E403" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="404" ht="18.75" customHeight="1">
       <c r="A404" t="inlineStr">
         <is>
-          <t>قسمة لميلاد الابن وفي الأعياد (اللهم المعتني بكل احد)</t>
+          <t>قسمة للآب في صوم الميلاد وعيد الميلاد وسنوى (أيها السيد الرب إلهنا)</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>{E1024E42-D34E-4378-A071-0E68524DECE6}</t>
+          <t>{C2F28915-B86E-4596-8EB2-7455EF4E91BD}</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2889</v>
+        <v>2895</v>
       </c>
       <c r="D404" t="n">
-        <v>2902</v>
+        <v>2899</v>
       </c>
       <c r="E404" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="405" ht="18.75" customHeight="1">
       <c r="A405" t="inlineStr">
         <is>
-          <t>قسمة في الأعياد السيدية وفي الميلاد (اللهم الذي سبق علمه وجود الكائنات)</t>
+          <t>قسمة لميلاد الابن وفي الأعياد (اللهم المعتني بكل احد)</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>{0E73CD3E-C982-4143-9947-E842D2626778}</t>
+          <t>{E1024E42-D34E-4378-A071-0E68524DECE6}</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>2903</v>
+        <v>2900</v>
       </c>
       <c r="D405" t="n">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="E405" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="406" ht="18.75" customHeight="1">
       <c r="A406" t="inlineStr">
         <is>
-          <t>قسمة عيد الختان و الدخول المسيح الهيكل (نسبح ونمجد إله الآلهة ورب الأرباب)</t>
+          <t>قسمة في الأعياد السيدية وفي الميلاد (اللهم الذي سبق علمه وجود الكائنات)</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>{7F6F8D4A-D920-4593-8079-02F63856B7EC}</t>
+          <t>{0E73CD3E-C982-4143-9947-E842D2626778}</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="D406" t="n">
-        <v>2918</v>
+        <v>2923</v>
       </c>
       <c r="E406" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="407" ht="18.75" customHeight="1">
       <c r="A407" t="inlineStr">
         <is>
-          <t>قسمة عيد عرس قانا الجليل (أنت هو كلمة الآب)</t>
+          <t>قسمة عيد الختان و الدخول المسيح الهيكل (نسبح ونمجد إله الآلهة ورب الأرباب)</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>{73518929-B0CA-4403-BF97-0AC121ED4EF6}</t>
+          <t>{7F6F8D4A-D920-4593-8079-02F63856B7EC}</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2919</v>
+        <v>2924</v>
       </c>
       <c r="D407" t="n">
-        <v>2924</v>
+        <v>2929</v>
       </c>
       <c r="E407" t="n">
         <v>6</v>
@@ -9036,565 +9033,565 @@
     <row r="408" ht="18.75" customHeight="1">
       <c r="A408" t="inlineStr">
         <is>
-          <t>قسمة للآب في عيد الغطاس وسنوى (إذ أعطيتنا نعمة البنوة بحميم الميلاد)</t>
+          <t>قسمة عيد عرس قانا الجليل (أنت هو كلمة الآب)</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>{31B52FC4-A94D-4CCF-951F-BB1D2DD2D5D9}</t>
+          <t>{73518929-B0CA-4403-BF97-0AC121ED4EF6}</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2925</v>
+        <v>2930</v>
       </c>
       <c r="D408" t="n">
-        <v>2928</v>
+        <v>2935</v>
       </c>
       <c r="E408" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="409" ht="18.75" customHeight="1">
       <c r="A409" t="inlineStr">
         <is>
-          <t>قسمه عيد الغطاس وعيد يوحنا المعمدان (يا الله الذي أنعم على زكريا)</t>
+          <t>قسمة للآب في عيد الغطاس وسنوى (إذ أعطيتنا نعمة البنوة بحميم الميلاد)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>{65D2E228-2773-41A5-AD1F-5A718752D590}</t>
+          <t>{31B52FC4-A94D-4CCF-951F-BB1D2DD2D5D9}</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2929</v>
+        <v>2936</v>
       </c>
       <c r="D409" t="n">
-        <v>2933</v>
+        <v>2939</v>
       </c>
       <c r="E409" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="410" ht="18.75" customHeight="1">
       <c r="A410" t="inlineStr">
         <is>
-          <t>قسمة صوم نينوى (الله الرحوم)</t>
+          <t>قسمه عيد الغطاس وعيد يوحنا المعمدان (يا الله الذي أنعم على زكريا)</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>{BB553AF2-8A5E-46E8-B567-4E8500E5A1C1}</t>
+          <t>{65D2E228-2773-41A5-AD1F-5A718752D590}</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2934</v>
+        <v>2940</v>
       </c>
       <c r="D410" t="n">
-        <v>2942</v>
+        <v>2944</v>
       </c>
       <c r="E410" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" ht="18.75" customHeight="1">
       <c r="A411" t="inlineStr">
         <is>
-          <t>قسمة للآب في الصوم الكبير المقدس (أيها السيد الرب الإله ضابط الكل)</t>
+          <t>قسمة صوم نينوى (الله الرحوم)</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>{41DD9B19-60F1-44CE-BF9E-34D6DA71F069}</t>
+          <t>{BB553AF2-8A5E-46E8-B567-4E8500E5A1C1}</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2943</v>
+        <v>2945</v>
       </c>
       <c r="D411" t="n">
-        <v>2950</v>
+        <v>2953</v>
       </c>
       <c r="E411" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="412" ht="18.75" customHeight="1">
       <c r="A412" t="inlineStr">
         <is>
-          <t>قسمة للإبن في أيام صوم الأربعين المقدس (أنت هو الله الرحوم مخلص)</t>
+          <t>قسمة للآب في الصوم الكبير المقدس (أيها السيد الرب الإله ضابط الكل)</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>{F076B353-F7AB-4001-959A-5D482DE256DB}</t>
+          <t>{41DD9B19-60F1-44CE-BF9E-34D6DA71F069}</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2951</v>
+        <v>2954</v>
       </c>
       <c r="D412" t="n">
-        <v>2955</v>
+        <v>2961</v>
       </c>
       <c r="E412" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413" ht="18.75" customHeight="1">
       <c r="A413" t="inlineStr">
         <is>
-          <t>قسمة عيد البشارة المجيد (نسبح ونمجد إله الآلهة ورب الأرباب)</t>
+          <t>قسمة للإبن في أيام صوم الأربعين المقدس (أنت هو الله الرحوم مخلص)</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>{3BCBBDE0-13A1-4825-B7A1-04CDC2E502E4}</t>
+          <t>{F076B353-F7AB-4001-959A-5D482DE256DB}</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2956</v>
+        <v>2962</v>
       </c>
       <c r="D413" t="n">
-        <v>2961</v>
+        <v>2966</v>
       </c>
       <c r="E413" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414" ht="18.75" customHeight="1">
       <c r="A414" t="inlineStr">
         <is>
-          <t>قسمة للآب في أحد الشعانين وسنوى (أيها الرب ربنا لقد صار إسمك)</t>
+          <t>قسمة عيد البشارة المجيد (نسبح ونمجد إله الآلهة ورب الأرباب)</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>{DBFE5A01-1D04-4F27-A7F4-057D75E8CBED}</t>
+          <t>{3BCBBDE0-13A1-4825-B7A1-04CDC2E502E4}</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2962</v>
+        <v>2967</v>
       </c>
       <c r="D414" t="n">
-        <v>2964</v>
+        <v>2972</v>
       </c>
       <c r="E414" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="415" ht="18.75" customHeight="1">
       <c r="A415" t="inlineStr">
         <is>
-          <t>قسمة تُقال في احد الشعانين (أيها الرب مثل ربنا مثل عجيب صار إسمك)</t>
+          <t>قسمة للآب في أحد الشعانين وسنوى (أيها الرب ربنا لقد صار إسمك)</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>{FA39B8EF-3898-43AD-B4E9-1E0FE167AE86}</t>
+          <t>{DBFE5A01-1D04-4F27-A7F4-057D75E8CBED}</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>2965</v>
+        <v>2973</v>
       </c>
       <c r="D415" t="n">
-        <v>2971</v>
+        <v>2975</v>
       </c>
       <c r="E415" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416" ht="18.75" customHeight="1">
       <c r="A416" t="inlineStr">
         <is>
-          <t>قسمة للأب علي ذبح اسحق (وحدث في الأيام)</t>
+          <t>قسمة تُقال في احد الشعانين (أيها الرب مثل ربنا مثل عجيب صار إسمك)</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>{F11101FD-3032-48C3-B6F9-29275566989B}</t>
+          <t>{FA39B8EF-3898-43AD-B4E9-1E0FE167AE86}</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2972</v>
+        <v>2976</v>
       </c>
       <c r="D416" t="n">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="E416" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="417" ht="18.75" customHeight="1">
       <c r="A417" t="inlineStr">
         <is>
-          <t>قسمة للإبن تقال في سبت الفرح (يا يسوع المسيح ذا الإسم المخلص)</t>
+          <t>قسمة للأب علي ذبح اسحق (وحدث في الأيام)</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>{F6C1CD0D-A2FB-4ED4-AB68-DC5D2D8AA3F1}</t>
+          <t>{F11101FD-3032-48C3-B6F9-29275566989B}</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="D417" t="n">
-        <v>2989</v>
+        <v>2992</v>
       </c>
       <c r="E417" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="418" ht="18.75" customHeight="1">
       <c r="A418" t="inlineStr">
         <is>
-          <t>قسمة للآب في عيد القيامة والخمسين (أيها السيد الرب الإله ضابط الكل)</t>
+          <t>قسمة للإبن تقال في سبت الفرح (يا يسوع المسيح ذا الإسم المخلص)</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>{3E1960C6-4E54-4563-B3A6-E8AAB1680607}</t>
+          <t>{F6C1CD0D-A2FB-4ED4-AB68-DC5D2D8AA3F1}</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>2990</v>
+        <v>2993</v>
       </c>
       <c r="D418" t="n">
-        <v>2996</v>
+        <v>3000</v>
       </c>
       <c r="E418" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="419" ht="18.75" customHeight="1">
       <c r="A419" t="inlineStr">
         <is>
-          <t>قسمة للإبن تقال في القيامة (أيها المسيح إلهنا رئيس كهنة)</t>
+          <t>قسمة للآب في عيد القيامة والخمسين (أيها السيد الرب الإله ضابط الكل)</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>{4AD14E1E-7934-4DBD-9067-5222067CDCCC}</t>
+          <t>{3E1960C6-4E54-4563-B3A6-E8AAB1680607}</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>2997</v>
+        <v>3001</v>
       </c>
       <c r="D419" t="n">
-        <v>3001</v>
+        <v>3007</v>
       </c>
       <c r="E419" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="420" ht="18.75" customHeight="1">
       <c r="A420" t="inlineStr">
         <is>
-          <t>قسمة صوم الرسل وسنوي (ما أبعد أحكامك عن الفحص)</t>
+          <t>قسمة للإبن تقال في القيامة (أيها المسيح إلهنا رئيس كهنة)</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>{F5E0EC3E-73EF-4E5E-8F7C-09BEC9CFCCDA}</t>
+          <t>{4AD14E1E-7934-4DBD-9067-5222067CDCCC}</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="D420" t="n">
-        <v>3009</v>
+        <v>3012</v>
       </c>
       <c r="E420" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="421" ht="18.75" customHeight="1">
       <c r="A421" t="inlineStr">
         <is>
-          <t>قسمة للإبن تقال في صوم الرسل (أنت هو كلمة الآب)</t>
+          <t>قسمة صوم الرسل وسنوي (ما أبعد أحكامك عن الفحص)</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>{A6211BD9-8280-4580-B6B5-6DD0D352FB24}</t>
+          <t>{F5E0EC3E-73EF-4E5E-8F7C-09BEC9CFCCDA}</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>3010</v>
+        <v>3013</v>
       </c>
       <c r="D421" t="n">
-        <v>3016</v>
+        <v>3020</v>
       </c>
       <c r="E421" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="422" ht="18.75" customHeight="1">
       <c r="A422" t="inlineStr">
         <is>
-          <t>قسمة لعيد الرسل (يا الله الآب السماوي)</t>
+          <t>قسمة للإبن تقال في صوم الرسل (أنت هو كلمة الآب)</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>{40A6164E-FE8E-46BF-8E33-41EB49A3EBD7}</t>
+          <t>{A6211BD9-8280-4580-B6B5-6DD0D352FB24}</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>3017</v>
+        <v>3021</v>
       </c>
       <c r="D422" t="n">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="E422" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="423" ht="18.75" customHeight="1">
       <c r="A423" t="inlineStr">
         <is>
-          <t>قسمة للإبن تُقال في عيد التجلي (أنت هو كلمة الآب)</t>
+          <t>قسمة لعيد الرسل (يا الله الآب السماوي)</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>{C23F094B-BD4E-4348-8186-D1C4B8744FAA}</t>
+          <t>{40A6164E-FE8E-46BF-8E33-41EB49A3EBD7}</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="D423" t="n">
-        <v>3034</v>
+        <v>3039</v>
       </c>
       <c r="E423" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="424" ht="18.75" customHeight="1">
       <c r="A424" t="inlineStr">
         <is>
-          <t>قسمة أعياد الملائكة والسيدة العذراء وسنوى (هوذا كائن معنا على هذه)</t>
+          <t>قسمة للإبن تُقال في عيد التجلي (أنت هو كلمة الآب)</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>{71232865-63AA-40C5-8F02-BABBFE7297D3}</t>
+          <t>{C23F094B-BD4E-4348-8186-D1C4B8744FAA}</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>3035</v>
+        <v>3040</v>
       </c>
       <c r="D424" t="n">
-        <v>3043</v>
+        <v>3045</v>
       </c>
       <c r="E424" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="425" ht="18.75" customHeight="1">
       <c r="A425" t="inlineStr">
         <is>
-          <t>صوم و أعياد القديسة العذراء مريم (يا الله الساكن في الأعالي)</t>
+          <t>قسمة أعياد الملائكة والسيدة العذراء وسنوى (هوذا كائن معنا على هذه)</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>{C78EDE33-ED5C-411D-A2E6-2B55E70B9F6B}</t>
+          <t>{71232865-63AA-40C5-8F02-BABBFE7297D3}</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>3044</v>
+        <v>3046</v>
       </c>
       <c r="D425" t="n">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="E425" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="426" ht="18.75" customHeight="1">
       <c r="A426" t="inlineStr">
         <is>
-          <t>قسمة للإبن تقال في الأعياد السيدية وسنوى (نسبح ونمجد إله الآلهة)</t>
+          <t>صوم و أعياد القديسة العذراء مريم (يا الله الساكن في الأعالي)</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>{2A09ADD1-849A-4776-9FF5-9E0F56C9BAED}</t>
+          <t>{C78EDE33-ED5C-411D-A2E6-2B55E70B9F6B}</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3058</v>
+        <v>3055</v>
       </c>
       <c r="D426" t="n">
-        <v>3065</v>
+        <v>3068</v>
       </c>
       <c r="E426" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="427" ht="18.75" customHeight="1">
       <c r="A427" t="inlineStr">
         <is>
-          <t>قسمة تذكار البشارة والميلاد والقيامة (نسبح ونمجد إله الآلهة ورب الأرباب)</t>
+          <t>قسمة الآب للصوم وأعياد العذراء (يا الله أبا ربنا وإلهنا ومخلصنا يسوع المسيح)</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>{BCFF601E-ED54-486A-9884-027CD11CA3C0}</t>
+          <t>{015F3171-49B8-440E-843F-799AF9F22B95}</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>3066</v>
+        <v>3069</v>
       </c>
       <c r="D427" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E427" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428" ht="18.75" customHeight="1">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ابانا الذي في السموات</t>
+          <t>قسمة للابن لصوم وأعياد العذراء (أيها الابن الوحيد المولود من الآب)</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>{F8657D52-0E61-475D-90AC-DB10509A5D22}</t>
+          <t>{93FC3113-B5D2-4725-88F8-579C70AE7A74}</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="D428" t="n">
-        <v>3081</v>
+        <v>3092</v>
       </c>
       <c r="E428" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="429" ht="18.75" customHeight="1">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ما قبل الإعتراف</t>
+          <t>قسمة للإبن تقال في الأعياد السيدية وسنوى (نسبح ونمجد إله الآلهة)</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>{80F60976-3BEB-4133-A7EB-026E12D4799C}</t>
+          <t>{2A09ADD1-849A-4776-9FF5-9E0F56C9BAED}</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>3082</v>
+        <v>3093</v>
       </c>
       <c r="D429" t="n">
-        <v>3106</v>
+        <v>3100</v>
       </c>
       <c r="E429" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430" ht="18.75" customHeight="1">
       <c r="A430" t="inlineStr">
         <is>
-          <t>الاعتراف</t>
+          <t>قسمة تذكار البشارة والميلاد والقيامة (نسبح ونمجد إله الآلهة ورب الأرباب)</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>{EE8004CA-FF9E-4471-963C-7F0946AE78FC}</t>
+          <t>{BCFF601E-ED54-486A-9884-027CD11CA3C0}</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>3107</v>
+        <v>3101</v>
       </c>
       <c r="D430" t="n">
-        <v>3130</v>
+        <v>3110</v>
       </c>
       <c r="E430" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="431" ht="18.75" customHeight="1">
       <c r="A431" t="inlineStr">
         <is>
-          <t>مرد توزيع النيروز</t>
+          <t>ابانا الذي في السموات</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>{76AC6D29-E354-4FF7-AA9F-EA0B71399749}</t>
+          <t>{F8657D52-0E61-475D-90AC-DB10509A5D22}</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3131</v>
+        <v>3111</v>
       </c>
       <c r="D431" t="n">
-        <v>3131</v>
+        <v>3116</v>
       </c>
       <c r="E431" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="432" ht="18.75" customHeight="1">
       <c r="A432" t="inlineStr">
         <is>
-          <t>مرد توزيع الصليب</t>
+          <t>ما قبل الإعتراف</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>{E4E79CE2-AD28-44FB-B8B3-6B59A5D64B62}</t>
+          <t>{80F60976-3BEB-4133-A7EB-026E12D4799C}</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>3132</v>
+        <v>3117</v>
       </c>
       <c r="D432" t="n">
-        <v>3132</v>
+        <v>3141</v>
       </c>
       <c r="E432" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="433" ht="18.75" customHeight="1">
       <c r="A433" t="inlineStr">
         <is>
-          <t>مرد توزيع الغطاس</t>
+          <t>الاعتراف</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>{96A65364-75BE-44B2-A2D8-29785DBD26C4}</t>
+          <t>{EE8004CA-FF9E-4471-963C-7F0946AE78FC}</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>3133</v>
+        <v>3142</v>
       </c>
       <c r="D433" t="n">
-        <v>3133</v>
+        <v>3165</v>
       </c>
       <c r="E433" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="434" ht="18.75" customHeight="1">
       <c r="A434" t="inlineStr">
         <is>
-          <t>مرد توزيع الختان</t>
+          <t>مرد توزيع النيروز</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>{3ED0ED6F-B67A-410E-958B-1437069EE8B5}</t>
+          <t>{76AC6D29-E354-4FF7-AA9F-EA0B71399749}</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>3134</v>
+        <v>3166</v>
       </c>
       <c r="D434" t="n">
-        <v>3134</v>
+        <v>3166</v>
       </c>
       <c r="E434" t="n">
         <v>1</v>
@@ -9603,19 +9600,19 @@
     <row r="435" ht="18.75" customHeight="1">
       <c r="A435" t="inlineStr">
         <is>
-          <t>مرد توزيع عرس قانا الجليل</t>
+          <t>مرد توزيع الصليب</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>{DACB52D6-560B-4038-BDA3-7A7315DEA6D0}</t>
+          <t>{E4E79CE2-AD28-44FB-B8B3-6B59A5D64B62}</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>3135</v>
+        <v>3167</v>
       </c>
       <c r="D435" t="n">
-        <v>3135</v>
+        <v>3167</v>
       </c>
       <c r="E435" t="n">
         <v>1</v>
@@ -9624,19 +9621,19 @@
     <row r="436" ht="18.75" customHeight="1">
       <c r="A436" t="inlineStr">
         <is>
-          <t>مرد توزيع دخول المسيح الهيكل</t>
+          <t>مرد توزيع الغطاس</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>{49900A3A-E6E6-4152-84C8-B741F3C50853}</t>
+          <t>{96A65364-75BE-44B2-A2D8-29785DBD26C4}</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>3136</v>
+        <v>3168</v>
       </c>
       <c r="D436" t="n">
-        <v>3136</v>
+        <v>3168</v>
       </c>
       <c r="E436" t="n">
         <v>1</v>
@@ -9645,19 +9642,19 @@
     <row r="437" ht="18.75" customHeight="1">
       <c r="A437" t="inlineStr">
         <is>
-          <t>مرد توزيع صوم نينوى</t>
+          <t>مرد توزيع الختان</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>{8B7ED515-48EF-40B6-B9F2-80B8A4CC1126}</t>
+          <t>{3ED0ED6F-B67A-410E-958B-1437069EE8B5}</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>3137</v>
+        <v>3169</v>
       </c>
       <c r="D437" t="n">
-        <v>3137</v>
+        <v>3169</v>
       </c>
       <c r="E437" t="n">
         <v>1</v>
@@ -9666,19 +9663,19 @@
     <row r="438" ht="18.75" customHeight="1">
       <c r="A438" t="inlineStr">
         <is>
-          <t>مرد توزيع الصوم الكبير</t>
+          <t>مرد توزيع عرس قانا الجليل</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>{F9ED982E-F6FB-4E2B-8955-C5E80C70C2D6}</t>
+          <t>{DACB52D6-560B-4038-BDA3-7A7315DEA6D0}</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>3138</v>
+        <v>3170</v>
       </c>
       <c r="D438" t="n">
-        <v>3138</v>
+        <v>3170</v>
       </c>
       <c r="E438" t="n">
         <v>1</v>
@@ -9687,19 +9684,19 @@
     <row r="439" ht="18.75" customHeight="1">
       <c r="A439" t="inlineStr">
         <is>
-          <t>مرد توزيع الشعانين</t>
+          <t>مرد توزيع دخول المسيح الهيكل</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>{C95D30EC-C174-40B5-8671-08FA653E3199}</t>
+          <t>{49900A3A-E6E6-4152-84C8-B741F3C50853}</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>3139</v>
+        <v>3171</v>
       </c>
       <c r="D439" t="n">
-        <v>3139</v>
+        <v>3171</v>
       </c>
       <c r="E439" t="n">
         <v>1</v>
@@ -9708,19 +9705,19 @@
     <row r="440" ht="18.75" customHeight="1">
       <c r="A440" t="inlineStr">
         <is>
-          <t>مرد توزيع البشارة</t>
+          <t>مرد توزيع صوم نينوى</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>{2F035E60-4CC5-4808-A906-367BDB0FC9B0}</t>
+          <t>{8B7ED515-48EF-40B6-B9F2-80B8A4CC1126}</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>3140</v>
+        <v>3172</v>
       </c>
       <c r="D440" t="n">
-        <v>3140</v>
+        <v>3172</v>
       </c>
       <c r="E440" t="n">
         <v>1</v>
@@ -9729,19 +9726,19 @@
     <row r="441" ht="18.75" customHeight="1">
       <c r="A441" t="inlineStr">
         <is>
-          <t>مرد توزيع الميلاد</t>
+          <t>مرد توزيع الصوم الكبير</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>{D10973F3-B5C6-431E-8EDA-60ABA7A98C9E}</t>
+          <t>{F9ED982E-F6FB-4E2B-8955-C5E80C70C2D6}</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>3141</v>
+        <v>3173</v>
       </c>
       <c r="D441" t="n">
-        <v>3141</v>
+        <v>3173</v>
       </c>
       <c r="E441" t="n">
         <v>1</v>
@@ -9750,19 +9747,19 @@
     <row r="442" ht="18.75" customHeight="1">
       <c r="A442" t="inlineStr">
         <is>
-          <t>مرد توزيع القيامة</t>
+          <t>مرد توزيع الشعانين</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>{AB0FAC0A-1DAB-4ABD-BAA1-7557AA4860AA}</t>
+          <t>{C95D30EC-C174-40B5-8671-08FA653E3199}</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>3142</v>
+        <v>3174</v>
       </c>
       <c r="D442" t="n">
-        <v>3142</v>
+        <v>3174</v>
       </c>
       <c r="E442" t="n">
         <v>1</v>
@@ -9771,19 +9768,19 @@
     <row r="443" ht="18.75" customHeight="1">
       <c r="A443" t="inlineStr">
         <is>
-          <t>مرد توزيع الصعود</t>
+          <t>مرد توزيع البشارة</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>{834F8F17-CEC0-4E51-A927-8074D22B6A78}</t>
+          <t>{2F035E60-4CC5-4808-A906-367BDB0FC9B0}</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>3143</v>
+        <v>3175</v>
       </c>
       <c r="D443" t="n">
-        <v>3143</v>
+        <v>3175</v>
       </c>
       <c r="E443" t="n">
         <v>1</v>
@@ -9792,19 +9789,19 @@
     <row r="444" ht="18.75" customHeight="1">
       <c r="A444" t="inlineStr">
         <is>
-          <t>مرد توزيع العنصرة</t>
+          <t>مرد توزيع الميلاد</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>{22674B27-BBD5-49D8-98B9-ABCA6F4C5504}</t>
+          <t>{D10973F3-B5C6-431E-8EDA-60ABA7A98C9E}</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>3144</v>
+        <v>3176</v>
       </c>
       <c r="D444" t="n">
-        <v>3144</v>
+        <v>3176</v>
       </c>
       <c r="E444" t="n">
         <v>1</v>
@@ -9813,19 +9810,19 @@
     <row r="445" ht="18.75" customHeight="1">
       <c r="A445" t="inlineStr">
         <is>
-          <t>مرد توزيع التجلي</t>
+          <t>مرد توزيع القيامة</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>{0080F7D2-9802-4100-8B27-DD23FBF42BCF}</t>
+          <t>{AB0FAC0A-1DAB-4ABD-BAA1-7557AA4860AA}</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>3145</v>
+        <v>3177</v>
       </c>
       <c r="D445" t="n">
-        <v>3145</v>
+        <v>3177</v>
       </c>
       <c r="E445" t="n">
         <v>1</v>
@@ -9834,376 +9831,376 @@
     <row r="446" ht="18.75" customHeight="1">
       <c r="A446" t="inlineStr">
         <is>
-          <t>مزمور التوزيع</t>
+          <t>مرد توزيع الصعود</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>{C29E5A83-A98B-4077-8194-99A6D803EF53}</t>
+          <t>{834F8F17-CEC0-4E51-A927-8074D22B6A78}</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3146</v>
+        <v>3178</v>
       </c>
       <c r="D446" t="n">
-        <v>3162</v>
+        <v>3178</v>
       </c>
       <c r="E446" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447" ht="18.75" customHeight="1">
       <c r="A447" t="inlineStr">
         <is>
-          <t>اطاي بارثينوس</t>
+          <t>مرد توزيع العنصرة</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>{18835C90-087E-4BAC-9D66-708BC1E04983}</t>
+          <t>{22674B27-BBD5-49D8-98B9-ABCA6F4C5504}</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3163</v>
+        <v>3179</v>
       </c>
       <c r="D447" t="n">
-        <v>3184</v>
+        <v>3179</v>
       </c>
       <c r="E447" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" ht="18.75" customHeight="1">
       <c r="A448" t="inlineStr">
         <is>
-          <t>لازاروس</t>
+          <t>مرد توزيع التجلي</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>{78C64C43-B3F6-4110-8CB0-1E10086C77C2}</t>
+          <t>{0080F7D2-9802-4100-8B27-DD23FBF42BCF}</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>3185</v>
+        <v>3180</v>
       </c>
       <c r="D448" t="n">
-        <v>3212</v>
+        <v>3180</v>
       </c>
       <c r="E448" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449" ht="18.75" customHeight="1">
       <c r="A449" t="inlineStr">
         <is>
-          <t>كاطا ني خوروس</t>
+          <t>مزمور التوزيع</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>{8E020F97-3459-40AC-828C-13346E2C46B1}</t>
+          <t>{C29E5A83-A98B-4077-8194-99A6D803EF53}</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>3213</v>
+        <v>3181</v>
       </c>
       <c r="D449" t="n">
-        <v>3216</v>
+        <v>3197</v>
       </c>
       <c r="E449" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="450" ht="18.75" customHeight="1">
       <c r="A450" t="inlineStr">
         <is>
-          <t>فهرس الحان التوزيع</t>
+          <t>اطاي بارثينوس</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>{688FAD52-7F6A-4FA9-8CF7-EBB80B3B6069}</t>
+          <t>{18835C90-087E-4BAC-9D66-708BC1E04983}</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>3217</v>
+        <v>3198</v>
       </c>
       <c r="D450" t="n">
-        <v>3217</v>
+        <v>3219</v>
       </c>
       <c r="E450" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="451" ht="18.75" customHeight="1">
       <c r="A451" t="inlineStr">
         <is>
-          <t>اك اسماروؤت</t>
+          <t>لازاروس</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>{507EFD97-98F8-4376-848B-20D72E16D2C1}</t>
+          <t>{78C64C43-B3F6-4110-8CB0-1E10086C77C2}</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="D451" t="n">
-        <v>3219</v>
+        <v>3247</v>
       </c>
       <c r="E451" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="452" ht="18.75" customHeight="1">
       <c r="A452" t="inlineStr">
         <is>
-          <t>بي اويك</t>
+          <t>كاطا ني خوروس</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>{B9A30F5E-0C89-471B-A99A-23DBE7F58504}</t>
+          <t>{8E020F97-3459-40AC-828C-13346E2C46B1}</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>3220</v>
+        <v>3248</v>
       </c>
       <c r="D452" t="n">
-        <v>3230</v>
+        <v>3251</v>
       </c>
       <c r="E452" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="453" ht="18.75" customHeight="1">
       <c r="A453" t="inlineStr">
         <is>
-          <t>جي اف اسماروؤت</t>
+          <t>فهرس الحان التوزيع</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>{82450F2E-38A9-42FB-ACFD-B874384545D2}</t>
+          <t>{688FAD52-7F6A-4FA9-8CF7-EBB80B3B6069}</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>3231</v>
+        <v>3252</v>
       </c>
       <c r="D453" t="n">
-        <v>3232</v>
+        <v>3252</v>
       </c>
       <c r="E453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" ht="18.75" customHeight="1">
       <c r="A454" t="inlineStr">
         <is>
-          <t>اسومين</t>
+          <t>اك اسماروؤت</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>{3F22DD0B-D926-42B9-BABE-6C6486C9BD62}</t>
+          <t>{507EFD97-98F8-4376-848B-20D72E16D2C1}</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>3233</v>
+        <v>3253</v>
       </c>
       <c r="D454" t="n">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="E454" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455" ht="18.75" customHeight="1">
       <c r="A455" t="inlineStr">
         <is>
-          <t>اف امبشا غار</t>
+          <t>بي اويك</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>{87BCA258-F572-4FEC-97DE-71CBA3159BB9}</t>
+          <t>{B9A30F5E-0C89-471B-A99A-23DBE7F58504}</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>3258</v>
+        <v>3255</v>
       </c>
       <c r="D455" t="n">
-        <v>3296</v>
+        <v>3265</v>
       </c>
       <c r="E455" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="456" ht="18.75" customHeight="1">
       <c r="A456" t="inlineStr">
         <is>
-          <t>تي بارثينوس</t>
+          <t>جي اف اسماروؤت</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>{185E1789-C295-487F-8018-CC029600A8F6}</t>
+          <t>{82450F2E-38A9-42FB-ACFD-B874384545D2}</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>3297</v>
+        <v>3266</v>
       </c>
       <c r="D456" t="n">
-        <v>3309</v>
+        <v>3267</v>
       </c>
       <c r="E456" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457" ht="18.75" customHeight="1">
       <c r="A457" t="inlineStr">
         <is>
-          <t>يونا بى ابروفيتيس</t>
+          <t>اسومين</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>{859D33B0-D7E3-4EDC-8AB9-E56533A2D980}</t>
+          <t>{3F22DD0B-D926-42B9-BABE-6C6486C9BD62}</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>3310</v>
+        <v>3268</v>
       </c>
       <c r="D457" t="n">
-        <v>3325</v>
+        <v>3292</v>
       </c>
       <c r="E457" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="458" ht="18.75" customHeight="1">
       <c r="A458" t="inlineStr">
         <is>
-          <t>بي ماي رومي</t>
+          <t>اف امبشا غار</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>{315091E2-E367-43B7-A35E-4175DF947038}</t>
+          <t>{87BCA258-F572-4FEC-97DE-71CBA3159BB9}</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>3326</v>
+        <v>3293</v>
       </c>
       <c r="D458" t="n">
-        <v>3340</v>
+        <v>3331</v>
       </c>
       <c r="E458" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="459" ht="18.75" customHeight="1">
       <c r="A459" t="inlineStr">
         <is>
-          <t>اونيشتي اميستيريون</t>
+          <t>تي بارثينوس</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>{DB680029-4B05-4C3F-98B3-FB5469AADBD7}</t>
+          <t>{185E1789-C295-487F-8018-CC029600A8F6}</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>3341</v>
+        <v>3332</v>
       </c>
       <c r="D459" t="n">
-        <v>3360</v>
+        <v>3344</v>
       </c>
       <c r="E459" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460" ht="18.75" customHeight="1">
       <c r="A460" t="inlineStr">
         <is>
-          <t>مدائح سنوي</t>
+          <t>يونا بى ابروفيتيس</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>{07298C47-E831-4285-ACB7-25BB3772C6A2}</t>
+          <t>{859D33B0-D7E3-4EDC-8AB9-E56533A2D980}</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>3361</v>
+        <v>3345</v>
       </c>
       <c r="D460" t="n">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E460" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="461" ht="18.75" customHeight="1">
       <c r="A461" t="inlineStr">
         <is>
-          <t>مدائح كيهك</t>
+          <t>بي ماي رومي</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>{DCEAD1F4-0405-4EE6-9905-219FC8E85798}</t>
+          <t>{315091E2-E367-43B7-A35E-4175DF947038}</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="D461" t="n">
-        <v>3362</v>
+        <v>3375</v>
       </c>
       <c r="E461" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="462" ht="18.75" customHeight="1">
       <c r="A462" t="inlineStr">
         <is>
-          <t>مدائح الميلاد</t>
+          <t>اونيشتي اميستيريون</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>{42181297-997B-4C4C-B43B-4E9D8A23858D}</t>
+          <t>{DB680029-4B05-4C3F-98B3-FB5469AADBD7}</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>3363</v>
+        <v>3376</v>
       </c>
       <c r="D462" t="n">
-        <v>3363</v>
+        <v>3395</v>
       </c>
       <c r="E462" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="463" ht="18.75" customHeight="1">
       <c r="A463" t="inlineStr">
         <is>
-          <t>مدائح صوم نينوى</t>
+          <t>مدائح سنوي</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>{43C9AE43-EC80-4A72-97F0-F38A712DDA09}</t>
+          <t>{07298C47-E831-4285-ACB7-25BB3772C6A2}</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>3364</v>
+        <v>3396</v>
       </c>
       <c r="D463" t="n">
-        <v>3364</v>
+        <v>3396</v>
       </c>
       <c r="E463" t="n">
         <v>1</v>
@@ -10212,19 +10209,19 @@
     <row r="464" ht="18.75" customHeight="1">
       <c r="A464" t="inlineStr">
         <is>
-          <t>مدائح الصوم الكبير</t>
+          <t>مدائح النيروز</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>{6C210ECD-CC91-4984-B251-46939B2A0039}</t>
+          <t>{61C536ED-3B9E-4448-A01E-0EE67B371A03}</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>3365</v>
+        <v>3397</v>
       </c>
       <c r="D464" t="n">
-        <v>3365</v>
+        <v>3397</v>
       </c>
       <c r="E464" t="n">
         <v>1</v>
@@ -10233,19 +10230,19 @@
     <row r="465" ht="18.75" customHeight="1">
       <c r="A465" t="inlineStr">
         <is>
-          <t>مدائح سبت لعازر</t>
+          <t>مدائح كيهك</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>{DB6B4ECA-F770-40E7-A7BA-46A8B5B46C3B}</t>
+          <t>{DCEAD1F4-0405-4EE6-9905-219FC8E85798}</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>3366</v>
+        <v>3398</v>
       </c>
       <c r="D465" t="n">
-        <v>3366</v>
+        <v>3398</v>
       </c>
       <c r="E465" t="n">
         <v>1</v>
@@ -10254,19 +10251,19 @@
     <row r="466" ht="18.75" customHeight="1">
       <c r="A466" t="inlineStr">
         <is>
-          <t>مدائح احد الشعانين</t>
+          <t>مدائح الميلاد</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>{37DC4920-98DA-477A-A6F7-6D252B149A22}</t>
+          <t>{42181297-997B-4C4C-B43B-4E9D8A23858D}</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>3367</v>
+        <v>3399</v>
       </c>
       <c r="D466" t="n">
-        <v>3367</v>
+        <v>3399</v>
       </c>
       <c r="E466" t="n">
         <v>1</v>
@@ -10275,19 +10272,19 @@
     <row r="467" ht="18.75" customHeight="1">
       <c r="A467" t="inlineStr">
         <is>
-          <t>مدائح القيامة</t>
+          <t>مدائح صوم نينوى</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>{1D781881-AD2E-41FE-97D4-458A86F892F1}</t>
+          <t>{43C9AE43-EC80-4A72-97F0-F38A712DDA09}</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>3368</v>
+        <v>3400</v>
       </c>
       <c r="D467" t="n">
-        <v>3368</v>
+        <v>3400</v>
       </c>
       <c r="E467" t="n">
         <v>1</v>
@@ -10296,19 +10293,19 @@
     <row r="468" ht="18.75" customHeight="1">
       <c r="A468" t="inlineStr">
         <is>
-          <t>مدائح الخماسين من 2 الى 39</t>
+          <t>مدائح الصوم الكبير</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>{F74608AC-8E8B-460A-97E7-1E6B86D50B5B}</t>
+          <t>{6C210ECD-CC91-4984-B251-46939B2A0039}</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>3369</v>
+        <v>3401</v>
       </c>
       <c r="D468" t="n">
-        <v>3369</v>
+        <v>3401</v>
       </c>
       <c r="E468" t="n">
         <v>1</v>
@@ -10317,19 +10314,19 @@
     <row r="469" ht="18.75" customHeight="1">
       <c r="A469" t="inlineStr">
         <is>
-          <t>مدائح الصعود الى العنصرة</t>
+          <t>مدائح سبت لعازر</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>{BAAC56F0-C9A0-4321-AB43-D79F5FCE37C9}</t>
+          <t>{DB6B4ECA-F770-40E7-A7BA-46A8B5B46C3B}</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>3370</v>
+        <v>3402</v>
       </c>
       <c r="D469" t="n">
-        <v>3370</v>
+        <v>3402</v>
       </c>
       <c r="E469" t="n">
         <v>1</v>
@@ -10338,19 +10335,19 @@
     <row r="470" ht="18.75" customHeight="1">
       <c r="A470" t="inlineStr">
         <is>
-          <t>مدائح صوم الرسل</t>
+          <t>مدائح احد الشعانين</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>{5F05D018-CCA5-41B9-A869-A1F64A0C2BCC}</t>
+          <t>{37DC4920-98DA-477A-A6F7-6D252B149A22}</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>3371</v>
+        <v>3403</v>
       </c>
       <c r="D470" t="n">
-        <v>3371</v>
+        <v>3403</v>
       </c>
       <c r="E470" t="n">
         <v>1</v>
@@ -10359,19 +10356,19 @@
     <row r="471" ht="18.75" customHeight="1">
       <c r="A471" t="inlineStr">
         <is>
-          <t>مدائح الاعياد السيدية</t>
+          <t>مدائح القيامة</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>{147FD013-1F73-40AC-92A0-5544B48FA888}</t>
+          <t>{1D781881-AD2E-41FE-97D4-458A86F892F1}</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>3372</v>
+        <v>3404</v>
       </c>
       <c r="D471" t="n">
-        <v>3372</v>
+        <v>3404</v>
       </c>
       <c r="E471" t="n">
         <v>1</v>
@@ -10380,19 +10377,19 @@
     <row r="472" ht="18.75" customHeight="1">
       <c r="A472" t="inlineStr">
         <is>
-          <t>مدائح ال29 من الشهر</t>
+          <t>مدائح الخماسين من 2 الى 39</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>{3BE1A381-B11E-4562-921A-ECB2221D0A43}</t>
+          <t>{F74608AC-8E8B-460A-97E7-1E6B86D50B5B}</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>3373</v>
+        <v>3405</v>
       </c>
       <c r="D472" t="n">
-        <v>3373</v>
+        <v>3405</v>
       </c>
       <c r="E472" t="n">
         <v>1</v>
@@ -10401,40 +10398,40 @@
     <row r="473" ht="18.75" customHeight="1">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ابؤرو للتوزيع</t>
+          <t>مدائح الصعود الى العنصرة</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>{7007E16E-5DD0-4268-A326-25AF88EA4DE9}</t>
+          <t>{BAAC56F0-C9A0-4321-AB43-D79F5FCE37C9}</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>3374</v>
+        <v>3406</v>
       </c>
       <c r="D473" t="n">
-        <v>3384</v>
+        <v>3406</v>
       </c>
       <c r="E473" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" ht="18.75" customHeight="1">
       <c r="A474" t="inlineStr">
         <is>
-          <t>الختام</t>
+          <t>مدائح صوم الرسل</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>{90F50AB7-3911-445D-9C45-41866ECCCED0}</t>
+          <t>{5F05D018-CCA5-41B9-A869-A1F64A0C2BCC}</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>3385</v>
+        <v>3407</v>
       </c>
       <c r="D474" t="n">
-        <v>3385</v>
+        <v>3407</v>
       </c>
       <c r="E474" t="n">
         <v>1</v>
@@ -10443,105 +10440,189 @@
     <row r="475" ht="18.75" customHeight="1">
       <c r="A475" t="inlineStr">
         <is>
-          <t>الختام السنوي</t>
+          <t>مدائح الاعياد السيدية</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>{0D2A50D9-F484-4E60-922B-66FF81444E2C}</t>
+          <t>{147FD013-1F73-40AC-92A0-5544B48FA888}</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>3386</v>
+        <v>3408</v>
       </c>
       <c r="D475" t="n">
-        <v>3388</v>
+        <v>3408</v>
       </c>
       <c r="E475" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476" ht="18.75" customHeight="1">
       <c r="A476" t="inlineStr">
         <is>
-          <t>الختام في الصوم المقدس</t>
+          <t>مدائح ال29 من الشهر</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>{4A3AE26D-6D71-4143-8C05-7618E08EF248}</t>
+          <t>{3BE1A381-B11E-4562-921A-ECB2221D0A43}</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>3389</v>
+        <v>3409</v>
       </c>
       <c r="D476" t="n">
-        <v>3394</v>
+        <v>3409</v>
       </c>
       <c r="E476" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477" ht="18.75" customHeight="1">
       <c r="A477" t="inlineStr">
         <is>
+          <t>ابؤرو للتوزيع</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>{7007E16E-5DD0-4268-A326-25AF88EA4DE9}</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>3410</v>
+      </c>
+      <c r="D477" t="n">
+        <v>3420</v>
+      </c>
+      <c r="E477" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="478" ht="18.75" customHeight="1">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>الختام</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>{90F50AB7-3911-445D-9C45-41866ECCCED0}</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>3421</v>
+      </c>
+      <c r="D478" t="n">
+        <v>3421</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" ht="18.75" customHeight="1">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>الختام السنوي</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>{0D2A50D9-F484-4E60-922B-66FF81444E2C}</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>3422</v>
+      </c>
+      <c r="D479" t="n">
+        <v>3424</v>
+      </c>
+      <c r="E479" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="480" ht="18.75" customHeight="1">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>الختام في الصوم المقدس</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>{4A3AE26D-6D71-4143-8C05-7618E08EF248}</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>3425</v>
+      </c>
+      <c r="D480" t="n">
+        <v>3430</v>
+      </c>
+      <c r="E480" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="481" ht="18.75" customHeight="1">
+      <c r="A481" t="inlineStr">
+        <is>
           <t>تكملة على حسب المناسبة</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>{A18EDC94-F257-4FAC-99C7-0A8EA70F0FAF}</t>
         </is>
       </c>
-      <c r="C477" t="n">
-        <v>3395</v>
-      </c>
-      <c r="D477" t="n">
-        <v>3419</v>
-      </c>
-      <c r="E477" t="n">
+      <c r="C481" t="n">
+        <v>3431</v>
+      </c>
+      <c r="D481" t="n">
+        <v>3455</v>
+      </c>
+      <c r="E481" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="482" ht="18.75" customHeight="1">
+      <c r="A482" t="inlineStr">
         <is>
           <t>في حضور الاسقف</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>{A9183893-7B7E-459F-8547-F7A8F7D2D521}</t>
         </is>
       </c>
-      <c r="C478" t="n">
-        <v>3420</v>
-      </c>
-      <c r="D478" t="n">
-        <v>3428</v>
-      </c>
-      <c r="E478" t="n">
+      <c r="C482" t="n">
+        <v>3456</v>
+      </c>
+      <c r="D482" t="n">
+        <v>3464</v>
+      </c>
+      <c r="E482" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="483" ht="18.75" customHeight="1">
+      <c r="A483" t="inlineStr">
         <is>
           <t>الختام 2</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>{A3DED752-5159-4F64-86F6-7B95F37A8327}</t>
         </is>
       </c>
-      <c r="C479" t="n">
-        <v>3429</v>
-      </c>
-      <c r="D479" t="n">
-        <v>3433</v>
-      </c>
-      <c r="E479" t="n">
+      <c r="C483" t="n">
+        <v>3465</v>
+      </c>
+      <c r="D483" t="n">
+        <v>3469</v>
+      </c>
+      <c r="E483" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10556,14 +10637,14 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="41.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -10701,985 +10782,985 @@
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(الصليب) أبدي باسم الثالوث</t>
+          <t>(النيروز) المجد لله في العلاء</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{B5D2D902-B7C5-4CD2-90B3-E801D0A771AC}</t>
+          <t>{CB259C01-3F96-4182-B5D7-67423596F62D}</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(كيهك) الأحد الاول - أمدح فيك يا بكر بتول</t>
+          <t>(النيروز) المجد للمحسن لعبيده</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{BD4BDDEF-F8A3-40F9-AA00-F79127250829}</t>
+          <t>{FE8243A3-0F6A-4A03-B14B-BF23595DD15D}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(كيهك) الأحد الثاني - أبدي باسم الله القدوس</t>
+          <t>(الصليب) أبدي باسم الثالوث</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{325893E1-7DA9-471B-8FFE-4A47EFFA1290}</t>
+          <t>{B5D2D902-B7C5-4CD2-90B3-E801D0A771AC}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="D9" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>(كيهك) الأحد الثالث - خطرت حمامة في بيت زكريا</t>
+          <t>(كيهك) الأحد الاول - أمدح فيك يا بكر بتول</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{7D4E120E-F047-4822-9A8F-DB92B77E97AE}</t>
+          <t>{BD4BDDEF-F8A3-40F9-AA00-F79127250829}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>(كيهك) الأحد الثالث - أبدي باسم الله القدوس</t>
+          <t>(كيهك) الأحد الثاني - أبدي باسم الله القدوس</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{15C386D8-99E3-43B2-B79E-47764A58CF47}</t>
+          <t>{325893E1-7DA9-471B-8FFE-4A47EFFA1290}</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>(كيهك) الأحد الرابع - أنا أفتح فاي بالتسبيح</t>
+          <t>(كيهك) الأحد الثالث - خطرت حمامة في بيت زكريا</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{423C4D73-197C-4744-9EE2-7AA3DE33C016}</t>
+          <t>{7D4E120E-F047-4822-9A8F-DB92B77E97AE}</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="D12" t="n">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>(البشارة) ابدأ باسم الله القدوس</t>
+          <t>(كيهك) الأحد الثالث - أبدي باسم الله القدوس</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{015AB153-74F1-4FF7-9277-8508A321E7CB}</t>
+          <t>{15C386D8-99E3-43B2-B79E-47764A58CF47}</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="D13" t="n">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>(الميلاد) أنا افتح فاي بمجد الله</t>
+          <t>(كيهك) الأحد الرابع - أنا أفتح فاي بالتسبيح</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{99CFF969-C99E-48F8-A8E9-E208BA5E4210}</t>
+          <t>{423C4D73-197C-4744-9EE2-7AA3DE33C016}</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D14" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>(القيامة) أنا افتح فمي وأتكلم</t>
+          <t>(البشارة) ابدأ باسم الله القدوس</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{05FB6036-013E-4B49-AF1F-F51A76197290}</t>
+          <t>{015AB153-74F1-4FF7-9277-8508A321E7CB}</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D15" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>(تذكار الاعياد السيدية) المجد للآب خالقنا</t>
+          <t>(الميلاد) أنا افتح فاي بمجد الله</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{A11F2970-128A-421A-92A7-78C73AEA4270}</t>
+          <t>{99CFF969-C99E-48F8-A8E9-E208BA5E4210}</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D16" t="n">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>(صوم نينوى) الصوم الصوم للنفس ثبات</t>
+          <t>(القيامة) أنا افتح فمي وأتكلم</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{22B730C4-9A84-4D38-B8FD-3409EF83C4BD}</t>
+          <t>{05FB6036-013E-4B49-AF1F-F51A76197290}</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D17" t="n">
         <v>434</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الاول - الصوم الصوم للنفس ثبات</t>
+          <t>(تذكار الاعياد السيدية) المجد للآب خالقنا</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{19C963C1-49D7-4905-842B-977245127917}</t>
+          <t>{A11F2970-128A-421A-92A7-78C73AEA4270}</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>435</v>
       </c>
       <c r="D18" t="n">
-        <v>516</v>
+        <v>450</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الثاني - سر عجيب هو سر المسيح</t>
+          <t>(صوم نينوى) الصوم الصوم للنفس ثبات</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{4A2CC73C-A3C7-45E5-9BFE-FBC538653C4B}</t>
+          <t>{22B730C4-9A84-4D38-B8FD-3409EF83C4BD}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c r="D19" t="n">
-        <v>573</v>
+        <v>491</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الثالث - الصوم هو حصن غير مهدوم</t>
+          <t>(الصوم الكبير) الاسبوع الاول - الصوم الصوم للنفس ثبات</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{4CDA093F-DDF6-4FED-8316-8CFC4A383925}</t>
+          <t>{19C963C1-49D7-4905-842B-977245127917}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>574</v>
+        <v>492</v>
       </c>
       <c r="D20" t="n">
-        <v>692</v>
+        <v>573</v>
       </c>
       <c r="E20" t="n">
-        <v>119</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الرابع - الصوم هو حصن غير مهدوم</t>
+          <t>(الصوم الكبير) الاسبوع الثاني - سر عجيب هو سر المسيح</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{FE32734F-5C08-4A79-BCCD-16672ABB653D}</t>
+          <t>{4A2CC73C-A3C7-45E5-9BFE-FBC538653C4B}</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>693</v>
+        <v>574</v>
       </c>
       <c r="D21" t="n">
-        <v>773</v>
+        <v>630</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع السابع و ختام الصوم ـ الصوم الصوم يا شعب يسوع</t>
+          <t>(الصوم الكبير) الاسبوع الثالث - الصوم هو حصن غير مهدوم</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{3DD0F949-75DE-4846-840E-7878908DF90E}</t>
+          <t>{4CDA093F-DDF6-4FED-8316-8CFC4A383925}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>774</v>
+        <v>631</v>
       </c>
       <c r="D22" t="n">
-        <v>824</v>
+        <v>749</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>(احد الشعانين) اليومَ تمت الأقوال</t>
+          <t>(الصوم الكبير) الاسبوع الرابع - الصوم هو حصن غير مهدوم</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{51A8EA9C-25BB-445D-B0EF-E66FBADDBE1A}</t>
+          <t>{FE32734F-5C08-4A79-BCCD-16672ABB653D}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>825</v>
+        <v>750</v>
       </c>
       <c r="D23" t="n">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(احد الشعانين) الجالس فوق الشاروبيم</t>
+          <t>(الصوم الكبير) الاسبوع السابع و ختام الصوم ـ الصوم الصوم يا شعب يسوع</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{2E674F43-188F-46C4-B421-E7ADF4DB57C7}</t>
+          <t>{3DD0F949-75DE-4846-840E-7878908DF90E}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="D24" t="n">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(احد الشعانين) المجد لله الأوحد</t>
+          <t>(احد الشعانين) اليومَ تمت الأقوال</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{D5D7C4B4-CC66-4076-8A09-DFD723D50F03}</t>
+          <t>{51A8EA9C-25BB-445D-B0EF-E66FBADDBE1A}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>857</v>
+        <v>882</v>
       </c>
       <c r="D25" t="n">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="E25" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(احد الشعانين) أوصنا يا ابن داود</t>
+          <t>(احد الشعانين) الجالس فوق الشاروبيم</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{FC1EEFC2-F019-4CD5-BD5A-23F9E734E63A}</t>
+          <t>{2E674F43-188F-46C4-B421-E7ADF4DB57C7}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D26" t="n">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>(خميس العهد) ليل العشاء السري</t>
+          <t>(احد الشعانين) المجد لله الأوحد</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{F55CB762-4A57-49B3-A691-C8660FCFC634}</t>
+          <t>{D5D7C4B4-CC66-4076-8A09-DFD723D50F03}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D27" t="n">
-        <v>923</v>
+        <v>956</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (خميس العهد) إن فادينا دعانا</t>
+          <t>(احد الشعانين) أوصنا يا ابن داود</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{1A183E7B-87A1-4C2F-841E-DFEC3B4A7D2F}</t>
+          <t>{FC1EEFC2-F019-4CD5-BD5A-23F9E734E63A}</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>924</v>
+        <v>957</v>
       </c>
       <c r="D28" t="n">
-        <v>939</v>
+        <v>967</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>(خميس العهد) أوصنا يا إبن داود</t>
+          <t>(خميس العهد) ليل العشاء السري</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{59DFCA58-6399-41A0-AB3D-6A5B0D8DDFBC}</t>
+          <t>{F55CB762-4A57-49B3-A691-C8660FCFC634}</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>940</v>
+        <v>968</v>
       </c>
       <c r="D29" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>(القيامة) مديح واطس لعشية - الله الأزلي قبل الأوقات</t>
+          <t xml:space="preserve"> (خميس العهد) إن فادينا دعانا</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{A72E6126-0320-4081-9967-7CDEDE602A51}</t>
+          <t>{1A183E7B-87A1-4C2F-841E-DFEC3B4A7D2F}</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>950</v>
+        <v>981</v>
       </c>
       <c r="D30" t="n">
-        <v>979</v>
+        <v>996</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>(القيامة) سبع قطع لباكر - المجد والعظمة للإله</t>
+          <t>(خميس العهد) أوصنا يا إبن داود</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{0D4A51F9-2CBC-4DB3-8764-00D5D185E9D3}</t>
+          <t>{59DFCA58-6399-41A0-AB3D-6A5B0D8DDFBC}</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>980</v>
+        <v>997</v>
       </c>
       <c r="D31" t="n">
-        <v>1030</v>
+        <v>1006</v>
       </c>
       <c r="E31" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>(القيامة) مديح للتوزيع - أنا افتح فمي و أتكلم</t>
+          <t>(القيامة) مديح واطس لعشية - الله الأزلي قبل الأوقات</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{41289D73-8401-47A3-BC9E-30C25C21967A}</t>
+          <t>{A72E6126-0320-4081-9967-7CDEDE602A51}</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1031</v>
+        <v>1007</v>
       </c>
       <c r="D32" t="n">
-        <v>1059</v>
+        <v>1036</v>
       </c>
       <c r="E32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الأول - أبدأ باسم الله القدوس</t>
+          <t>(القيامة) سبع قطع لباكر - المجد والعظمة للإله</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{E652151D-56BC-4E03-935C-6CB473E64AC9}</t>
+          <t>{0D4A51F9-2CBC-4DB3-8764-00D5D185E9D3}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1060</v>
+        <v>1037</v>
       </c>
       <c r="D33" t="n">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الثاني - أنا أفتح فمي بمجد الله</t>
+          <t>(القيامة) مديح للتوزيع - أنا افتح فمي و أتكلم</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{12A7A1D0-EC34-4F91-93B4-77F40C22A4E0}</t>
+          <t>{41289D73-8401-47A3-BC9E-30C25C21967A}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="D34" t="n">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الثالث - المجد يليق والأكرام</t>
+          <t>(الخماسين) الاسبوع الأول - أبدأ باسم الله القدوس</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{CCFAA7F8-17F8-4620-BE25-841890829953}</t>
+          <t>{E652151D-56BC-4E03-935C-6CB473E64AC9}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="D35" t="n">
-        <v>1168</v>
+        <v>1148</v>
       </c>
       <c r="E35" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الرابع - أنا أفتح فمي واتكلم</t>
+          <t>(الخماسين) الاسبوع الثاني - أنا أفتح فمي بمجد الله</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{6896F5AC-12DD-450D-A6A9-E7A0FC24A7D1}</t>
+          <t>{12A7A1D0-EC34-4F91-93B4-77F40C22A4E0}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1169</v>
+        <v>1149</v>
       </c>
       <c r="D36" t="n">
-        <v>1225</v>
+        <v>1168</v>
       </c>
       <c r="E36" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الخامس - أبدى باسم الله القدوس</t>
+          <t>(الخماسين) الاسبوع الثالث - المجد يليق والأكرام</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{F0F8F790-9F1B-48CC-B4CF-E7411C57B0C8}</t>
+          <t>{CCFAA7F8-17F8-4620-BE25-841890829953}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1226</v>
+        <v>1169</v>
       </c>
       <c r="D37" t="n">
-        <v>1286</v>
+        <v>1225</v>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع السادس - أنا أفتح فاي وأخبركم</t>
+          <t>(الخماسين) الاسبوع الرابع - أنا أفتح فمي واتكلم</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{852F6F54-9767-4FF5-B8C5-8BE0B6729F8D}</t>
+          <t>{6896F5AC-12DD-450D-A6A9-E7A0FC24A7D1}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1287</v>
+        <v>1226</v>
       </c>
       <c r="D38" t="n">
-        <v>1302</v>
+        <v>1282</v>
       </c>
       <c r="E38" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>(الخماسين) عيد الصعود - المجد لله والأكرام</t>
+          <t>(الخماسين) الاسبوع الخامس - أبدى باسم الله القدوس</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{0B00A682-598E-42FA-9F88-D72EAFF6E783}</t>
+          <t>{F0F8F790-9F1B-48CC-B4CF-E7411C57B0C8}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1303</v>
+        <v>1283</v>
       </c>
       <c r="D39" t="n">
-        <v>1319</v>
+        <v>1343</v>
       </c>
       <c r="E39" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>(الخماسين) عيد العنصرة - المجد لله القدوس</t>
+          <t>(الخماسين) الاسبوع السادس - أنا أفتح فاي وأخبركم</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{C028FF9B-09C1-42E1-90E0-2C45A634BAF0}</t>
+          <t>{852F6F54-9767-4FF5-B8C5-8BE0B6729F8D}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1320</v>
+        <v>1344</v>
       </c>
       <c r="D40" t="n">
-        <v>1337</v>
+        <v>1359</v>
       </c>
       <c r="E40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>(صوم وعيد الرسل) الفاعل الأمين لا يخزى</t>
+          <t>(الخماسين) عيد الصعود - المجد لله والأكرام</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{B9A8D07C-0514-491C-A91B-A5BD0B14C556}</t>
+          <t>{0B00A682-598E-42FA-9F88-D72EAFF6E783}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1338</v>
+        <v>1360</v>
       </c>
       <c r="D41" t="n">
-        <v>1367</v>
+        <v>1376</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>(صوم و عيد الرسل) فلنسبح إلهنا القـدوس</t>
+          <t>(الخماسين) عيد العنصرة - المجد لله القدوس</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{FFAC3DB8-CD69-4363-AEEE-0A77AFA5C14C}</t>
+          <t>{C028FF9B-09C1-42E1-90E0-2C45A634BAF0}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1368</v>
+        <v>1377</v>
       </c>
       <c r="D42" t="n">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>(التجلي) المجد لله ذي الرحمة</t>
+          <t>(صوم وعيد الرسل) الفاعل الأمين لا يخزى</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{72B6A886-BE5B-444C-ADB8-80108ED1C462}</t>
+          <t>{B9A8D07C-0514-491C-A91B-A5BD0B14C556}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="D43" t="n">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="E43" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>(سنوي) ابانا الذي في السموات</t>
+          <t>(صوم و عيد الرسل) فلنسبح إلهنا القـدوس</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{55AD0713-7619-4F4A-BBF7-CBEC78E9D2B6}</t>
+          <t>{FFAC3DB8-CD69-4363-AEEE-0A77AFA5C14C}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="D44" t="n">
-        <v>1428</v>
+        <v>1454</v>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>(سنوي) اسمعوا يا شعب المسيح</t>
+          <t>(التجلي) المجد لله ذي الرحمة</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{FBABEA1B-1917-427E-BD5E-EB2368CB6293}</t>
+          <t>{72B6A886-BE5B-444C-ADB8-80108ED1C462}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1429</v>
+        <v>1455</v>
       </c>
       <c r="D45" t="n">
-        <v>1457</v>
+        <v>1471</v>
       </c>
       <c r="E45" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>(سنوي) المجد لمن رفع السموات</t>
+          <t>(سنوي) ابانا الذي في السموات</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{12A69F25-ED75-4850-8C2A-4864364C2131}</t>
+          <t>{55AD0713-7619-4F4A-BBF7-CBEC78E9D2B6}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1458</v>
+        <v>1472</v>
       </c>
       <c r="D46" t="n">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="E46" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>(سنوي) أول ما أبدي أسبح الإله</t>
+          <t>(سنوي) اسمعوا يا شعب المسيح</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{BA707332-FF09-40ED-BD05-0F3CE5931805}</t>
+          <t>{FBABEA1B-1917-427E-BD5E-EB2368CB6293}</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="D47" t="n">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="E47" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>الباب الثاني</t>
+          <t>(سنوي) المجد لمن رفع السموات</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{E9ED8CBA-74AF-4903-9BE7-83949A2E6042}</t>
+          <t>{12A69F25-ED75-4850-8C2A-4864364C2131}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="D48" t="n">
-        <v>1519</v>
+        <v>1545</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>أبادير وإيرائي اخته</t>
+          <t>(سنوي) أول ما أبدي أسبح الإله</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{418E980F-1BC4-40C4-AED7-1DE2566AF0A8}</t>
+          <t>{BA707332-FF09-40ED-BD05-0F3CE5931805}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1520</v>
+        <v>1546</v>
       </c>
       <c r="D49" t="n">
-        <v>1544</v>
+        <v>1575</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>أبا اسخيرون القليني</t>
+          <t>الباب الثاني</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{21D2DCA4-5857-4F13-886C-A79FCE9F45CF}</t>
+          <t>{E9ED8CBA-74AF-4903-9BE7-83949A2E6042}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1545</v>
+        <v>1576</v>
       </c>
       <c r="D50" t="n">
-        <v>1556</v>
+        <v>1576</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>أباكراجون البتانوني</t>
+          <t>أبادير وإيرائي اخته</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{C6670786-A976-4B52-868E-171137C94BF0}</t>
+          <t>{418E980F-1BC4-40C4-AED7-1DE2566AF0A8}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1557</v>
+        <v>1577</v>
       </c>
       <c r="D51" t="n">
-        <v>1572</v>
+        <v>1601</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>اباكير و يوحنا</t>
+          <t>أبا اسخيرون القليني</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{94B1CF6F-400F-4EBB-BEB3-7561B8B79E22}</t>
+          <t>{21D2DCA4-5857-4F13-886C-A79FCE9F45CF}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1573</v>
+        <v>1602</v>
       </c>
       <c r="D52" t="n">
-        <v>1589</v>
+        <v>1613</v>
       </c>
       <c r="E52" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>أبانوب النهيسي</t>
+          <t>أباكراجون البتانوني</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{B7505EB8-9095-443D-8AB4-76B429FB6882}</t>
+          <t>{C6670786-A976-4B52-868E-171137C94BF0}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1590</v>
+        <v>1614</v>
       </c>
       <c r="D53" t="n">
-        <v>1605</v>
+        <v>1629</v>
       </c>
       <c r="E53" t="n">
         <v>16</v>
@@ -11688,253 +11769,253 @@
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>الأنبا إبرآم أسقف الفيوم</t>
+          <t>اباكير و يوحنا</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{76A5C39E-E378-49E4-A1B3-3C3C6AD0FC45}</t>
+          <t>{94B1CF6F-400F-4EBB-BEB3-7561B8B79E22}</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1606</v>
+        <v>1630</v>
       </c>
       <c r="D54" t="n">
-        <v>1625</v>
+        <v>1646</v>
       </c>
       <c r="E54" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>الأنبا أبوللو والأنبا أبيب</t>
+          <t>أبانوب النهيسي</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{15F37CDF-162E-4235-B0CD-3EC560293C8F}</t>
+          <t>{B7505EB8-9095-443D-8AB4-76B429FB6882}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1626</v>
+        <v>1647</v>
       </c>
       <c r="D55" t="n">
-        <v>1644</v>
+        <v>1662</v>
       </c>
       <c r="E55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>الشهيد مارجرجس الروماني</t>
+          <t>الأنبا إبرآم أسقف الفيوم</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{FFF1B9FE-C89C-4F56-85B7-F375461AEA62}</t>
+          <t>{76A5C39E-E378-49E4-A1B3-3C3C6AD0FC45}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1645</v>
+        <v>1663</v>
       </c>
       <c r="D56" t="n">
-        <v>1656</v>
+        <v>1682</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>القديس لوقا الانجيلي</t>
+          <t>الأنبا أبوللو والأنبا أبيب</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{50EEB170-6F56-438C-943C-B8B3136DBB6A}</t>
+          <t>{15F37CDF-162E-4235-B0CD-3EC560293C8F}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1657</v>
+        <v>1683</v>
       </c>
       <c r="D57" t="n">
-        <v>1674</v>
+        <v>1701</v>
       </c>
       <c r="E57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>القديس مارمرقس الرسول</t>
+          <t>الشهيد مارجرجس الروماني</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{D4872368-E5CE-4B87-A314-70582CB26D33}</t>
+          <t>{FFF1B9FE-C89C-4F56-85B7-F375461AEA62}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1675</v>
+        <v>1702</v>
       </c>
       <c r="D58" t="n">
-        <v>1693</v>
+        <v>1713</v>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>العذراء مريم</t>
+          <t>القديس لوقا الانجيلي</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{BC31EDAD-70A8-41AD-8F09-30FB6E612B63}</t>
+          <t>{50EEB170-6F56-438C-943C-B8B3136DBB6A}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1694</v>
+        <v>1714</v>
       </c>
       <c r="D59" t="n">
-        <v>1712</v>
+        <v>1731</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>الملاك ميخائيل</t>
+          <t>القديس مارمرقس الرسول</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{12793581-7FD0-4EE7-B903-2943F410A5D2}</t>
+          <t>{D4872368-E5CE-4B87-A314-70582CB26D33}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1713</v>
+        <v>1732</v>
       </c>
       <c r="D60" t="n">
-        <v>1724</v>
+        <v>1750</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>الملاك غبريال</t>
+          <t>العذراء مريم</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{FFD2036A-0F2D-47E3-B5B9-AC167E3F6FF3}</t>
+          <t>{BC31EDAD-70A8-41AD-8F09-30FB6E612B63}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1725</v>
+        <v>1751</v>
       </c>
       <c r="D61" t="n">
-        <v>1736</v>
+        <v>1769</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>الباب الثالث</t>
+          <t>الملاك ميخائيل</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{E5B98BC1-9C9D-42EC-BB16-E848179FB9DC}</t>
+          <t>{12793581-7FD0-4EE7-B903-2943F410A5D2}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1737</v>
+        <v>1770</v>
       </c>
       <c r="D62" t="n">
-        <v>1737</v>
+        <v>1781</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>رحلة الصوم الكبير</t>
+          <t>الملاك غبريال</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{11755A37-6BDF-4E72-9537-F39867C5BB7D}</t>
+          <t>{FFD2036A-0F2D-47E3-B5B9-AC167E3F6FF3}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1738</v>
+        <v>1782</v>
       </c>
       <c r="D63" t="n">
-        <v>1744</v>
+        <v>1793</v>
       </c>
       <c r="E63" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>عند شق الفجر باكر</t>
+          <t>الباب الثالث</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{D4859CD1-25CE-465C-846E-A0311D24DB66}</t>
+          <t>{E5B98BC1-9C9D-42EC-BB16-E848179FB9DC}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1745</v>
+        <v>1794</v>
       </c>
       <c r="D64" t="n">
-        <v>1777</v>
+        <v>1794</v>
       </c>
       <c r="E64" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>قام حقا</t>
+          <t>أعروس الفادي القبطية</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{4615B620-F94D-4CAD-843A-EB32E8369AAB}</t>
+          <t>{3CBD5E49-3BE4-475A-A6D3-2858A4DB1030}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1778</v>
+        <v>1795</v>
       </c>
       <c r="D65" t="n">
-        <v>1791</v>
+        <v>1823</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
@@ -11949,10 +12030,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1792</v>
+        <v>1824</v>
       </c>
       <c r="D66" t="n">
-        <v>1806</v>
+        <v>1838</v>
       </c>
       <c r="E66" t="n">
         <v>15</v>
@@ -11961,21 +12042,147 @@
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
+          <t>رحلة الصوم الكبير</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>{11755A37-6BDF-4E72-9537-F39867C5BB7D}</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1839</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1845</v>
+      </c>
+      <c r="E67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" ht="18.75" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>عند شق الفجر باكر</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>{D4859CD1-25CE-465C-846E-A0311D24DB66}</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E68" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" ht="18.75" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>قام حقا</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>{4615B620-F94D-4CAD-843A-EB32E8369AAB}</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1879</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1892</v>
+      </c>
+      <c r="E69" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" ht="18.75" customHeight="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>كنيستي أرجو لك</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>{8A08F2A7-DAF4-4998-9EF9-8221744F0038}</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1893</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1903</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" ht="18.75" customHeight="1">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>كنيستي القبطية كنيسة الإله</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>{B1A30565-0CDB-40D5-8B05-21F68D5C9160}</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1930</v>
+      </c>
+      <c r="E71" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" ht="18.75" customHeight="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>كنيستي القبطية نشرت المسيحية</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>{AB60D02D-F80E-4E53-B0A0-3A54593EB31B}</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1943</v>
+      </c>
+      <c r="E72" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" ht="18.75" customHeight="1">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>يا ربنا مولى السلام</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>{325B4DE6-FA63-4B6D-827F-BCC78EF1FEC9}</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>1807</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1850</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="C73" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1987</v>
+      </c>
+      <c r="E73" t="n">
         <v>44</v>
       </c>
     </row>
@@ -11995,9 +12202,9 @@
   <cols>
     <col width="20.29071428571428" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -12344,9 +12551,9 @@
   <cols>
     <col width="15.29071428571429" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -12735,9 +12942,9 @@
   <cols>
     <col width="17.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -13399,9 +13606,9 @@
   <cols>
     <col width="28.43357142857143" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -18818,947 +19025,953 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20.71928571428571" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Section Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Section ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>First Slide Number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Last Slide Number</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Number of Slides</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>اليسون ايماس (باكر)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>{BAB6351C-8F49-4AF7-A6DA-7BC3E0D82644}</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>صلاة الشكر</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>{7E6178CD-134C-4213-83A1-1BF57030499A}</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ارباع الناقوس</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>{8B27D80D-B166-4555-85E2-39A92ED59D83}</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ارباع الناقوس الادام</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>{D02C088A-01E0-4A8C-8D73-21E3FD3616EB}</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>أرباع الناقوس الواطس</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>{9495E38B-CE03-4E75-AED4-960DE95BA747}</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>تكملة ارباع الناقوس</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>{0120814B-6347-4FF3-9CA8-883FC9FEF728}</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>تكملة ارباع الناقوس 2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>{3C444163-4B5E-4306-8A8A-489D9AF24A2A}</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ارباع الناقوس فرايحي</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>{51C36C67-358C-4892-BD9C-2F7E2876602E}</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>تكملة ارباع الناقوس الفرايحي</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>{4F03AFB7-A6ED-4B11-9B20-66C18A7A3B43}</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ختام ارباع الناقوس</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>{B87EBA1A-E0E4-4E68-87D7-3C4A798CF278}</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>اوشية الراقدين</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>{5ED0058A-E113-43EA-826B-8CFF85D1E0B1}</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>اوشية المرضي</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>{069F7A79-999B-4223-82AE-CAF356118167}</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>السبع طرايق</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>{385BAEA4-D798-4AD0-920D-ADEC0B972186}</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>142</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>اوشية المسافرين</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>{A059EEC9-5D25-453F-A956-A2E149F0773C}</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>391</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>419</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>اوشية القرابين</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>{2C897F14-44CC-430E-9BE1-EB379FE7A9C7}</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>420</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>449</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>فلنسبح مع الملائكة</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>{2ECE1F1B-C143-4CE2-B550-348BEE185974}</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>450</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>469</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>مقدمة الذوكصولجيات</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>{A844BC14-2548-4840-ADC5-0CE69C53FD26}</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>470</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>490</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ذكصولوجية العذراء باكر</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>{9621F9CE-ABC8-4FF6-A8C6-3AA9D24690A0}</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>491</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>511</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>العدراء عشية</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>{A8C38D6F-163F-43BD-9D48-1D5BD7895F37}</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>512</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>521</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>الملاك يمخائيل</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>{2DF9DA91-F75F-4421-952F-5C53E381AD5C}</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>522</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>529</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>السمائيين</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>{19B2B411-A081-44A9-A9D4-6984C6562464}</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="3" t="n">
         <v>530</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>541</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="3" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>الرسل</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>{2387AF74-BB8E-4CCF-B053-FD51E1D73752}</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="3" t="n">
         <v>542</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>549</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>بطرس و بولس</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>{81E5C2F6-C71A-4711-83D2-FBF56C7FD101}</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="3" t="n">
         <v>550</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>561</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="3" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>مارمرقس</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>{38DFA630-51F2-4B3D-B8C1-DCD7E5437697}</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="3" t="n">
         <v>562</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>569</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>استفانوس</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>{209C3EAC-5409-4876-9A9B-D128FC987C62}</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="3" t="n">
         <v>570</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>579</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>مارجرجس</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>{B4C861C7-1754-4DC5-BDD2-71012C4162B9}</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>ختام الذوكصولجيات</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>{993398CB-4D3A-460E-BB58-16A4CE243F38}</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="3" t="n">
         <v>588</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>595</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>قانون الايمان</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>{03485131-4F01-4089-94A4-376623C60D5D}</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="3" t="n">
         <v>596</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>616</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>افنوتي ناي نان</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>{61880C5D-7B19-4DA9-9517-587F0006E7A4}</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="3" t="n">
         <v>617</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>626</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>دورة الصليب</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>{9402F031-15CE-461A-BAAF-ECBBCBEABDBC}</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="3" t="n">
         <v>627</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>774</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>اوشية الانجيل</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>{8A6D5C5D-CC6E-42BB-B6EA-98569DF56779}</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="3" t="n">
         <v>775</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>مارو اتشاسف</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>{99CAC194-A18E-4EA4-8D93-C7B66B816EE5}</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="3" t="n">
         <v>801</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>804</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>مرد المزمور الشعانين</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>{4101FB26-80C4-4B94-9B5C-31C7D72BE02D}</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="3" t="n">
         <v>805</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>806</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>مرد المزمور</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>{AB2B0CF5-7465-4457-BFC8-4E1205EA1B21}</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="3" t="n">
         <v>807</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>807</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>مقدمة الانجيل</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>{DF64771F-5EFF-4EFE-A4A8-4EFE76083EC1}</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="3" t="n">
         <v>808</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>818</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>الانجيل قبطي</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>{B39F1356-4D6C-4165-9619-14EF091FCF09}</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="3" t="n">
         <v>819</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>823</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>الانجيل</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>{385FAEA1-2238-4574-A5A0-FC50C6EC81E1}</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="3" t="n">
         <v>824</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>833</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>مرد انجيل باكر الشعانين</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>{C5445028-B6A0-4403-884C-6A54E71F6EBD}</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="3" t="n">
         <v>834</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>836</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>مرد الانجيل باكر</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>{BEECCC68-2AEF-4568-91AA-98BCD14D3B92}</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="3" t="n">
         <v>837</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>839</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>ربع يقال في صوم الرسل</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>{F5AB11D4-D7D2-4DA3-A830-32BA45BCB16D}</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>جي افسمارؤوت</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>{DD53DBD3-9599-4D1D-B8C1-EAB35FBD36D3}</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="3" t="n">
         <v>841</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>842</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>ابانا الذي في السموات</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>{F8657D52-0E61-475D-90AC-DB10509A5D22}</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="3" t="n">
         <v>843</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>858</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>ختام الصلوات</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>{BEEAE6F0-9166-497C-86B7-417C571F8944}</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="3" t="n">
         <v>859</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>872</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="45" ht="18.75" customHeight="1"/>
+    <row r="45" ht="18.75" customHeight="1">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19770,1703 +19983,1709 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Section Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Section ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>First Slide Number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Last Slide Number</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Number of Slides</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>اليسون ايماس</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>{BAB6351C-8F49-4AF7-A6DA-7BC3E0D82644}</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>صلاة الشكر</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>{03B57C83-EC25-40DE-9969-D1416437B668}</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ارباع الناقوس</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>{8B27D80D-B166-4555-85E2-39A92ED59D83}</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ارباع الناقوس الادام</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>{D02C088A-01E0-4A8C-8D73-21E3FD3616EB}</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>أرباع الناقوس الواطس</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>{9495E38B-CE03-4E75-AED4-960DE95BA747}</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>تكملة ارباع الناقوس</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>{0120814B-6347-4FF3-9CA8-883FC9FEF728}</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>تكملة ارباع الناقوس 2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>{3C444163-4B5E-4306-8A8A-489D9AF24A2A}</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ختام ارباع الناقوس</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>{52EB6B04-BCFD-460D-A692-2D541D7484D5}</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ختام ارباع الناقوس الفرايحي</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>{B87EBA1A-E0E4-4E68-87D7-3C4A798CF278}</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>اوشية الراقدين</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>{83E6BC33-A9EC-45CA-89B6-24EFBC51B654}</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>تفضل يا رب</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>{D8AFA182-3999-4072-94E9-F65D50B876B9}</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>مقدمة الذوكصولوجيات</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>{D72E4090-F25E-47FA-91CC-49FA1BFA5556}</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="3" t="n">
         <v>198</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ذكصولوجية الصليب</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>{C7BDC7C7-019E-4A5F-8438-CD8E144D52F1}</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="3" t="n">
         <v>214</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ذكصولوجية التجلي</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>{DC61EC21-9EF0-4E7C-8E4E-CD4269024AE6}</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>قائمة الذكصولوجيات</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>{D0DE0DB5-B996-4112-BA51-F26B12ECA9F1}</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>241</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>العذراء والدة الاله</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>{267B00F5-E8C1-4DF6-A5CB-DFF5531064E8}</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ميخائيل رئيس الملائكه</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>{587F2187-AC08-4FA1-A543-DE7AF1E6D642}</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>السمائين</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>{49EDE834-BC88-4FFE-AC72-EB777F4C014F}</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>يوحنا المعمدان</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>{1D8E1CE8-DD12-4876-B140-508806EABA7E}</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="3" t="n">
         <v>268</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>الرسل</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>{FD3C940F-1D13-465A-BDD8-A7F81854ED40}</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="3" t="n">
         <v>272</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>277</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>مارمرقس</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>{0269CF42-BC07-405C-9C64-D7D9519BFD7B}</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>إستفانوس</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>{A00FA592-D399-47C6-9A3E-4E0AB63517AA}</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>291</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>مارجرجس</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>{2E4F1F7B-1D5B-4980-886C-CCE4F8163F62}</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="3" t="n">
         <v>292</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>297</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>الشهيد فيلوباتير مرقوريوس</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>{E7EA499B-B3B0-44ED-A6D1-7E24579DED91}</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="3" t="n">
         <v>298</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>305</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>الشهيد مارمينا</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>{EEB4FA54-386E-454B-8A7D-29D05B5616C5}</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="3" t="n">
         <v>306</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>311</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>الأنبا أنطونيوس</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>{84FAB6BF-A555-4AEB-9336-608E93DE4A97}</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="3" t="n">
         <v>312</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>319</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>الانبا بولا</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>{92DF5EE6-CAC9-48C3-8BEC-59BEF8DCF65D}</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>325</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>الأنبا بيشوى و الأنبا بولا</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>{0EF7C112-4EED-42CA-9672-FDAC6D5ECA6F}</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="3" t="n">
         <v>326</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>332</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ختام الذوكصولوجيات</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>{4AC87784-88F2-4407-A37B-FE777E0B9CBC}</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="3" t="n">
         <v>333</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>قانون الإيمان</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>{BA246F91-8526-4A8F-8E43-CEF5EEE442BB}</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="3" t="n">
         <v>341</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>359</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>افنوتي ناي نان</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>{61880C5D-7B19-4DA9-9517-587F0006E7A4}</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>370</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ايطاف اني اسخاي</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>{60A6EF5E-A7D1-4E39-AAE6-A0EA92726711}</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="3" t="n">
         <v>371</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>384</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>طرح عيد الصليب</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>{17F6A454-5ABF-4DFB-A78A-D146D086082D}</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="3" t="n">
         <v>385</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>389</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>طرح اخر لعيد الصليب</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>{0BD005D7-2E83-417A-9686-5430EAAF391B}</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>394</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>مرد طرح عيد الصليب</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>{68F134B0-811C-48F0-A7D0-5BB19CE61443}</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="3" t="n">
         <v>395</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>395</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>أفرحى يا مريم</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>{1C20AEEF-0DEB-4F74-A46A-AFC5A06DC744}</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="3" t="n">
         <v>396</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>409</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>تماجيد نهضة العذراء</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>{7DE226B6-2157-492D-AB80-4448CDB8A41A}</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="3" t="n">
         <v>410</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>410</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>لحن شيري ماريا</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>{1E7E7987-2CAA-4858-AB80-5A0AF761B6EF}</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="3" t="n">
         <v>411</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>431</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>إك اسماروؤت</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>{D2101135-3E00-460B-BDBC-0ED4AE799C01}</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="3" t="n">
         <v>432</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>433</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>لحن شيرى ثيؤطوكى</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>{18389A37-F3FC-4832-AAAE-BB56BAA2569D}</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="3" t="n">
         <v>434</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>443</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>لحن أو كيريوس</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>{9374086D-AF79-49C7-AD9E-A4DD1D98361A}</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="3" t="n">
         <v>444</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>459</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>شاشف إنسوب إمميني</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>{93BD22E8-BF7D-4E60-A57A-13DAE76001A3}</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="3" t="n">
         <v>460</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>لحن راشى نى</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>{0506AF9A-7F49-49A6-942D-C2D14565C280}</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="3" t="n">
         <v>498</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>512</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>ذفتية بانديس</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>{E63D9888-2FCA-494A-AA68-15E76387F435}</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="3" t="n">
         <v>513</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>538</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="3" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>سينا اتشو</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>{63C8AA8A-342F-4B05-BFCE-A3098B55F558}</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="3" t="n">
         <v>539</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>550</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="3" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>فاي بى إبليمين</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>{01E8A009-C53E-4034-AA0C-E39290F9C47E}</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="3" t="n">
         <v>551</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>567</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="3" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>اطاي بارثينوس</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>{18835C90-087E-4BAC-9D66-708BC1E04983}</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="3" t="n">
         <v>568</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>589</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="3" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>او اون او هلبيس</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>{1F005296-1C13-4026-A9B3-26C9C6CD6D9D}</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>596</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="3" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>اري ابرسفافين</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>{A72D1337-AC85-4792-8213-9E4E0B9D5DDB}</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="3" t="n">
         <v>597</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>598</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>ابؤرو</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>{DD757736-F2EB-40FA-9016-1E28087A0BE5}</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="3" t="n">
         <v>599</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>608</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>مديح السلام لك يا مريم</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>{1796645F-35B4-4F6F-9673-838DE7EF8F58}</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="3" t="n">
         <v>609</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>639</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="3" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>خين أفران</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>{FD75781B-0996-4E12-BF4C-D163B4D1708F}</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>642</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>اسمعي يا ابنة</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>{3C5D9889-94E1-4B35-82B5-58786720BA8A}</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="3" t="n">
         <v>643</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>647</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>اوشية الانجيل</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>{B897D380-076C-414A-9934-423AA6230FED}</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="3" t="n">
         <v>648</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>673</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="3" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>مرد مزمور الصليب</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>{0BC1F8D8-BE35-4C07-A134-EAB9CF63D177}</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="3" t="n">
         <v>674</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>675</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>مرد مزمور التجلي</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>{B4E31E38-8F7C-4D46-A7DE-F133483CE935}</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="3" t="n">
         <v>676</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>676</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>مزمور صوم وعشيات اعياد السيدة العذراء</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>{AB54231C-F141-461A-8580-187ADC04F4DB}</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="3" t="n">
         <v>677</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>677</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>طواف مزمور عشية صوم العذراء</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>{87E7D451-6436-42DA-ABE0-FEA288E58E18}</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>683</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>مارو اتشاسف</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>{62A12AF8-CB6D-4CC5-9DB0-B73A7C24E2AD}</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="3" t="n">
         <v>684</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>693</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>مقدمة الانجيل</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>{C9DDD86A-610C-49CA-81D2-F3293213F325}</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="3" t="n">
         <v>694</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>704</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="3" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>الانجيل قبطي</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>{B900AA98-6A60-4787-8E81-4111C4CE8DC1}</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="3" t="n">
         <v>705</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>709</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>الانجيل</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>{B74DBB8C-2B2D-46E4-9508-DA46008D19A4}</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="3" t="n">
         <v>710</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>719</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>مرد انجيل الصليب</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>{EDE09087-B069-49CA-8211-757926594D3F}</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>722</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>مرد انجيل التجلي</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>{424645C4-4007-414C-8960-3DE1095D0419}</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>فاي اريه بي اوو</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>{B7D98377-B994-4654-B49C-DE10E0DDE4F1}</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="3" t="n">
         <v>724</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>724</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>مرد الانجيل عشية</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>{BEECCC68-2AEF-4568-91AA-98BCD14D3B92}</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="3" t="n">
         <v>725</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>726</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>مرد الانجيل صوم العذراء</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>{5043F523-486A-4B7C-9F73-2F3F943BB30C}</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="3" t="n">
         <v>727</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="3" t="n">
         <v>728</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>اري ابرسفافين</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>{49534D46-CF48-4D9B-ADBF-B776827F6670}</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="3" t="n">
         <v>729</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>730</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>جي افسمارؤوت</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>{DD53DBD3-9599-4D1D-B8C1-EAB35FBD36D3}</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="3" t="n">
         <v>731</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>732</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>السلام</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>{FB3BBCD6-61C4-4CD7-99A6-9684EED85D24}</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="3" t="n">
         <v>733</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>764</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="3" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>الاباء</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>{F7876A88-78F7-47CE-84DA-69B0A26420C3}</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="3" t="n">
         <v>765</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>805</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="3" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>اوشية الموضع</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>{BC126108-FF9E-447F-A97A-11EA19936C11}</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="3" t="n">
         <v>806</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="3" t="n">
         <v>818</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="3" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>تكملة الاواشي</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>{5DFBA264-6756-41DD-8F16-17B76F3E3F0F}</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="3" t="n">
         <v>819</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>837</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="3" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>أوشية الإجتماعات</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>{DFE590F6-47E2-4485-8E4F-7B40DBAD15C6}</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="3" t="n">
         <v>838</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>870</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="3" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>ابانا الذي في السموات</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>{F8657D52-0E61-475D-90AC-DB10509A5D22}</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="3" t="n">
         <v>871</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>886</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>الختام</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>{CEFEB5CF-151F-4CBA-8281-175C90531CA6}</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="3" t="n">
         <v>887</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>899</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="3" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>اوشية المياة</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>{BA51DE45-1C6C-43E6-AFF3-A98C3B049C70}</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>907</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>اوشية الاهوية</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>{BD1D9BBC-5109-4880-BAFF-4C03F37555C1}</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="3" t="n">
         <v>908</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="3" t="n">
         <v>916</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="3" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>اوشية الزروع و العشب</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>{9EFCF222-45AA-4F5C-8E28-25DB33AC666A}</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="3" t="n">
         <v>917</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>928</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="3" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="81" ht="18.75" customHeight="1"/>
+    <row r="81" ht="18.75" customHeight="1">
+      <c r="A81" s="4" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21483,9 +21702,9 @@
   <cols>
     <col width="30.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -21875,12 +22094,12 @@
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ربع مارمينا</t>
+          <t>ربع فيلوباتير ميرقوريوس</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{6961CDD1-5D71-496E-B14F-1243FFFD6BBB}</t>
+          <t>{7666EA7B-1BFC-44EC-AB49-26F16C714438}</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -21896,12 +22115,12 @@
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ربع فيلوباتير ميرقوريوس</t>
+          <t>ربع مارمينا</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{7666EA7B-1BFC-44EC-AB49-26F16C714438}</t>
+          <t>{6961CDD1-5D71-496E-B14F-1243FFFD6BBB}</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -22013,10 +22232,10 @@
         <v>164</v>
       </c>
       <c r="D25" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
@@ -22031,10 +22250,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D26" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="E26" t="n">
         <v>35</v>
@@ -22052,10 +22271,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D27" t="n">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E27" t="n">
         <v>131</v>
@@ -22073,10 +22292,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D28" t="n">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E28" t="n">
         <v>28</v>
@@ -22094,10 +22313,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D29" t="n">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="E29" t="n">
         <v>29</v>
@@ -22115,10 +22334,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="D30" t="n">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="E30" t="n">
         <v>17</v>
@@ -22136,10 +22355,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="D31" t="n">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E31" t="n">
         <v>13</v>
@@ -22157,10 +22376,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="D32" t="n">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -22178,10 +22397,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="D33" t="n">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
@@ -22199,10 +22418,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="D34" t="n">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="E34" t="n">
         <v>4</v>
@@ -22220,10 +22439,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D35" t="n">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="E35" t="n">
         <v>9</v>
@@ -22241,10 +22460,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D36" t="n">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="E36" t="n">
         <v>14</v>
@@ -22262,10 +22481,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D37" t="n">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="E37" t="n">
         <v>5</v>
@@ -22283,10 +22502,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="D38" t="n">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
@@ -22304,10 +22523,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="D39" t="n">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -22325,10 +22544,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="D40" t="n">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="E40" t="n">
         <v>14</v>
@@ -22346,10 +22565,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="D41" t="n">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -22367,10 +22586,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="D42" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E42" t="n">
         <v>20</v>
@@ -22388,10 +22607,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="D43" t="n">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -22409,10 +22628,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="D44" t="n">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="E44" t="n">
         <v>7</v>
@@ -22430,10 +22649,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="D45" t="n">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="E45" t="n">
         <v>15</v>
@@ -22451,10 +22670,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="D46" t="n">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="E46" t="n">
         <v>38</v>
@@ -22472,10 +22691,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="D47" t="n">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="E47" t="n">
         <v>15</v>
@@ -22493,10 +22712,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="D48" t="n">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="E48" t="n">
         <v>25</v>
@@ -22514,10 +22733,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="D49" t="n">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="E49" t="n">
         <v>12</v>
@@ -22535,10 +22754,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="D50" t="n">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="E50" t="n">
         <v>17</v>
@@ -22556,10 +22775,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="D51" t="n">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="E51" t="n">
         <v>22</v>
@@ -22577,10 +22796,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="D52" t="n">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="E52" t="n">
         <v>5</v>
@@ -22598,10 +22817,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="D53" t="n">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -22619,10 +22838,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="D54" t="n">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="E54" t="n">
         <v>5</v>
@@ -22640,10 +22859,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="D55" t="n">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="E55" t="n">
         <v>31</v>
@@ -22661,10 +22880,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="D56" t="n">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
@@ -22682,10 +22901,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="D57" t="n">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="E57" t="n">
         <v>5</v>
@@ -22703,10 +22922,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="D58" t="n">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="E58" t="n">
         <v>22</v>
@@ -22724,10 +22943,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="D59" t="n">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -22745,10 +22964,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="D60" t="n">
-        <v>748</v>
+        <v>733</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -22766,10 +22985,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>749</v>
+        <v>734</v>
       </c>
       <c r="D61" t="n">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -22787,10 +23006,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="D62" t="n">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
@@ -22808,10 +23027,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="D63" t="n">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -22829,10 +23048,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="D64" t="n">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
@@ -22850,10 +23069,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="D65" t="n">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -22871,10 +23090,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="D66" t="n">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -22892,10 +23111,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="D67" t="n">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="E67" t="n">
         <v>3</v>
@@ -22913,10 +23132,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="D68" t="n">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="E68" t="n">
         <v>10</v>
@@ -22934,10 +23153,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="D69" t="n">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="E69" t="n">
         <v>10</v>
@@ -22955,10 +23174,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="D70" t="n">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="E70" t="n">
         <v>4</v>
@@ -22976,10 +23195,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="D71" t="n">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -22997,10 +23216,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="D72" t="n">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="E72" t="n">
         <v>3</v>
@@ -23018,10 +23237,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="D73" t="n">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -23039,10 +23258,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="D74" t="n">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="E74" t="n">
         <v>3</v>
@@ -23060,10 +23279,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="D75" t="n">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -23081,10 +23300,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="D76" t="n">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
@@ -23102,10 +23321,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="D77" t="n">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -23123,10 +23342,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="D78" t="n">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -23144,10 +23363,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="D79" t="n">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -23165,10 +23384,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="D80" t="n">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -23186,10 +23405,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="D81" t="n">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -23207,10 +23426,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="D82" t="n">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
@@ -23228,10 +23447,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="D83" t="n">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -23249,10 +23468,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="D84" t="n">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -23270,10 +23489,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="D85" t="n">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -23291,10 +23510,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="D86" t="n">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
@@ -23312,10 +23531,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="D87" t="n">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -23333,10 +23552,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="D88" t="n">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="E88" t="n">
         <v>2</v>
@@ -23354,10 +23573,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="D89" t="n">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="E89" t="n">
         <v>13</v>
@@ -23375,10 +23594,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="D90" t="n">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="E90" t="n">
         <v>9</v>
@@ -23396,10 +23615,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="D91" t="n">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="E91" t="n">
         <v>9</v>
@@ -23417,10 +23636,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="D92" t="n">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="E92" t="n">
         <v>15</v>
@@ -23438,10 +23657,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="D93" t="n">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="E93" t="n">
         <v>26</v>
@@ -23459,10 +23678,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="D94" t="n">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="E94" t="n">
         <v>7</v>
@@ -23480,16 +23699,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="D95" t="n">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="E95" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="18.75" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
           <t>تكملة على حسب المناسبة</t>
@@ -23501,16 +23720,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="D96" t="n">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="E96" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="18.75" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
           <t>في حضور الاسقف</t>
@@ -23522,16 +23741,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="D97" t="n">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="E97" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="18.75" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
           <t>الختام 2</t>
@@ -23543,16 +23762,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="D98" t="n">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="E98" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="18.75" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
           <t>اوشية المياة</t>
@@ -23564,16 +23783,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>937</v>
+        <v>922</v>
       </c>
       <c r="D99" t="n">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="E99" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="18.75" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
           <t>أوشية الزروع</t>
@@ -23585,16 +23804,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="D100" t="n">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="E100" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="18.75" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
           <t>اوشية الأهوية والثمار</t>
@@ -23606,10 +23825,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="D101" t="n">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="E101" t="n">
         <v>6</v>
@@ -23631,9 +23850,9 @@
   <cols>
     <col width="19.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -24708,9 +24927,9 @@
   <cols>
     <col width="17.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -24904,9 +25123,9 @@
   <cols>
     <col width="21.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -26364,7 +26583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="18.75" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>ابانا الذي في السموات</t>
@@ -26401,9 +26620,9 @@
   <cols>
     <col width="28.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">

--- a/Files Data.xlsx
+++ b/Files Data.xlsx
@@ -10629,7 +10629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" ht="18.75" customHeight="1">
       <c r="A484" t="inlineStr">
         <is>
           <t>الختام 2</t>
@@ -10661,7 +10661,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="41.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -10995,460 +10995,460 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>(الميلاد) أنا افتح فاي بمجد الله</t>
+          <t>(برمون الميلاد) أنا أول كلامي</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{99CFF969-C99E-48F8-A8E9-E208BA5E4210}</t>
+          <t>{6DD39CD1-C8E1-46F1-9C04-9847B6F46197}</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>378</v>
       </c>
       <c r="D16" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>(تذكار الاعياد السيدية) المجد للآب خالقنا</t>
+          <t>(الميلاد) أنا افتح فاي بمجد الله</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{A11F2970-128A-421A-92A7-78C73AEA4270}</t>
+          <t>{99CFF969-C99E-48F8-A8E9-E208BA5E4210}</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D17" t="n">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>(صوم نينوى) الصوم الصوم للنفس ثبات</t>
+          <t>(تذكار الاعياد السيدية) المجد للآب خالقنا</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{22B730C4-9A84-4D38-B8FD-3409EF83C4BD}</t>
+          <t>{A11F2970-128A-421A-92A7-78C73AEA4270}</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="D18" t="n">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الاول - الصوم الصوم للنفس ثبات</t>
+          <t>(صوم نينوى) الصوم الصوم للنفس ثبات</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{19C963C1-49D7-4905-842B-977245127917}</t>
+          <t>{22B730C4-9A84-4D38-B8FD-3409EF83C4BD}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="D19" t="n">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الثاني - سر عجيب هو سر المسيح</t>
+          <t>(الصوم الكبير) الاسبوع الاول - الصوم الصوم للنفس ثبات</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{4A2CC73C-A3C7-45E5-9BFE-FBC538653C4B}</t>
+          <t>{19C963C1-49D7-4905-842B-977245127917}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="D20" t="n">
         <v>536</v>
       </c>
       <c r="E20" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الثالث - الصوم هو حصن غير مهدوم</t>
+          <t>(الصوم الكبير) الاسبوع الثاني - سر عجيب هو سر المسيح</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{4CDA093F-DDF6-4FED-8316-8CFC4A383925}</t>
+          <t>{4A2CC73C-A3C7-45E5-9BFE-FBC538653C4B}</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>537</v>
       </c>
       <c r="D21" t="n">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الرابع - الصوم هو حصن غير مهدوم</t>
+          <t>(الصوم الكبير) الاسبوع الثالث - الصوم هو حصن غير مهدوم</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{FE32734F-5C08-4A79-BCCD-16672ABB653D}</t>
+          <t>{4CDA093F-DDF6-4FED-8316-8CFC4A383925}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="D22" t="n">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع السابع و ختام الصوم ـ الصوم الصوم يا شعب يسوع</t>
+          <t>(الصوم الكبير) الاسبوع الرابع - الصوم هو حصن غير مهدوم</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{3DD0F949-75DE-4846-840E-7878908DF90E}</t>
+          <t>{FE32734F-5C08-4A79-BCCD-16672ABB653D}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="D23" t="n">
-        <v>688</v>
+        <v>666</v>
       </c>
       <c r="E23" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(احد الشعانين) اليومَ تمت الأقوال</t>
+          <t>(الصوم الكبير) الاسبوع السابع و ختام الصوم ـ الصوم الصوم يا شعب يسوع</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{51A8EA9C-25BB-445D-B0EF-E66FBADDBE1A}</t>
+          <t>{3DD0F949-75DE-4846-840E-7878908DF90E}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>689</v>
+        <v>667</v>
       </c>
       <c r="D24" t="n">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(احد الشعانين) الجالس فوق الشاروبيم</t>
+          <t>(احد الشعانين) اليومَ تمت الأقوال</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{2E674F43-188F-46C4-B421-E7ADF4DB57C7}</t>
+          <t>{51A8EA9C-25BB-445D-B0EF-E66FBADDBE1A}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="D25" t="n">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(احد الشعانين) المجد لله الأوحد</t>
+          <t>(احد الشعانين) الجالس فوق الشاروبيم</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{D5D7C4B4-CC66-4076-8A09-DFD723D50F03}</t>
+          <t>{2E674F43-188F-46C4-B421-E7ADF4DB57C7}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="D26" t="n">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>(احد الشعانين) أوصنا يا ابن داود</t>
+          <t>(احد الشعانين) المجد لله الأوحد</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{FC1EEFC2-F019-4CD5-BD5A-23F9E734E63A}</t>
+          <t>{D5D7C4B4-CC66-4076-8A09-DFD723D50F03}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="D27" t="n">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>(خميس العهد) ليل العشاء السري</t>
+          <t>(احد الشعانين) أوصنا يا ابن داود</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{F55CB762-4A57-49B3-A691-C8660FCFC634}</t>
+          <t>{FC1EEFC2-F019-4CD5-BD5A-23F9E734E63A}</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>775</v>
+        <v>793</v>
       </c>
       <c r="D28" t="n">
-        <v>787</v>
+        <v>803</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (خميس العهد) إن فادينا دعانا</t>
+          <t>(خميس العهد) ليل العشاء السري</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{1A183E7B-87A1-4C2F-841E-DFEC3B4A7D2F}</t>
+          <t>{F55CB762-4A57-49B3-A691-C8660FCFC634}</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="D29" t="n">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>(خميس العهد) أوصنا يا إبن داود</t>
+          <t xml:space="preserve"> (خميس العهد) إن فادينا دعانا</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{59DFCA58-6399-41A0-AB3D-6A5B0D8DDFBC}</t>
+          <t>{1A183E7B-87A1-4C2F-841E-DFEC3B4A7D2F}</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="D30" t="n">
-        <v>813</v>
+        <v>844</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>(القيامة) مديح واطس لعشية - الله الأزلي قبل الأوقات</t>
+          <t>(خميس العهد) أوصنا يا إبن داود</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{A72E6126-0320-4081-9967-7CDEDE602A51}</t>
+          <t>{59DFCA58-6399-41A0-AB3D-6A5B0D8DDFBC}</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>814</v>
+        <v>845</v>
       </c>
       <c r="D31" t="n">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>(القيامة) سبع قطع لباكر - المجد والعظمة للإله</t>
+          <t>(القيامة) مديح واطس لعشية - الله الأزلي قبل الأوقات</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{0D4A51F9-2CBC-4DB3-8764-00D5D185E9D3}</t>
+          <t>{A72E6126-0320-4081-9967-7CDEDE602A51}</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="D32" t="n">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="E32" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>(القيامة) أنا افتح فمي وأتكلم</t>
+          <t>(القيامة) سبع قطع لباكر - المجد والعظمة للإله</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{05FB6036-013E-4B49-AF1F-F51A76197290}</t>
+          <t>{0D4A51F9-2CBC-4DB3-8764-00D5D185E9D3}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="D33" t="n">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="E33" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الأول - أبدأ باسم الله القدوس</t>
+          <t>(القيامة) أنا افتح فمي وأتكلم</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{E652151D-56BC-4E03-935C-6CB473E64AC9}</t>
+          <t>{05FB6036-013E-4B49-AF1F-F51A76197290}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="D34" t="n">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="E34" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الثاني - أنا أفتح فمي بمجد الله</t>
+          <t>(الخماسين) الاسبوع الأول - أبدأ باسم الله القدوس</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{12A7A1D0-EC34-4F91-93B4-77F40C22A4E0}</t>
+          <t>{E652151D-56BC-4E03-935C-6CB473E64AC9}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="D35" t="n">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الثالث - المجد يليق والأكرام</t>
+          <t>(الخماسين) الاسبوع الثاني - أنا أفتح فمي بمجد الله</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{CCFAA7F8-17F8-4620-BE25-841890829953}</t>
+          <t>{12A7A1D0-EC34-4F91-93B4-77F40C22A4E0}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>958</v>
+        <v>979</v>
       </c>
       <c r="D36" t="n">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="E36" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الرابع - أنا أفتح فمي واتكلم</t>
+          <t>(الخماسين) الاسبوع الثالث - المجد يليق والأكرام</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{6896F5AC-12DD-450D-A6A9-E7A0FC24A7D1}</t>
+          <t>{CCFAA7F8-17F8-4620-BE25-841890829953}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="D37" t="n">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="E37" t="n">
         <v>29</v>
@@ -11457,124 +11457,124 @@
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الخامس - أبدى باسم الله القدوس</t>
+          <t>(الخماسين) الاسبوع الرابع - أنا أفتح فمي واتكلم</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{F0F8F790-9F1B-48CC-B4CF-E7411C57B0C8}</t>
+          <t>{6896F5AC-12DD-450D-A6A9-E7A0FC24A7D1}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="D38" t="n">
-        <v>1076</v>
+        <v>1056</v>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع السادس - أنا أفتح فاي وأخبركم</t>
+          <t>(الخماسين) الاسبوع الخامس - أبدى باسم الله القدوس</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{852F6F54-9767-4FF5-B8C5-8BE0B6729F8D}</t>
+          <t>{F0F8F790-9F1B-48CC-B4CF-E7411C57B0C8}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1077</v>
+        <v>1057</v>
       </c>
       <c r="D39" t="n">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>(الخماسين) عيد الصعود - المجد لله والأكرام</t>
+          <t>(الخماسين) الاسبوع السادس - أنا أفتح فاي وأخبركم</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{0B00A682-598E-42FA-9F88-D72EAFF6E783}</t>
+          <t>{852F6F54-9767-4FF5-B8C5-8BE0B6729F8D}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="D40" t="n">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="E40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>(الخماسين) عيد العنصرة - المجد لله القدوس</t>
+          <t>(الخماسين) عيد الصعود - المجد لله والأكرام</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{C028FF9B-09C1-42E1-90E0-2C45A634BAF0}</t>
+          <t>{0B00A682-598E-42FA-9F88-D72EAFF6E783}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="D41" t="n">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>(صوم وعيد الرسل) الفاعل الأمين لا يخزى</t>
+          <t>(الخماسين) عيد العنصرة - المجد لله القدوس</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{B9A8D07C-0514-491C-A91B-A5BD0B14C556}</t>
+          <t>{C028FF9B-09C1-42E1-90E0-2C45A634BAF0}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="D42" t="n">
-        <v>1157</v>
+        <v>1137</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>(صوم و عيد الرسل) فلنسبح إلهنا القـدوس</t>
+          <t>(صوم وعيد الرسل) الفاعل الأمين لا يخزى</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{FFAC3DB8-CD69-4363-AEEE-0A77AFA5C14C}</t>
+          <t>{B9A8D07C-0514-491C-A91B-A5BD0B14C556}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="D43" t="n">
-        <v>1187</v>
+        <v>1167</v>
       </c>
       <c r="E43" t="n">
         <v>30</v>
@@ -11583,292 +11583,292 @@
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>(التجلي) المجد لله ذي الرحمة</t>
+          <t>(صوم و عيد الرسل) فلنسبح إلهنا القـدوس</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{72B6A886-BE5B-444C-ADB8-80108ED1C462}</t>
+          <t>{FFAC3DB8-CD69-4363-AEEE-0A77AFA5C14C}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1188</v>
+        <v>1168</v>
       </c>
       <c r="D44" t="n">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E44" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>(سنوي) ابانا الذي في السموات</t>
+          <t>(التجلي) المجد لله ذي الرحمة</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{55AD0713-7619-4F4A-BBF7-CBEC78E9D2B6}</t>
+          <t>{72B6A886-BE5B-444C-ADB8-80108ED1C462}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="D45" t="n">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>(سنوي) اسمعوا يا شعب المسيح</t>
+          <t>(سنوي) ابانا الذي في السموات</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{FBABEA1B-1917-427E-BD5E-EB2368CB6293}</t>
+          <t>{55AD0713-7619-4F4A-BBF7-CBEC78E9D2B6}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="D46" t="n">
-        <v>1247</v>
+        <v>1228</v>
       </c>
       <c r="E46" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>(سنوي) المجد لمن رفع السموات</t>
+          <t>(سنوي) اسمعوا يا شعب المسيح</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{12A69F25-ED75-4850-8C2A-4864364C2131}</t>
+          <t>{FBABEA1B-1917-427E-BD5E-EB2368CB6293}</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1248</v>
+        <v>1229</v>
       </c>
       <c r="D47" t="n">
-        <v>1278</v>
+        <v>1257</v>
       </c>
       <c r="E47" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>(سنوي) أول ما أبدي أسبح الإله</t>
+          <t>(سنوي) المجد لمن رفع السموات</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{BA707332-FF09-40ED-BD05-0F3CE5931805}</t>
+          <t>{12A69F25-ED75-4850-8C2A-4864364C2131}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1279</v>
+        <v>1258</v>
       </c>
       <c r="D48" t="n">
-        <v>1308</v>
+        <v>1288</v>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>الباب الثاني</t>
+          <t>(سنوي) أول ما أبدي أسبح الإله</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{E9ED8CBA-74AF-4903-9BE7-83949A2E6042}</t>
+          <t>{BA707332-FF09-40ED-BD05-0F3CE5931805}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1309</v>
+        <v>1289</v>
       </c>
       <c r="D49" t="n">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>أبادير وإيرائي اخته</t>
+          <t>الباب الثاني</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{418E980F-1BC4-40C4-AED7-1DE2566AF0A8}</t>
+          <t>{E9ED8CBA-74AF-4903-9BE7-83949A2E6042}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="D50" t="n">
-        <v>1334</v>
+        <v>1319</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>أبسخيرون القليني</t>
+          <t>أبادير وإيرائي اخته</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{21D2DCA4-5857-4F13-886C-A79FCE9F45CF}</t>
+          <t>{418E980F-1BC4-40C4-AED7-1DE2566AF0A8}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1335</v>
+        <v>1320</v>
       </c>
       <c r="D51" t="n">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>أباكراجون البتانوني</t>
+          <t>أبسخيرون القليني</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{C6670786-A976-4B52-868E-171137C94BF0}</t>
+          <t>{21D2DCA4-5857-4F13-886C-A79FCE9F45CF}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="D52" t="n">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="E52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>اباكير و يوحنا</t>
+          <t>أباكراجون البتانوني</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{94B1CF6F-400F-4EBB-BEB3-7561B8B79E22}</t>
+          <t>{C6670786-A976-4B52-868E-171137C94BF0}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="D53" t="n">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>أبانوب النهيسي</t>
+          <t>اباكير و يوحنا</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{B7505EB8-9095-443D-8AB4-76B429FB6882}</t>
+          <t>{94B1CF6F-400F-4EBB-BEB3-7561B8B79E22}</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="D54" t="n">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>الأنبا إبرآم أسقف الفيوم</t>
+          <t>أبانوب النهيسي</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{76A5C39E-E378-49E4-A1B3-3C3C6AD0FC45}</t>
+          <t>{B7505EB8-9095-443D-8AB4-76B429FB6882}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="D55" t="n">
-        <v>1415</v>
+        <v>1405</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>الأنبا أبوللو والأنبا أبيب</t>
+          <t>الأنبا إبرآم أسقف الفيوم</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{15F37CDF-162E-4235-B0CD-3EC560293C8F}</t>
+          <t>{76A5C39E-E378-49E4-A1B3-3C3C6AD0FC45}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1416</v>
+        <v>1406</v>
       </c>
       <c r="D56" t="n">
-        <v>1434</v>
+        <v>1425</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>الأنبا بيشوي</t>
+          <t>الأنبا أبوللو والأنبا أبيب</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{A7827B46-8853-4630-8C57-25D12D4BB0CC}</t>
+          <t>{15F37CDF-162E-4235-B0CD-3EC560293C8F}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="D57" t="n">
-        <v>1453</v>
+        <v>1444</v>
       </c>
       <c r="E57" t="n">
         <v>19</v>
@@ -11877,61 +11877,61 @@
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>الأنبا أنطونيوس</t>
+          <t>الأنبا بيشوي</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{AE159095-D310-4A30-980A-0B3122A27E47}</t>
+          <t>{A7827B46-8853-4630-8C57-25D12D4BB0CC}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="D58" t="n">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>القديس أبو مقار الكبير</t>
+          <t>الأنبا أنطونيوس</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{D1D7B229-E53D-4C04-AC77-B8E34223EEAF}</t>
+          <t>{AE159095-D310-4A30-980A-0B3122A27E47}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="D59" t="n">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="E59" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>الأنبا ساويرس الأنطاكي</t>
+          <t>القديس أبو مقار الكبير</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{9BAA7FB0-F8B8-4E53-A01A-F247E651EA5F}</t>
+          <t>{D1D7B229-E53D-4C04-AC77-B8E34223EEAF}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="D60" t="n">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="E60" t="n">
         <v>16</v>
@@ -11940,208 +11940,208 @@
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>الأنبا أرسانيوس</t>
+          <t>الأنبا ساويرس الأنطاكي</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{C7297DB4-629F-4E57-809D-A2D2D80CBC90}</t>
+          <t>{9BAA7FB0-F8B8-4E53-A01A-F247E651EA5F}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="D61" t="n">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>الأنبا رويس (أفتح فاي باسم الله)</t>
+          <t>الأنبا أرسانيوس</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{6DD4328F-B2A2-4D8E-B789-5A48B3861347}</t>
+          <t>{C7297DB4-629F-4E57-809D-A2D2D80CBC90}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D62" t="n">
-        <v>1530</v>
+        <v>1521</v>
       </c>
       <c r="E62" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>الأنبا رويس (السلام للأنبا فريج)</t>
+          <t>الأنبا رويس (أفتح فاي باسم الله)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{E747FAEF-A32D-48E7-9745-27FFACBBF45C}</t>
+          <t>{6DD4328F-B2A2-4D8E-B789-5A48B3861347}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1531</v>
+        <v>1522</v>
       </c>
       <c r="D63" t="n">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="E63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>البابا بطرس خاتم الشهداء (أفتح فاى بالتمجيد)</t>
+          <t>الأنبا رويس (السلام للأنبا فريج)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{713E38EC-7043-46DD-9D08-0B816BE65A07}</t>
+          <t>{E747FAEF-A32D-48E7-9745-27FFACBBF45C}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="D64" t="n">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="E64" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>البابا بطرس خاتم الشهداء (افتح فاي بالتسبيح)</t>
+          <t>البابا بطرس خاتم الشهداء (أفتح فاى بالتمجيد)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{0A2C786B-9166-4B00-8893-BDBFED3B96C5}</t>
+          <t>{713E38EC-7043-46DD-9D08-0B816BE65A07}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="D65" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="E65" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>الشهيد مارجرجس الروماني</t>
+          <t>البابا بطرس خاتم الشهداء (افتح فاي بالتسبيح)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{FFF1B9FE-C89C-4F56-85B7-F375461AEA62}</t>
+          <t>{0A2C786B-9166-4B00-8893-BDBFED3B96C5}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="D66" t="n">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (تعالوا نتهلل بالالحان)</t>
+          <t>الشهيد مارجرجس الروماني</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{1CB7C0A9-70EC-46E1-9942-6BB8469F3452}</t>
+          <t>{FFF1B9FE-C89C-4F56-85B7-F375461AEA62}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="D67" t="n">
-        <v>1615</v>
+        <v>1601</v>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (افتح فاى بالتسبيح)</t>
+          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (تعالوا نتهلل بالالحان)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{A09196A5-E8C6-4842-A208-B0D3C60A9650}</t>
+          <t>{1CB7C0A9-70EC-46E1-9942-6BB8469F3452}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1616</v>
+        <v>1602</v>
       </c>
       <c r="D68" t="n">
-        <v>1629</v>
+        <v>1625</v>
       </c>
       <c r="E68" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>الشهيد مارمينا العجائبي</t>
+          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (افتح فاى بالتسبيح)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{FEF9FE36-19EB-47C1-B153-89D4179D816D}</t>
+          <t>{A09196A5-E8C6-4842-A208-B0D3C60A9650}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="D69" t="n">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="E69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>الشهيد اسطفانوس</t>
+          <t>الشهيد مارمينا العجائبي</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{B37BED38-74B5-4E20-9C68-02F0B138FB76}</t>
+          <t>{FEF9FE36-19EB-47C1-B153-89D4179D816D}</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D70" t="n">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="E70" t="n">
         <v>13</v>
@@ -12150,378 +12150,399 @@
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>القديس لوقا الانجيلي</t>
+          <t>الشهيد اسطفانوس</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{50EEB170-6F56-438C-943C-B8B3136DBB6A}</t>
+          <t>{B37BED38-74B5-4E20-9C68-02F0B138FB76}</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="D71" t="n">
-        <v>1673</v>
+        <v>1665</v>
       </c>
       <c r="E71" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>القديس مارمرقس الرسول</t>
+          <t>القديس لوقا الانجيلي</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{D4872368-E5CE-4B87-A314-70582CB26D33}</t>
+          <t>{50EEB170-6F56-438C-943C-B8B3136DBB6A}</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="D72" t="n">
-        <v>1692</v>
+        <v>1683</v>
       </c>
       <c r="E72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
+          <t>القديس مارمرقس الرسول</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>{D4872368-E5CE-4B87-A314-70582CB26D33}</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1684</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1702</v>
+      </c>
+      <c r="E73" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" ht="18.75" customHeight="1">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>شهداء اخميم</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>{BCD6DB0F-7899-4280-8F26-43D95DAD6C10}</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>1693</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1705</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="C74" t="n">
+        <v>1703</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1715</v>
+      </c>
+      <c r="E74" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="18.75" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>القديسة ڤيرينا</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>{97AE3AB0-0AA8-460A-9F07-02DB0D944E28}</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>1706</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1719</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="C75" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1729</v>
+      </c>
+      <c r="E75" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="18.75" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>العذراء مريم .. يا أم الله القدوس</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>{BC31EDAD-70A8-41AD-8F09-30FB6E612B63}</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>1720</v>
-      </c>
-      <c r="D75" t="n">
+      <c r="C76" t="n">
         <v>1730</v>
       </c>
-      <c r="E75" t="n">
+      <c r="D76" t="n">
+        <v>1740</v>
+      </c>
+      <c r="E76" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="18.75" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>العذراء مريم .. يا يمامة جليلة تصيح</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>{CA9FFDD9-E5B0-41CC-901F-6882250D1D1A}</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>1731</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1745</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="C77" t="n">
+        <v>1741</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1755</v>
+      </c>
+      <c r="E77" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="18.75" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>الملاك ميخائيل</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>{12793581-7FD0-4EE7-B903-2943F410A5D2}</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>1746</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1757</v>
-      </c>
-      <c r="E77" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>الملاك غبريال</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>{FFD2036A-0F2D-47E3-B5B9-AC167E3F6FF3}</t>
-        </is>
-      </c>
       <c r="C78" t="n">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="D78" t="n">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="E78" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="18.75" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
+          <t>الملاك غبريال</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{FFD2036A-0F2D-47E3-B5B9-AC167E3F6FF3}</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1768</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1779</v>
+      </c>
+      <c r="E79" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" ht="18.75" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>الباب الثالث</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>{E5B98BC1-9C9D-42EC-BB16-E848179FB9DC}</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>1770</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1770</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="C80" t="n">
+        <v>1780</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1780</v>
+      </c>
+      <c r="E80" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="18.75" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>أعروس الفادي القبطية</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>{3CBD5E49-3BE4-475A-A6D3-2858A4DB1030}</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>1771</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1799</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="C81" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1809</v>
+      </c>
+      <c r="E81" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="18.75" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>انظروا يديه تأملوا رجليه</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>{E1A31474-7F00-4B7D-90FD-A67415E32872}</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1814</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="C82" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1824</v>
+      </c>
+      <c r="E82" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="18.75" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>رحلة الصوم الكبير</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>{11755A37-6BDF-4E72-9537-F39867C5BB7D}</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>1815</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1821</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="C83" t="n">
+        <v>1825</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E83" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="18.75" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>عند شق الفجر باكر</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>{D4859CD1-25CE-465C-846E-A0311D24DB66}</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>1822</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1854</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="C84" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1864</v>
+      </c>
+      <c r="E84" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="18.75" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>قام حقا</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>{4615B620-F94D-4CAD-843A-EB32E8369AAB}</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>1855</v>
-      </c>
-      <c r="D84" t="n">
-        <v>1868</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="C85" t="n">
+        <v>1865</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E85" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="18.75" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>كنيستي أرجو لك</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>{8A08F2A7-DAF4-4998-9EF9-8221744F0038}</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>1869</v>
-      </c>
-      <c r="D85" t="n">
+      <c r="C86" t="n">
         <v>1879</v>
       </c>
-      <c r="E85" t="n">
+      <c r="D86" t="n">
+        <v>1889</v>
+      </c>
+      <c r="E86" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="18.75" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>كنيستي القبطية كنيسة الإله</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>{B1A30565-0CDB-40D5-8B05-21F68D5C9160}</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>1880</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1906</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="C87" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1916</v>
+      </c>
+      <c r="E87" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="18.75" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>كنيستي القبطية نشرت المسيحية</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>{AB60D02D-F80E-4E53-B0A0-3A54593EB31B}</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>1907</v>
-      </c>
-      <c r="D87" t="n">
-        <v>1919</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="C88" t="n">
+        <v>1917</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E88" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>يا ربنا مولى السلام</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>{325B4DE6-FA63-4B6D-827F-BCC78EF1FEC9}</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1963</v>
-      </c>
-      <c r="E88" t="n">
+      <c r="C89" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1973</v>
+      </c>
+      <c r="E89" t="n">
         <v>44</v>
       </c>
     </row>
@@ -22024,7 +22045,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -22274,40 +22295,40 @@
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ارباع عيد الصليب</t>
+          <t>ارباع الناقوس الفرايحي</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{0120814B-6347-4FF3-9CA8-883FC9FEF728}</t>
+          <t>{08277E26-4A59-441A-90BE-E448498302F7}</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ارباع عيد التجلي</t>
+          <t>ارباع عيد الميلاد</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{AC5F2BCF-F75D-4BF9-819A-BF7F656F9A0D}</t>
+          <t>{013099AC-E8DF-4B35-A585-A33DD38F2D00}</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -22316,40 +22337,40 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ارباع العذراء</t>
+          <t>ارباع عيد الصليب</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{95F2B000-887E-494A-9B06-BF2AE6AB7F7E}</t>
+          <t>{0120814B-6347-4FF3-9CA8-883FC9FEF728}</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ربع الملاك ميخائيل و الملاك غبريال</t>
+          <t>ارباع عيد التجلي</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{7035C199-A9B1-43CB-B809-8B94B2CC1797}</t>
+          <t>{AC5F2BCF-F75D-4BF9-819A-BF7F656F9A0D}</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -22358,19 +22379,19 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ربع الملاك غبريال</t>
+          <t>ارباع العذراء</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{E79471F5-6C95-4ECB-AD9D-CE660DCAAA70}</t>
+          <t>{95F2B000-887E-494A-9B06-BF2AE6AB7F7E}</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -22379,61 +22400,61 @@
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ربع السمائين</t>
+          <t>ربع الملاك ميخائيل و الملاك غبريال</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{8D5918BA-0867-41FC-88A4-68C63B56B069}</t>
+          <t>{7035C199-A9B1-43CB-B809-8B94B2CC1797}</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D17" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ربع يوحنا المعمدان</t>
+          <t>ربع الملاك غبريال</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{467BEA0C-D398-40D8-B035-09A73444E5CA}</t>
+          <t>{E79471F5-6C95-4ECB-AD9D-CE660DCAAA70}</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ربع للرسل</t>
+          <t>ربع السمائين</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{1D0ED759-A51B-4B3B-8186-AE1DBCC397B8}</t>
+          <t>{8D5918BA-0867-41FC-88A4-68C63B56B069}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -22442,19 +22463,19 @@
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ربع بطرس و بولس</t>
+          <t>ربع يوحنا المعمدان</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{3C444163-4B5E-4306-8A8A-489D9AF24A2A}</t>
+          <t>{467BEA0C-D398-40D8-B035-09A73444E5CA}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -22463,40 +22484,40 @@
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ربع مارمرقس</t>
+          <t>ربع للرسل</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{3CEEB174-A27F-4ACB-B72B-4D39D2FC700F}</t>
+          <t>{1D0ED759-A51B-4B3B-8186-AE1DBCC397B8}</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ربع اسطفانوس</t>
+          <t>ربع بطرس و بولس</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{A7614D8D-F4B4-41D2-A880-10234332DD2F}</t>
+          <t>{3C444163-4B5E-4306-8A8A-489D9AF24A2A}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D22" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -22505,19 +22526,19 @@
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ربع مارجرجس</t>
+          <t>ربع مارمرقس</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{4E9FE7F7-74A7-4CEE-8CA7-DD64178EF766}</t>
+          <t>{3CEEB174-A27F-4ACB-B72B-4D39D2FC700F}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D23" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -22526,40 +22547,40 @@
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ربع فيلوباتير ميرقوريوس</t>
+          <t>ربع اسطفانوس</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{7666EA7B-1BFC-44EC-AB49-26F16C714438}</t>
+          <t>{A7614D8D-F4B4-41D2-A880-10234332DD2F}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ربع مارمينا</t>
+          <t>ربع مارجرجس</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{6961CDD1-5D71-496E-B14F-1243FFFD6BBB}</t>
+          <t>{4E9FE7F7-74A7-4CEE-8CA7-DD64178EF766}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -22568,859 +22589,859 @@
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ختام ارباع الناقوس</t>
+          <t>ربع فيلوباتير ميرقوريوس</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{52EB6B04-BCFD-460D-A692-2D541D7484D5}</t>
+          <t>{7666EA7B-1BFC-44EC-AB49-26F16C714438}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D26" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ختام ارباع الناقوس السنوي</t>
+          <t>ربع مارمينا</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{BE52E209-B022-45B3-8B56-2C35B7DE60D1}</t>
+          <t>{6961CDD1-5D71-496E-B14F-1243FFFD6BBB}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D27" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ختام ارباع الناقوس الفرايحي</t>
+          <t>ارباع البطريرك و الأسقف</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{B87EBA1A-E0E4-4E68-87D7-3C4A798CF278}</t>
+          <t>{3DFBF6DB-0CEC-4420-BF0E-724CBB82E1A1}</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D28" t="n">
         <v>111</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>اوشية الراقدين</t>
+          <t>ختام ارباع الناقوس</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{83E6BC33-A9EC-45CA-89B6-24EFBC51B654}</t>
+          <t>{52EB6B04-BCFD-460D-A692-2D541D7484D5}</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>112</v>
       </c>
       <c r="D29" t="n">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="E29" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>تفضل يا رب</t>
+          <t>ختام ارباع الناقوس السنوي</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{D8AFA182-3999-4072-94E9-F65D50B876B9}</t>
+          <t>{BE52E209-B022-45B3-8B56-2C35B7DE60D1}</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="D30" t="n">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>اوشية المرضي</t>
+          <t>ختام ارباع الناقوس الفرايحي</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{069F7A79-999B-4223-82AE-CAF356118167}</t>
+          <t>{B87EBA1A-E0E4-4E68-87D7-3C4A798CF278}</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="D31" t="n">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>السبع طرايق</t>
+          <t>اوشية الراقدين</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{385BAEA4-D798-4AD0-920D-ADEC0B972186}</t>
+          <t>{83E6BC33-A9EC-45CA-89B6-24EFBC51B654}</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="D32" t="n">
-        <v>340</v>
+        <v>179</v>
       </c>
       <c r="E32" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>اوشية المسافرين</t>
+          <t>تفضل يا رب</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{A059EEC9-5D25-453F-A956-A2E149F0773C}</t>
+          <t>{D8AFA182-3999-4072-94E9-F65D50B876B9}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>341</v>
+        <v>180</v>
       </c>
       <c r="D33" t="n">
-        <v>368</v>
+        <v>185</v>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>اوشية القرابين</t>
+          <t>اوشية المرضى</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{2C897F14-44CC-430E-9BE1-EB379FE7A9C7}</t>
+          <t>{069F7A79-999B-4223-82AE-CAF356118167}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>369</v>
+        <v>186</v>
       </c>
       <c r="D34" t="n">
-        <v>397</v>
+        <v>220</v>
       </c>
       <c r="E34" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>فلنسبح مع الملائكة</t>
+          <t>السبع طرائق</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{2ECE1F1B-C143-4CE2-B550-348BEE185974}</t>
+          <t>{385BAEA4-D798-4AD0-920D-ADEC0B972186}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>398</v>
+        <v>221</v>
       </c>
       <c r="D35" t="n">
-        <v>414</v>
+        <v>294</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>مقدمة الذوكصولوجيات</t>
+          <t>اوشية المسافرين</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{D72E4090-F25E-47FA-91CC-49FA1BFA5556}</t>
+          <t>{A059EEC9-5D25-453F-A956-A2E149F0773C}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>415</v>
+        <v>295</v>
       </c>
       <c r="D36" t="n">
-        <v>427</v>
+        <v>322</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>الذكصولوجيات</t>
+          <t>اوشية القرابين</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{A5B9CE2F-90E3-44D7-B22F-CAE6783C8E2F}</t>
+          <t>{2C897F14-44CC-430E-9BE1-EB379FE7A9C7}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>428</v>
+        <v>323</v>
       </c>
       <c r="D37" t="n">
-        <v>428</v>
+        <v>351</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>مقدمة قانون الإيمان</t>
+          <t>تسبحة الملائكة</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{409B3D0A-B40A-4475-811D-72C5125134AB}</t>
+          <t>{2ECE1F1B-C143-4CE2-B550-348BEE185974}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>429</v>
+        <v>352</v>
       </c>
       <c r="D38" t="n">
-        <v>431</v>
+        <v>355</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>قانون الايمان</t>
+          <t>قدوس الميلاد</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{3CD34DC9-72C7-4E1F-A24E-3878EF0435D6}</t>
+          <t>{C361BE0A-6275-4F21-8ACA-B240ABDAEF5D}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>432</v>
+        <v>356</v>
       </c>
       <c r="D39" t="n">
-        <v>435</v>
+        <v>356</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>افنوتي ناي نان</t>
+          <t>قدوس الصلب</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{61880C5D-7B19-4DA9-9517-587F0006E7A4}</t>
+          <t>{F5175F64-5E0E-4336-A80A-F953446C58B3}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>436</v>
+        <v>357</v>
       </c>
       <c r="D40" t="n">
-        <v>444</v>
+        <v>357</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ايطاف اني اسخاي</t>
+          <t>قدوس القيامة</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{60A6EF5E-A7D1-4E39-AAE6-A0EA92726711}</t>
+          <t>{918261AE-C329-45C0-A17E-464E56904539}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="D41" t="n">
-        <v>458</v>
+        <v>358</v>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>طرح عيد الصليب</t>
+          <t>قدوس الصعود</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{17F6A454-5ABF-4DFB-A78A-D146D086082D}</t>
+          <t>{AE3146ED-6425-4136-9613-0253836230D1}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>459</v>
+        <v>359</v>
       </c>
       <c r="D42" t="n">
-        <v>463</v>
+        <v>359</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>طرح اخر لعيد الصليب</t>
+          <t>تكملة للثلاثة تقديسات</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{0BD005D7-2E83-417A-9686-5430EAAF391B}</t>
+          <t>{CC1A9D94-B13E-44A2-A47D-E02D1811698D}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>464</v>
+        <v>360</v>
       </c>
       <c r="D43" t="n">
-        <v>468</v>
+        <v>363</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>مرد طرح عيد الصليب</t>
+          <t>مقدمة الذوكصولوجيات</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{68F134B0-811C-48F0-A7D0-5BB19CE61443}</t>
+          <t>{D72E4090-F25E-47FA-91CC-49FA1BFA5556}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>469</v>
+        <v>364</v>
       </c>
       <c r="D44" t="n">
-        <v>469</v>
+        <v>376</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>أفرحى يا مريم</t>
+          <t>الذكصولوجيات</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{1C20AEEF-0DEB-4F74-A46A-AFC5A06DC744}</t>
+          <t>{A5B9CE2F-90E3-44D7-B22F-CAE6783C8E2F}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>470</v>
+        <v>377</v>
       </c>
       <c r="D45" t="n">
-        <v>483</v>
+        <v>377</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>تماجيد نهضة العذراء</t>
+          <t>مقدمة قانون الإيمان</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{7DE226B6-2157-492D-AB80-4448CDB8A41A}</t>
+          <t>{409B3D0A-B40A-4475-811D-72C5125134AB}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>484</v>
+        <v>378</v>
       </c>
       <c r="D46" t="n">
-        <v>484</v>
+        <v>380</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>لحن شيري ماريا</t>
+          <t>قانون الايمان</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{1E7E7987-2CAA-4858-AB80-5A0AF761B6EF}</t>
+          <t>{3CD34DC9-72C7-4E1F-A24E-3878EF0435D6}</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>485</v>
+        <v>381</v>
       </c>
       <c r="D47" t="n">
-        <v>504</v>
+        <v>384</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>إك اسماروؤت</t>
+          <t>افنوتي ناي نان</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{D2101135-3E00-460B-BDBC-0ED4AE799C01}</t>
+          <t>{61880C5D-7B19-4DA9-9517-587F0006E7A4}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>505</v>
+        <v>385</v>
       </c>
       <c r="D48" t="n">
-        <v>505</v>
+        <v>393</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>لحن شيرى ثيؤطوكى</t>
+          <t>ايطاف اني اسخاي</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{18389A37-F3FC-4832-AAAE-BB56BAA2569D}</t>
+          <t>{60A6EF5E-A7D1-4E39-AAE6-A0EA92726711}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>506</v>
+        <v>394</v>
       </c>
       <c r="D49" t="n">
-        <v>512</v>
+        <v>407</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>لحن أو كيريوس</t>
+          <t>طرح عيد الصليب</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{9374086D-AF79-49C7-AD9E-A4DD1D98361A}</t>
+          <t>{17F6A454-5ABF-4DFB-A78A-D146D086082D}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>513</v>
+        <v>408</v>
       </c>
       <c r="D50" t="n">
-        <v>527</v>
+        <v>412</v>
       </c>
       <c r="E50" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>شاشف إنسوب إمميني</t>
+          <t>طرح اخر لعيد الصليب</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{93BD22E8-BF7D-4E60-A57A-13DAE76001A3}</t>
+          <t>{0BD005D7-2E83-417A-9686-5430EAAF391B}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>528</v>
+        <v>413</v>
       </c>
       <c r="D51" t="n">
-        <v>565</v>
+        <v>417</v>
       </c>
       <c r="E51" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>لحن راشى نى</t>
+          <t>مرد طرح عيد الصليب</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{0506AF9A-7F49-49A6-942D-C2D14565C280}</t>
+          <t>{68F134B0-811C-48F0-A7D0-5BB19CE61443}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>566</v>
+        <v>418</v>
       </c>
       <c r="D52" t="n">
-        <v>580</v>
+        <v>418</v>
       </c>
       <c r="E52" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ذفتية بانديس</t>
+          <t>أفرحى يا مريم</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{E63D9888-2FCA-494A-AA68-15E76387F435}</t>
+          <t>{1C20AEEF-0DEB-4F74-A46A-AFC5A06DC744}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>581</v>
+        <v>419</v>
       </c>
       <c r="D53" t="n">
-        <v>605</v>
+        <v>432</v>
       </c>
       <c r="E53" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>سينا اتشو</t>
+          <t>تماجيد نهضة العذراء</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{63C8AA8A-342F-4B05-BFCE-A3098B55F558}</t>
+          <t>{7DE226B6-2157-492D-AB80-4448CDB8A41A}</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>606</v>
+        <v>433</v>
       </c>
       <c r="D54" t="n">
-        <v>617</v>
+        <v>433</v>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>فاي بى إبليمين</t>
+          <t>لحن شيري ماريا</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{01E8A009-C53E-4034-AA0C-E39290F9C47E}</t>
+          <t>{1E7E7987-2CAA-4858-AB80-5A0AF761B6EF}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>618</v>
+        <v>434</v>
       </c>
       <c r="D55" t="n">
-        <v>634</v>
+        <v>453</v>
       </c>
       <c r="E55" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>اطاي بارثينوس</t>
+          <t>إك اسماروؤت</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{18835C90-087E-4BAC-9D66-708BC1E04983}</t>
+          <t>{D2101135-3E00-460B-BDBC-0ED4AE799C01}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>635</v>
+        <v>454</v>
       </c>
       <c r="D56" t="n">
-        <v>656</v>
+        <v>454</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>او اون او هلبيس</t>
+          <t>لحن شيرى ثيؤطوكى</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{1F005296-1C13-4026-A9B3-26C9C6CD6D9D}</t>
+          <t>{18389A37-F3FC-4832-AAAE-BB56BAA2569D}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>657</v>
+        <v>455</v>
       </c>
       <c r="D57" t="n">
-        <v>661</v>
+        <v>461</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>اري ابريسفافين</t>
+          <t>لحن أو كيريوس</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{08694BF7-6D62-4C4C-BA7C-6CFED091D44A}</t>
+          <t>{9374086D-AF79-49C7-AD9E-A4DD1D98361A}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>662</v>
+        <v>462</v>
       </c>
       <c r="D58" t="n">
-        <v>663</v>
+        <v>476</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ابؤرو</t>
+          <t>شاشف إنسوب إمميني</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{DD757736-F2EB-40FA-9016-1E28087A0BE5}</t>
+          <t>{93BD22E8-BF7D-4E60-A57A-13DAE76001A3}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>664</v>
+        <v>477</v>
       </c>
       <c r="D59" t="n">
-        <v>668</v>
+        <v>514</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>مديح السلام لك يا مريم</t>
+          <t>لحن راشى نى</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{1796645F-35B4-4F6F-9673-838DE7EF8F58}</t>
+          <t>{0506AF9A-7F49-49A6-942D-C2D14565C280}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>669</v>
+        <v>515</v>
       </c>
       <c r="D60" t="n">
-        <v>699</v>
+        <v>529</v>
       </c>
       <c r="E60" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>خين أفران</t>
+          <t>ذفتية بانديس</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{FD75781B-0996-4E12-BF4C-D163B4D1708F}</t>
+          <t>{E63D9888-2FCA-494A-AA68-15E76387F435}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>700</v>
+        <v>530</v>
       </c>
       <c r="D61" t="n">
-        <v>702</v>
+        <v>554</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>اسمعي يا ابنة</t>
+          <t>سينا اتشو</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{3C5D9889-94E1-4B35-82B5-58786720BA8A}</t>
+          <t>{63C8AA8A-342F-4B05-BFCE-A3098B55F558}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>703</v>
+        <v>555</v>
       </c>
       <c r="D62" t="n">
-        <v>707</v>
+        <v>566</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>اوشية الانجيل</t>
+          <t>فاي بى إبليمين</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{B897D380-076C-414A-9934-423AA6230FED}</t>
+          <t>{01E8A009-C53E-4034-AA0C-E39290F9C47E}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>708</v>
+        <v>567</v>
       </c>
       <c r="D63" t="n">
-        <v>729</v>
+        <v>583</v>
       </c>
       <c r="E63" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>طواف مزمور عيد النيروز</t>
+          <t>اطاي بارثينوس</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{A05C62FF-6D7E-4E98-A99D-9A598F41AECB}</t>
+          <t>{18835C90-087E-4BAC-9D66-708BC1E04983}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>730</v>
+        <v>584</v>
       </c>
       <c r="D64" t="n">
-        <v>731</v>
+        <v>605</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>مرد مزمور النيروز</t>
+          <t>او اون او هلبيس</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{11818F8A-85CC-4811-BF72-D444EBE28DB4}</t>
+          <t>{1F005296-1C13-4026-A9B3-26C9C6CD6D9D}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>732</v>
+        <v>606</v>
       </c>
       <c r="D65" t="n">
-        <v>733</v>
+        <v>610</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>طواف المزمور</t>
+          <t>اري ابريسفافين</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{FD80A82A-8C5C-4D6C-9644-19E9CC3FEC0F}</t>
+          <t>{08694BF7-6D62-4C4C-BA7C-6CFED091D44A}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>734</v>
+        <v>611</v>
       </c>
       <c r="D66" t="n">
-        <v>735</v>
+        <v>612</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -23429,292 +23450,292 @@
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>مرد مزمور الصليب</t>
+          <t>ابؤرو</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{0BC1F8D8-BE35-4C07-A134-EAB9CF63D177}</t>
+          <t>{DD757736-F2EB-40FA-9016-1E28087A0BE5}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>736</v>
+        <v>613</v>
       </c>
       <c r="D67" t="n">
-        <v>737</v>
+        <v>617</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>مرد مزمور الشعانين</t>
+          <t>مديح السلام لك يا مريم</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{2AA95ED2-79CB-40D2-B716-1CB9E9E65C87}</t>
+          <t>{1796645F-35B4-4F6F-9673-838DE7EF8F58}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>738</v>
+        <v>618</v>
       </c>
       <c r="D68" t="n">
-        <v>738</v>
+        <v>648</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>مرد مزمور التجلي</t>
+          <t>خين أفران</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{51B41EEC-6FED-4A00-98C4-8291643CE6F6}</t>
+          <t>{FD75781B-0996-4E12-BF4C-D163B4D1708F}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>739</v>
+        <v>649</v>
       </c>
       <c r="D69" t="n">
-        <v>740</v>
+        <v>651</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>لحن جي افساجي</t>
+          <t>اسمعي يا ابنة</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{BADDC8B6-0477-4F7D-94E5-E13A260C8ECA}</t>
+          <t>{3C5D9889-94E1-4B35-82B5-58786720BA8A}</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>741</v>
+        <v>652</v>
       </c>
       <c r="D70" t="n">
-        <v>741</v>
+        <v>656</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>مزمور صوم وعشيات اعياد السيدة العذراء</t>
+          <t>اوشية الانجيل</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{AB54231C-F141-461A-8580-187ADC04F4DB}</t>
+          <t>{B897D380-076C-414A-9934-423AA6230FED}</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>742</v>
+        <v>657</v>
       </c>
       <c r="D71" t="n">
-        <v>743</v>
+        <v>678</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>طواف صوم واعياد العذراء</t>
+          <t>لحن جي افساجي</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{AD767EA5-20E9-48D6-9567-43335CC42D9A}</t>
+          <t>{BADDC8B6-0477-4F7D-94E5-E13A260C8ECA}</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>744</v>
+        <v>679</v>
       </c>
       <c r="D72" t="n">
-        <v>746</v>
+        <v>679</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>مارو اتشاسف</t>
+          <t>مزمور صوم وعشيات اعياد السيدة العذراء</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{62A12AF8-CB6D-4CC5-9DB0-B73A7C24E2AD}</t>
+          <t>{AB54231C-F141-461A-8580-187ADC04F4DB}</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>747</v>
+        <v>680</v>
       </c>
       <c r="D73" t="n">
-        <v>756</v>
+        <v>681</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>مقدمة الانجيل</t>
+          <t>طواف مزمور عيد النيروز</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{C9DDD86A-610C-49CA-81D2-F3293213F325}</t>
+          <t>{A05C62FF-6D7E-4E98-A99D-9A598F41AECB}</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>757</v>
+        <v>682</v>
       </c>
       <c r="D74" t="n">
-        <v>766</v>
+        <v>683</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>الانجيل قبطي</t>
+          <t>طواف صوم واعياد العذراء</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{B900AA98-6A60-4787-8E81-4111C4CE8DC1}</t>
+          <t>{AD767EA5-20E9-48D6-9567-43335CC42D9A}</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>767</v>
+        <v>684</v>
       </c>
       <c r="D75" t="n">
-        <v>770</v>
+        <v>686</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>المزمور</t>
+          <t>مزمور باكر عيد الميلاد قبطي</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{6D1E6E7D-EECE-483C-A3AE-C135D02E717C}</t>
+          <t>{215DD854-9794-4375-BC3C-48AB43CE6E80}</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>771</v>
+        <v>687</v>
       </c>
       <c r="D76" t="n">
-        <v>772</v>
+        <v>690</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>فليرفعوه</t>
+          <t>طواف مزمور عشية وباكر عيد الميلاد</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{23533FC3-43FE-456F-9454-70C3088055E7}</t>
+          <t>{978B4431-5038-42EA-A7C5-E7190483D4CF}</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>773</v>
+        <v>691</v>
       </c>
       <c r="D77" t="n">
-        <v>775</v>
+        <v>694</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>الانجيل</t>
+          <t>طواف المزمور</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{B74DBB8C-2B2D-46E4-9508-DA46008D19A4}</t>
+          <t>{FD80A82A-8C5C-4D6C-9644-19E9CC3FEC0F}</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>776</v>
+        <v>695</v>
       </c>
       <c r="D78" t="n">
-        <v>777</v>
+        <v>697</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>مرد انجيل الصليب</t>
+          <t>مارو اتشاسف</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{EDE09087-B069-49CA-8211-757926594D3F}</t>
+          <t>{62A12AF8-CB6D-4CC5-9DB0-B73A7C24E2AD}</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>778</v>
+        <v>698</v>
       </c>
       <c r="D79" t="n">
-        <v>780</v>
+        <v>707</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>مرد انجيل عشية الشعانين</t>
+          <t>مرد مزمور النيروز</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{995B3A40-EED6-4463-A2DC-498DF1965406}</t>
+          <t>{11818F8A-85CC-4811-BF72-D444EBE28DB4}</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>781</v>
+        <v>708</v>
       </c>
       <c r="D80" t="n">
-        <v>782</v>
+        <v>709</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -23723,61 +23744,61 @@
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>مرد انجيل باكر الشعانين</t>
+          <t>مرد مزمور الصليب</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{AE580C60-FE10-48A4-8A58-816566E88A65}</t>
+          <t>{0BC1F8D8-BE35-4C07-A134-EAB9CF63D177}</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>783</v>
+        <v>710</v>
       </c>
       <c r="D81" t="n">
-        <v>785</v>
+        <v>711</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>مرد انجيل التجلي</t>
+          <t>مرد مزمور الميلاد</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{424645C4-4007-414C-8960-3DE1095D0419}</t>
+          <t>{49683C84-CF98-4F29-AD91-1CF871381FD1}</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>786</v>
+        <v>712</v>
       </c>
       <c r="D82" t="n">
-        <v>786</v>
+        <v>713</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>فاي اريه بي اوو</t>
+          <t>مرد مزمور الشعانين</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{B7D98377-B994-4654-B49C-DE10E0DDE4F1}</t>
+          <t>{2AA95ED2-79CB-40D2-B716-1CB9E9E65C87}</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>787</v>
+        <v>714</v>
       </c>
       <c r="D83" t="n">
-        <v>787</v>
+        <v>714</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -23786,19 +23807,19 @@
     <row r="84" ht="18.75" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>مرد الانجيل السنوي</t>
+          <t>مرد مزمور التجلي</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{BEECCC68-2AEF-4568-91AA-98BCD14D3B92}</t>
+          <t>{51B41EEC-6FED-4A00-98C4-8291643CE6F6}</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>788</v>
+        <v>715</v>
       </c>
       <c r="D84" t="n">
-        <v>789</v>
+        <v>716</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -23807,61 +23828,61 @@
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>مرد انجيل كيهك 1</t>
+          <t>مقدمة الانجيل</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{765066DC-37D0-48B3-9046-D4F98F5B05BC}</t>
+          <t>{C9DDD86A-610C-49CA-81D2-F3293213F325}</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>790</v>
+        <v>717</v>
       </c>
       <c r="D85" t="n">
-        <v>791</v>
+        <v>726</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>مرد انجيل كيهك 2</t>
+          <t>الانجيل قبطي</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{D5E69BAC-0157-4B69-9255-B6775E2EE11D}</t>
+          <t>{B900AA98-6A60-4787-8E81-4111C4CE8DC1}</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>792</v>
+        <v>727</v>
       </c>
       <c r="D86" t="n">
-        <v>793</v>
+        <v>730</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" ht="18.75" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>تكملة مشتركة لكيهك</t>
+          <t>المزمور</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{98BAFA87-CFC9-4304-8B00-99AA9EC72A3D}</t>
+          <t>{6D1E6E7D-EECE-483C-A3AE-C135D02E717C}</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>794</v>
+        <v>731</v>
       </c>
       <c r="D87" t="n">
-        <v>795</v>
+        <v>732</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -23870,103 +23891,103 @@
     <row r="88" ht="18.75" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>مرد انجيل صوم العذراء - عشية</t>
+          <t>فليرفعوه</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{5043F523-486A-4B7C-9F73-2F3F943BB30C}</t>
+          <t>{23533FC3-43FE-456F-9454-70C3088055E7}</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>796</v>
+        <v>733</v>
       </c>
       <c r="D88" t="n">
-        <v>797</v>
+        <v>735</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" ht="18.75" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>مرد انجيل صوم العذراء - باكر</t>
+          <t>الانجيل</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{037D8578-7219-4388-AFC5-4753352BFA8C}</t>
+          <t>{B74DBB8C-2B2D-46E4-9508-DA46008D19A4}</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>798</v>
+        <v>736</v>
       </c>
       <c r="D89" t="n">
-        <v>798</v>
+        <v>737</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>اري ابرسفافين</t>
+          <t>مرد انجيل الصليب</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{49534D46-CF48-4D9B-ADBF-B776827F6670}</t>
+          <t>{EDE09087-B069-49CA-8211-757926594D3F}</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>799</v>
+        <v>738</v>
       </c>
       <c r="D90" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ربع يقال في صوم الرسل</t>
+          <t>مرد إنجيل عشية وباكر عيد الميلاد</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{F5AB11D4-D7D2-4DA3-A830-32BA45BCB16D}</t>
+          <t>{DC185CA7-709B-4E23-B0E7-0543D701D531}</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>801</v>
+        <v>741</v>
       </c>
       <c r="D91" t="n">
-        <v>802</v>
+        <v>743</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ربع قال في عيد الرسل</t>
+          <t>مرد انجيل عشية الشعانين</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{38E5A337-7696-4261-833A-DF790456C6A8}</t>
+          <t>{995B3A40-EED6-4463-A2DC-498DF1965406}</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>803</v>
+        <v>744</v>
       </c>
       <c r="D92" t="n">
-        <v>804</v>
+        <v>745</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
@@ -23975,294 +23996,546 @@
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>جي افسمارؤوت</t>
+          <t>مرد انجيل باكر الشعانين</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{DD53DBD3-9599-4D1D-B8C1-EAB35FBD36D3}</t>
+          <t>{AE580C60-FE10-48A4-8A58-816566E88A65}</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>805</v>
+        <v>746</v>
       </c>
       <c r="D93" t="n">
-        <v>806</v>
+        <v>748</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>اوشية السلام</t>
+          <t>مرد انجيل التجلي</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{4DB48091-D529-44E1-939A-81BC51E41D41}</t>
+          <t>{424645C4-4007-414C-8960-3DE1095D0419}</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>807</v>
+        <v>749</v>
       </c>
       <c r="D94" t="n">
-        <v>819</v>
+        <v>749</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>اوشية الآباء</t>
+          <t>فاي اريه بي اوو</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{64C3B268-ED69-4006-B650-A09460633196}</t>
+          <t>{B7D98377-B994-4654-B49C-DE10E0DDE4F1}</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="D95" t="n">
-        <v>828</v>
+        <v>750</v>
       </c>
       <c r="E95" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>أوشية الموضع</t>
+          <t>مرد الانجيل السنوي</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{9DACDA4B-74BF-4F4B-A961-DA43C70DC545}</t>
+          <t>{BEECCC68-2AEF-4568-91AA-98BCD14D3B92}</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>829</v>
+        <v>751</v>
       </c>
       <c r="D96" t="n">
-        <v>837</v>
+        <v>752</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>تكملة الاواشي</t>
+          <t>مرد انجيل كيهك 1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{5DFBA264-6756-41DD-8F16-17B76F3E3F0F}</t>
+          <t>{765066DC-37D0-48B3-9046-D4F98F5B05BC}</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>838</v>
+        <v>753</v>
       </c>
       <c r="D97" t="n">
-        <v>852</v>
+        <v>754</v>
       </c>
       <c r="E97" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>أوشية الإجتماعات</t>
+          <t>مرد انجيل كيهك 2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{7259AEAC-8F21-4B0E-9C69-498513DD91E4}</t>
+          <t>{D5E69BAC-0157-4B69-9255-B6775E2EE11D}</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>853</v>
+        <v>755</v>
       </c>
       <c r="D98" t="n">
-        <v>878</v>
+        <v>756</v>
       </c>
       <c r="E98" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ابانا الذي في السموات</t>
+          <t>تكملة مشتركة لكيهك</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{FD187B58-5CE8-4776-8487-9C5928B14F0D}</t>
+          <t>{98BAFA87-CFC9-4304-8B00-99AA9EC72A3D}</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>879</v>
+        <v>757</v>
       </c>
       <c r="D99" t="n">
-        <v>885</v>
+        <v>758</v>
       </c>
       <c r="E99" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>الختام</t>
+          <t>مرد انجيل صوم العذراء - عشية</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{90F50AB7-3911-445D-9C45-41866ECCCED0}</t>
+          <t>{5043F523-486A-4B7C-9F73-2F3F943BB30C}</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>886</v>
+        <v>759</v>
       </c>
       <c r="D100" t="n">
-        <v>888</v>
+        <v>760</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" ht="18.75" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>تكملة على حسب المناسبة</t>
+          <t>مرد انجيل صوم العذراء - باكر</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{A18EDC94-F257-4FAC-99C7-0A8EA70F0FAF}</t>
+          <t>{037D8578-7219-4388-AFC5-4753352BFA8C}</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>889</v>
+        <v>761</v>
       </c>
       <c r="D101" t="n">
-        <v>907</v>
+        <v>761</v>
       </c>
       <c r="E101" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" ht="18.75" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>في حضور الاسقف</t>
+          <t>اري ابرسفافين</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{A9183893-7B7E-459F-8547-F7A8F7D2D521}</t>
+          <t>{49534D46-CF48-4D9B-ADBF-B776827F6670}</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>908</v>
+        <v>762</v>
       </c>
       <c r="D102" t="n">
-        <v>916</v>
+        <v>763</v>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" ht="18.75" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>الختام 2</t>
+          <t>ربع يقال في صوم الرسل</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{A3DED752-5159-4F64-86F6-7B95F37A8327}</t>
+          <t>{F5AB11D4-D7D2-4DA3-A830-32BA45BCB16D}</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>917</v>
+        <v>764</v>
       </c>
       <c r="D103" t="n">
-        <v>921</v>
+        <v>765</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" ht="18.75" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>اوشية المياة</t>
+          <t>ربع قال في عيد الرسل</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{BA51DE45-1C6C-43E6-AFF3-A98C3B049C70}</t>
+          <t>{38E5A337-7696-4261-833A-DF790456C6A8}</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>922</v>
+        <v>766</v>
       </c>
       <c r="D104" t="n">
-        <v>928</v>
+        <v>767</v>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" ht="18.75" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>أوشية الزروع</t>
+          <t>جي افسمارؤوت</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{A0DD24B6-1053-42A1-8391-038649B3219B}</t>
+          <t>{DD53DBD3-9599-4D1D-B8C1-EAB35FBD36D3}</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>929</v>
+        <v>768</v>
       </c>
       <c r="D105" t="n">
-        <v>936</v>
+        <v>769</v>
       </c>
       <c r="E105" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" ht="18.75" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
+          <t>اوشية السلام</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>{4DB48091-D529-44E1-939A-81BC51E41D41}</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>770</v>
+      </c>
+      <c r="D106" t="n">
+        <v>782</v>
+      </c>
+      <c r="E106" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" ht="18.75" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>اوشية الآباء</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>{64C3B268-ED69-4006-B650-A09460633196}</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>783</v>
+      </c>
+      <c r="D107" t="n">
+        <v>791</v>
+      </c>
+      <c r="E107" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" ht="18.75" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>أوشية الموضع</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>{9DACDA4B-74BF-4F4B-A961-DA43C70DC545}</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>792</v>
+      </c>
+      <c r="D108" t="n">
+        <v>800</v>
+      </c>
+      <c r="E108" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" ht="18.75" customHeight="1">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>تكملة الاواشي</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>{5DFBA264-6756-41DD-8F16-17B76F3E3F0F}</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>801</v>
+      </c>
+      <c r="D109" t="n">
+        <v>815</v>
+      </c>
+      <c r="E109" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" ht="18.75" customHeight="1">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>أوشية الإجتماعات</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>{7259AEAC-8F21-4B0E-9C69-498513DD91E4}</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>816</v>
+      </c>
+      <c r="D110" t="n">
+        <v>841</v>
+      </c>
+      <c r="E110" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111" ht="18.75" customHeight="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ابانا الذي في السموات</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>{FD187B58-5CE8-4776-8487-9C5928B14F0D}</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>842</v>
+      </c>
+      <c r="D111" t="n">
+        <v>848</v>
+      </c>
+      <c r="E111" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" ht="18.75" customHeight="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>الختام</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>{90F50AB7-3911-445D-9C45-41866ECCCED0}</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>849</v>
+      </c>
+      <c r="D112" t="n">
+        <v>851</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" ht="18.75" customHeight="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>تكملة على حسب المناسبة</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{A18EDC94-F257-4FAC-99C7-0A8EA70F0FAF}</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>852</v>
+      </c>
+      <c r="D113" t="n">
+        <v>870</v>
+      </c>
+      <c r="E113" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" ht="18.75" customHeight="1">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>في حضور الاسقف</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>{A9183893-7B7E-459F-8547-F7A8F7D2D521}</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>871</v>
+      </c>
+      <c r="D114" t="n">
+        <v>879</v>
+      </c>
+      <c r="E114" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" ht="18.75" customHeight="1">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>الختام 2</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>{A3DED752-5159-4F64-86F6-7B95F37A8327}</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>880</v>
+      </c>
+      <c r="D115" t="n">
+        <v>884</v>
+      </c>
+      <c r="E115" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" ht="18.75" customHeight="1">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>اوشية المياة</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>{BA51DE45-1C6C-43E6-AFF3-A98C3B049C70}</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>885</v>
+      </c>
+      <c r="D116" t="n">
+        <v>891</v>
+      </c>
+      <c r="E116" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" ht="18.75" customHeight="1">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>أوشية الزروع</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>{A0DD24B6-1053-42A1-8391-038649B3219B}</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>892</v>
+      </c>
+      <c r="D117" t="n">
+        <v>899</v>
+      </c>
+      <c r="E117" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" ht="18.75" customHeight="1">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>اوشية الأهوية والثمار</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>{BD1D9BBC-5109-4880-BAFF-4C03F37555C1}</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>937</v>
-      </c>
-      <c r="D106" t="n">
-        <v>942</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="C118" t="n">
+        <v>900</v>
+      </c>
+      <c r="D118" t="n">
+        <v>905</v>
+      </c>
+      <c r="E118" t="n">
         <v>6</v>
       </c>
     </row>
@@ -25550,14 +25823,14 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="21.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
     <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -26829,40 +27102,40 @@
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>مقدمة الدفنار</t>
+          <t>مقدمة الدفنار الآدام</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{DBBEB49F-3396-41D0-81FF-0A028C3CB4DA}</t>
+          <t>{0420AA0C-B21A-478D-88EA-8378E9539EDE}</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1532</v>
       </c>
       <c r="D61" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>مقدمة الدفنار الآدام</t>
+          <t>مقدمة الدفنار الواطس</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{0420AA0C-B21A-478D-88EA-8378E9539EDE}</t>
+          <t>{F2541D73-C210-4196-BE50-DF6E6142A86C}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="D62" t="n">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
@@ -26871,103 +27144,103 @@
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>مقدمة الدفنار الواطس</t>
+          <t>الدفنار</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{F2541D73-C210-4196-BE50-DF6E6142A86C}</t>
+          <t>{A509B738-02BB-455A-944E-9E56D85C8942}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="D63" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>الدفنار</t>
+          <t>ختام الثؤطوكيات الادام</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{A509B738-02BB-455A-944E-9E56D85C8942}</t>
+          <t>{14A3A43C-A9F7-45A8-A510-EE3F33D99572}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="D64" t="n">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ختام الثؤطوكيات الادام</t>
+          <t>ختام الثيؤطوكيات الواطس</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{14A3A43C-A9F7-45A8-A510-EE3F33D99572}</t>
+          <t>{BF439D71-64D1-4376-8E4A-812437425EBB}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1543</v>
+        <v>1559</v>
       </c>
       <c r="D65" t="n">
-        <v>1559</v>
+        <v>1578</v>
       </c>
       <c r="E65" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ختام الثيؤطوكيات الواطس</t>
+          <t>قانون الايمان</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{BF439D71-64D1-4376-8E4A-812437425EBB}</t>
+          <t>{A12368B5-4E89-4682-AF79-DC1979BA120B}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1560</v>
+        <v>1579</v>
       </c>
       <c r="D66" t="n">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>قانون الايمان</t>
+          <t>ختام التسبحة</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{A12368B5-4E89-4682-AF79-DC1979BA120B}</t>
+          <t>{BABBF91F-DC4B-4DBC-A6C1-054AEA7290F3}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1580</v>
+        <v>1594</v>
       </c>
       <c r="D67" t="n">
-        <v>1594</v>
+        <v>1608</v>
       </c>
       <c r="E67" t="n">
         <v>15</v>
@@ -26976,66 +27249,46 @@
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ختام التسبحة</t>
+          <t>قدوس قدوس قدوس</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{BABBF91F-DC4B-4DBC-A6C1-054AEA7290F3}</t>
+          <t>{F2F363F3-5DD8-474B-94A0-6895758AB76D}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="D68" t="n">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>قدوس قدوس قدوس</t>
+          <t>ابانا الذي في السموات</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{F2F363F3-5DD8-474B-94A0-6895758AB76D}</t>
+          <t>{68CD9B8E-B861-4695-8C6E-F8E0D19B6D78}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="D69" t="n">
         <v>1613</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>ابانا الذي في السموات</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>{68CD9B8E-B861-4695-8C6E-F8E0D19B6D78}</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1614</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1614</v>
-      </c>
-      <c r="E70" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="70" ht="18.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27047,14 +27300,14 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="28.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="17.71928571428571" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.29071428571428" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="16.43357142857143" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="53.86214285714286" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="41.29071428571429" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17.71928571428571" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
+    <col width="17.29071428571428" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
+    <col width="16.43357142857143" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -27084,10 +27337,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
+    <row r="2" ht="19.5" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hyperlink</t>
+          <t>الفهرس</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -27105,7 +27358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1">
+    <row r="3" ht="19.5" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>تين ثينو</t>
@@ -27126,7 +27379,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1">
+    <row r="4" ht="19.5" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>الهوس الكبير</t>
@@ -27147,7 +27400,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
+    <row r="5" ht="19.5" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>مديح أجيوس أوثيؤوس</t>
@@ -27168,7 +27421,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1">
+    <row r="6" ht="19.5" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>ابصالية آدام على الهوس الاول</t>
@@ -27189,7 +27442,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>الهوس الاول</t>
@@ -27210,7 +27463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1">
+    <row r="8" ht="19.5" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>لبش الهوس الاول</t>
@@ -27231,7 +27484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1">
+    <row r="9" ht="19.5" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>قال الرب لموسى</t>
@@ -27252,7 +27505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>طرح آدام على الهوس الاول</t>
@@ -27273,7 +27526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>ابصالية آدام على الهوس الثاني</t>
@@ -27294,7 +27547,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1">
+    <row r="12" ht="19.5" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>انشئ وزنا و نظام</t>
@@ -27315,7 +27568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1">
+    <row r="13" ht="19.5" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>الهوس التاني</t>
@@ -27336,7 +27589,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>لبش الهوس الثاني</t>
@@ -27357,7 +27610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1">
+    <row r="15" ht="19.5" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>فلنرتل مع داود</t>
@@ -27378,7 +27631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1">
+    <row r="16" ht="19.5" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>طرح على الهوس الثانى</t>
@@ -27399,7 +27652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1">
+    <row r="17" ht="19.5" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>ابصالية آدام على الهوس الثالث</t>
@@ -27420,7 +27673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1">
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>ابصالية أشكرك يا إله يعقوب</t>
@@ -27441,7 +27694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1">
+    <row r="19" ht="19.5" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>السجود يليق بالثالوث القدوس</t>
@@ -27462,7 +27715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1">
+    <row r="20" ht="19.5" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>الهوس الثالث</t>
@@ -27483,7 +27736,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1">
+    <row r="21" ht="19.5" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>اريبصالين</t>
@@ -27504,7 +27757,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1">
+    <row r="22" ht="19.5" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>مديح اللـه الازلي</t>
@@ -27525,7 +27778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1">
+    <row r="23" ht="19.5" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>لحن تينين</t>
@@ -27546,7 +27799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1">
+    <row r="24" ht="19.5" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>تين اويه انسوك</t>
@@ -27717,544 +27970,544 @@
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>الهوس الرابع</t>
+          <t>ني اثنوس تيرو</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{96EEC7EB-8964-4F67-B63E-CA55A0A3D11D}</t>
+          <t>{E052F467-3B39-4F35-9D72-8B11039F040B}</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>635</v>
       </c>
       <c r="D32" t="n">
-        <v>687</v>
+        <v>638</v>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>طرح على الهوس الرابع</t>
+          <t>الهوس الرابع</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{E6455E19-6AB4-419E-A7B4-41F6B15F563F}</t>
+          <t>{96EEC7EB-8964-4F67-B63E-CA55A0A3D11D}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>688</v>
+        <v>639</v>
       </c>
       <c r="D33" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>تسبحة الأيام</t>
+          <t>طرح على الهوس الرابع</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{34B2EF10-1881-4BA7-95A7-7AB2F6F6651C}</t>
+          <t>{E6455E19-6AB4-419E-A7B4-41F6B15F563F}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D34" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>امدح عذراء و بتول</t>
+          <t>تسبحة الأيام</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{C8259B7A-94EF-4DD5-9C63-1B633E2C4874}</t>
+          <t>{34B2EF10-1881-4BA7-95A7-7AB2F6F6651C}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D35" t="n">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ابصالية الأحد</t>
+          <t>امدح عذراء و بتول</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{F263153B-C7A8-4E6B-AACA-6F05AF050F2E}</t>
+          <t>{C8259B7A-94EF-4DD5-9C63-1B633E2C4874}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="D36" t="n">
-        <v>738</v>
+        <v>710</v>
       </c>
       <c r="E36" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>افتح فاي بالتسابيح</t>
+          <t>ابصالية الأحد</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{B03ABE31-398B-41D7-BA50-E82521E94218}</t>
+          <t>{F263153B-C7A8-4E6B-AACA-6F05AF050F2E}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>739</v>
+        <v>711</v>
       </c>
       <c r="D37" t="n">
-        <v>764</v>
+        <v>742</v>
       </c>
       <c r="E37" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ابصالية الاثنين كيهك</t>
+          <t>افتح فاي بالتسابيح</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{6D03F8B8-BBB8-4739-8247-6A6F19C0BB14}</t>
+          <t>{B03ABE31-398B-41D7-BA50-E82521E94218}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>765</v>
+        <v>743</v>
       </c>
       <c r="D38" t="n">
-        <v>788</v>
+        <v>768</v>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ابصالية الاثنين</t>
+          <t>ابصالية الاثنين كيهك</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{C966C7AC-73F9-4177-AA7F-71D0428224AF}</t>
+          <t>{6D03F8B8-BBB8-4739-8247-6A6F19C0BB14}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="D39" t="n">
-        <v>819</v>
+        <v>792</v>
       </c>
       <c r="E39" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ابصالية الثلاثاء كيهك</t>
+          <t>ابصالية الاثنين</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{62D9D915-CEA8-47B8-8125-39CCB37E9C9E}</t>
+          <t>{C966C7AC-73F9-4177-AA7F-71D0428224AF}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>820</v>
+        <v>793</v>
       </c>
       <c r="D40" t="n">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="E40" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ابصالية الثلاثاء</t>
+          <t>ابصالية الثلاثاء كيهك</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{31645468-E515-4F5A-85DB-DEE662F6432A}</t>
+          <t>{62D9D915-CEA8-47B8-8125-39CCB37E9C9E}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>844</v>
+        <v>824</v>
       </c>
       <c r="D41" t="n">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ابصالية الأربعاء كيهك</t>
+          <t>ابصالية الثلاثاء</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{B6F734EE-FC8D-472D-B813-157D0BD9098F}</t>
+          <t>{31645468-E515-4F5A-85DB-DEE662F6432A}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="D42" t="n">
-        <v>889</v>
+        <v>859</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ابصالية الأربعاء</t>
+          <t>ابصالية الأربعاء كيهك</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{8ABA75EA-D793-46A0-8AE2-5B61A6B4FD7E}</t>
+          <t>{B6F734EE-FC8D-472D-B813-157D0BD9098F}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>890</v>
+        <v>860</v>
       </c>
       <c r="D43" t="n">
-        <v>914</v>
+        <v>893</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ابصالية الخميس كيهك</t>
+          <t>ابصالية الأربعاء</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{9D0078A8-FA50-4195-B6E6-FCCB6C77304B}</t>
+          <t>{8ABA75EA-D793-46A0-8AE2-5B61A6B4FD7E}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>915</v>
+        <v>894</v>
       </c>
       <c r="D44" t="n">
-        <v>944</v>
+        <v>918</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ابصالية الخميس</t>
+          <t>ابصالية الخميس كيهك</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{02352F94-02C4-4D7F-9247-697DA282E7C9}</t>
+          <t>{9D0078A8-FA50-4195-B6E6-FCCB6C77304B}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>945</v>
+        <v>919</v>
       </c>
       <c r="D45" t="n">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ابصالية الجمعة كيهك</t>
+          <t>ابصالية الخميس</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{27A7777D-CD4E-4006-8A71-1FCFDEBEEC50}</t>
+          <t>{02352F94-02C4-4D7F-9247-697DA282E7C9}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>966</v>
+        <v>949</v>
       </c>
       <c r="D46" t="n">
-        <v>994</v>
+        <v>969</v>
       </c>
       <c r="E46" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ابصالية الجمعة</t>
+          <t>ابصالية الجمعة كيهك</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{E8504067-DC7B-4818-8157-B947A0A74D9A}</t>
+          <t>{27A7777D-CD4E-4006-8A71-1FCFDEBEEC50}</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>995</v>
+        <v>970</v>
       </c>
       <c r="D47" t="n">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ابصالية السبت كيهك</t>
+          <t>ابصالية الجمعة</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{0215A718-3256-4C80-A208-2CF20C32ED43}</t>
+          <t>{E8504067-DC7B-4818-8157-B947A0A74D9A}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="D48" t="n">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ابصالية السبت</t>
+          <t>ابصالية السبت كيهك</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{BF504610-6275-426C-A939-798A885C5C71}</t>
+          <t>{0215A718-3256-4C80-A208-2CF20C32ED43}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D49" t="n">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="E49" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>مقدمة الثيؤطوكيات الأدام</t>
+          <t>تسبحة عشية - ابصالية السبت للسيدة العذراء (اي سوتيم)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{E358EDB7-F8FF-43DA-A8B6-81839E23E4C6}</t>
+          <t>{DD360667-581E-4622-96F0-75719F64FCC3}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="D50" t="n">
-        <v>1052</v>
+        <v>1066</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>مديح واطس على ثيؤطوكية يوم الأربعاء</t>
+          <t>ابصالية السبت</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{4810C4FE-0FD4-43E8-BA7D-D3C0522636DE}</t>
+          <t>{BF504610-6275-426C-A939-798A885C5C71}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1053</v>
+        <v>1067</v>
       </c>
       <c r="D51" t="n">
-        <v>1070</v>
+        <v>1098</v>
       </c>
       <c r="E51" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>مديح واطس ثاني على ثيؤطوكية يوم الأربعاء</t>
+          <t>تسبحة عشية - ابصالية السبت واطس للسيدة العذراء</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{9261CAF4-1583-4F46-A926-6B219C2AC417}</t>
+          <t>{9E9DC12F-A89B-4949-9B62-ABC328F0E5F6}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1071</v>
+        <v>1099</v>
       </c>
       <c r="D52" t="n">
-        <v>1081</v>
+        <v>1122</v>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>مديح واطس على ثيؤطوكية يوم الجمعة</t>
+          <t>تسبحة عشية - مديح واطس للسيدة العذراء (أمدح في عذراء و بتول)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{C50B9029-6A87-42EB-BA77-2B532903A4FB}</t>
+          <t>{E4EA5A74-6525-499C-B8AE-CF72710B4DF7}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1082</v>
+        <v>1123</v>
       </c>
       <c r="D53" t="n">
-        <v>1096</v>
+        <v>1136</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>مقدمة الثيؤطوكيات الواطس</t>
+          <t>مقدمة الثيؤطوكيات الأدام</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{F96B080A-3FB2-430B-9BED-E692E913A9B0}</t>
+          <t>{E358EDB7-F8FF-43DA-A8B6-81839E23E4C6}</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1097</v>
+        <v>1137</v>
       </c>
       <c r="D54" t="n">
-        <v>1098</v>
+        <v>1141</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 1</t>
+          <t>مديح واطس على ثيؤطوكية يوم الأربعاء</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{8B50A9B8-162A-45FD-A40D-5405E501F1E6}</t>
+          <t>{4810C4FE-0FD4-43E8-BA7D-D3C0522636DE}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1099</v>
+        <v>1142</v>
       </c>
       <c r="D55" t="n">
-        <v>1113</v>
+        <v>1159</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>التفسير الأول</t>
+          <t>مديح واطس ثاني على ثيؤطوكية يوم الأربعاء</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{D4868DAE-CB74-4C0C-A7FB-753304BC37AD}</t>
+          <t>{9261CAF4-1583-4F46-A926-6B219C2AC417}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1114</v>
+        <v>1160</v>
       </c>
       <c r="D56" t="n">
-        <v>1122</v>
+        <v>1170</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 2</t>
+          <t>مديح واطس على ثيؤطوكية يوم الجمعة</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{32EA2B33-D0B1-4614-A1AE-C38DAD90639C}</t>
+          <t>{C50B9029-6A87-42EB-BA77-2B532903A4FB}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1123</v>
+        <v>1171</v>
       </c>
       <c r="D57" t="n">
-        <v>1137</v>
+        <v>1185</v>
       </c>
       <c r="E57" t="n">
         <v>15</v>
@@ -28263,61 +28516,61 @@
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>التفسير الثاني</t>
+          <t>مقدمة الثيؤطوكيات الواطس</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{45BFB4F9-197A-4C0C-A878-E3701BD6C849}</t>
+          <t>{F96B080A-3FB2-430B-9BED-E692E913A9B0}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1138</v>
+        <v>1186</v>
       </c>
       <c r="D58" t="n">
-        <v>1146</v>
+        <v>1187</v>
       </c>
       <c r="E58" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 3</t>
+          <t>ثيؤطوكية الأحد 1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{FA3CD3F7-54E6-492D-9CF7-0C7BEAA495D3}</t>
+          <t>{8B50A9B8-162A-45FD-A40D-5405E501F1E6}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1147</v>
+        <v>1188</v>
       </c>
       <c r="D59" t="n">
-        <v>1158</v>
+        <v>1202</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>التفسير الثالث</t>
+          <t>التفسير الأول</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{2C0AB6E1-095C-45F7-AF6B-D2DF92820FEF}</t>
+          <t>{D4868DAE-CB74-4C0C-A7FB-753304BC37AD}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1159</v>
+        <v>1203</v>
       </c>
       <c r="D60" t="n">
-        <v>1167</v>
+        <v>1211</v>
       </c>
       <c r="E60" t="n">
         <v>9</v>
@@ -28326,40 +28579,40 @@
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 4</t>
+          <t>ثيؤطوكية الأحد 2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{02B12569-6A3B-46FB-83E0-2431778D54AE}</t>
+          <t>{32EA2B33-D0B1-4614-A1AE-C38DAD90639C}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1168</v>
+        <v>1212</v>
       </c>
       <c r="D61" t="n">
-        <v>1179</v>
+        <v>1226</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>التفسير الرابع</t>
+          <t>التفسير الثاني</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{62BFD2F3-715B-4943-A3A8-E9468430D253}</t>
+          <t>{45BFB4F9-197A-4C0C-A878-E3701BD6C849}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1180</v>
+        <v>1227</v>
       </c>
       <c r="D62" t="n">
-        <v>1188</v>
+        <v>1235</v>
       </c>
       <c r="E62" t="n">
         <v>9</v>
@@ -28368,40 +28621,40 @@
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 5</t>
+          <t>ثيؤطوكية الأحد 3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{63C9FA19-303C-4B52-AA1C-3573D6A07E8F}</t>
+          <t>{FA3CD3F7-54E6-492D-9CF7-0C7BEAA495D3}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1189</v>
+        <v>1236</v>
       </c>
       <c r="D63" t="n">
-        <v>1203</v>
+        <v>1247</v>
       </c>
       <c r="E63" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>التفسير الخامس</t>
+          <t>التفسير الثالث</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{2C7014BD-372E-4B33-A67C-3EC82A75F2F5}</t>
+          <t>{2C0AB6E1-095C-45F7-AF6B-D2DF92820FEF}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1204</v>
+        <v>1248</v>
       </c>
       <c r="D64" t="n">
-        <v>1212</v>
+        <v>1256</v>
       </c>
       <c r="E64" t="n">
         <v>9</v>
@@ -28410,124 +28663,124 @@
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 6</t>
+          <t>ثيؤطوكية الأحد 4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{BAF08F53-9FAC-4861-B580-81A0251D1BC9}</t>
+          <t>{02B12569-6A3B-46FB-83E0-2431778D54AE}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1213</v>
+        <v>1257</v>
       </c>
       <c r="D65" t="n">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="E65" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>التفسير السادس</t>
+          <t>التفسير الرابع</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{A26163E2-B977-4DA6-A9E2-BD97D007A7A4}</t>
+          <t>{62BFD2F3-715B-4943-A3A8-E9468430D253}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1229</v>
+        <v>1269</v>
       </c>
       <c r="D66" t="n">
-        <v>1236</v>
+        <v>1277</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 7-أ</t>
+          <t>ثيؤطوكية الأحد 5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{64CE0420-479F-4F12-AE0C-F1218BF21635}</t>
+          <t>{63C9FA19-303C-4B52-AA1C-3573D6A07E8F}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1237</v>
+        <v>1278</v>
       </c>
       <c r="D67" t="n">
-        <v>1243</v>
+        <v>1292</v>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>طرح سيموتي</t>
+          <t>التفسير الخامس</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{49B7BA3B-2EC5-4A86-9A89-6531E7EB66A1}</t>
+          <t>{2C7014BD-372E-4B33-A67C-3EC82A75F2F5}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1244</v>
+        <v>1293</v>
       </c>
       <c r="D68" t="n">
-        <v>1249</v>
+        <v>1301</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 7-ب</t>
+          <t>ثيؤطوكية الأحد 6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{C4B931D0-8DA1-4146-B123-E379AB560D91}</t>
+          <t>{BAF08F53-9FAC-4861-B580-81A0251D1BC9}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1250</v>
+        <v>1302</v>
       </c>
       <c r="D69" t="n">
-        <v>1256</v>
+        <v>1317</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>التفسير السابع</t>
+          <t>التفسير السادس</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{1A78E779-8644-4A60-B3F5-68D3624F5401}</t>
+          <t>{A26163E2-B977-4DA6-A9E2-BD97D007A7A4}</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1257</v>
+        <v>1318</v>
       </c>
       <c r="D70" t="n">
-        <v>1264</v>
+        <v>1325</v>
       </c>
       <c r="E70" t="n">
         <v>8</v>
@@ -28536,187 +28789,187 @@
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 8</t>
+          <t>ثيؤطوكية الأحد 7-أ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{2DEEC34A-05B2-4184-A1BE-0F84AFC92A44}</t>
+          <t>{64CE0420-479F-4F12-AE0C-F1218BF21635}</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1265</v>
+        <v>1326</v>
       </c>
       <c r="D71" t="n">
-        <v>1297</v>
+        <v>1332</v>
       </c>
       <c r="E71" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>مديح شيري ني ماريا</t>
+          <t>طرح سيموتي</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{762923AF-53D6-489C-ADA0-A18931824CD6}</t>
+          <t>{49B7BA3B-2EC5-4A86-9A89-6531E7EB66A1}</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1298</v>
+        <v>1333</v>
       </c>
       <c r="D72" t="n">
-        <v>1326</v>
+        <v>1338</v>
       </c>
       <c r="E72" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>طرح شاشف انسوب</t>
+          <t>ثيؤطوكية الأحد 7-ب</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{4FDA7C4D-870C-43F3-B4B6-38F5B1B4D5A6}</t>
+          <t>{C4B931D0-8DA1-4146-B123-E379AB560D91}</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1327</v>
+        <v>1339</v>
       </c>
       <c r="D73" t="n">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>مديح راشي او ماريا</t>
+          <t>التفسير السابع</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{2018CEFD-DE71-4360-A7FF-A6765C92FCA5}</t>
+          <t>{1A78E779-8644-4A60-B3F5-68D3624F5401}</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="D74" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="E74" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>يا م ر ي م</t>
+          <t>ثيؤطوكية الأحد 8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{6EFF99AC-BDD5-400B-AD02-BDDD7891E5E3}</t>
+          <t>{2DEEC34A-05B2-4184-A1BE-0F84AFC92A44}</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="D75" t="n">
-        <v>1374</v>
+        <v>1386</v>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>يا ابنة داود</t>
+          <t>مديح شيري ني ماريا</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{AC841333-B14A-4205-894D-DA7DF6653E1B}</t>
+          <t>{762923AF-53D6-489C-ADA0-A18931824CD6}</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1375</v>
+        <v>1387</v>
       </c>
       <c r="D76" t="n">
-        <v>1401</v>
+        <v>1415</v>
       </c>
       <c r="E76" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 9</t>
+          <t>طرح شاشف انسوب</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{45A96BB7-91BA-4E03-AC22-F7E7039923CE}</t>
+          <t>{4FDA7C4D-870C-43F3-B4B6-38F5B1B4D5A6}</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1402</v>
+        <v>1416</v>
       </c>
       <c r="D77" t="n">
-        <v>1406</v>
+        <v>1424</v>
       </c>
       <c r="E77" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>طرح القطعة ال9</t>
+          <t>مديح راشي او ماريا</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{1FE88F57-6CDF-4D29-B2DF-31EBB20D9FD9}</t>
+          <t>{2018CEFD-DE71-4360-A7FF-A6765C92FCA5}</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1407</v>
+        <v>1425</v>
       </c>
       <c r="D78" t="n">
-        <v>1411</v>
+        <v>1439</v>
       </c>
       <c r="E78" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>امدح في البتول</t>
+          <t>يا م ر ي م</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{32D40C07-0BD1-438B-B72F-50D1FC539907}</t>
+          <t>{6EFF99AC-BDD5-400B-AD02-BDDD7891E5E3}</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1412</v>
+        <v>1440</v>
       </c>
       <c r="D79" t="n">
-        <v>1435</v>
+        <v>1463</v>
       </c>
       <c r="E79" t="n">
         <v>24</v>
@@ -28725,187 +28978,187 @@
     <row r="80" ht="18.75" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 10</t>
+          <t>يا ابنة داود</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{797B381C-F875-4BB4-8ACB-A5852FFBD8FC}</t>
+          <t>{AC841333-B14A-4205-894D-DA7DF6653E1B}</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1436</v>
+        <v>1464</v>
       </c>
       <c r="D80" t="n">
-        <v>1441</v>
+        <v>1490</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأحد 11-15</t>
+          <t>ثيؤطوكية الأحد 9</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{67866127-A8D5-451C-B0C2-1CE6E6FBCD1F}</t>
+          <t>{45A96BB7-91BA-4E03-AC22-F7E7039923CE}</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1442</v>
+        <v>1491</v>
       </c>
       <c r="D81" t="n">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="E81" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>مديح آدام على ثيؤطوكية يوم الإثنين</t>
+          <t>طرح القطعة ال9</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{26E3A1FA-190A-4FFD-A7B6-55DB4CF37CB7}</t>
+          <t>{1FE88F57-6CDF-4D29-B2DF-31EBB20D9FD9}</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="D82" t="n">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>مديح ثالث على ثيؤطوكية يوم الاثنين</t>
+          <t>امدح في البتول</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{96001EBB-7783-4531-BED2-E8DC45D913A4}</t>
+          <t>{32D40C07-0BD1-438B-B72F-50D1FC539907}</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="D83" t="n">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="E83" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" ht="18.75" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الإثنين</t>
+          <t>ثيؤطوكية الأحد 10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{5022D768-2E12-4BEA-8D76-E3896BD58932}</t>
+          <t>{797B381C-F875-4BB4-8ACB-A5852FFBD8FC}</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="D84" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="E84" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>مديح آدام على ثيئوطوكية يوم الثلاثاء</t>
+          <t>ثيؤطوكية الأحد 11-15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{91C639CD-0839-48C7-93C2-8702F0A3AC85}</t>
+          <t>{67866127-A8D5-451C-B0C2-1CE6E6FBCD1F}</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1567</v>
+        <v>1531</v>
       </c>
       <c r="D85" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="E85" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>مديح ثانى آدام على ثيؤطوكية يوم الثلاثاء</t>
+          <t>مديح آدام على ثيؤطوكية يوم الإثنين</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{D3C67D5B-3D73-4555-B8F4-D8024A8D822D}</t>
+          <t>{26E3A1FA-190A-4FFD-A7B6-55DB4CF37CB7}</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="D86" t="n">
-        <v>1602</v>
+        <v>1593</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" ht="18.75" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الثلاثاء</t>
+          <t>مديح ثالث على ثيؤطوكية يوم الاثنين</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{D1BFEE47-99F3-4046-8C36-B6397205435B}</t>
+          <t>{96001EBB-7783-4531-BED2-E8DC45D913A4}</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1603</v>
+        <v>1594</v>
       </c>
       <c r="D87" t="n">
-        <v>1650</v>
+        <v>1610</v>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" ht="18.75" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الأربعاء</t>
+          <t>ثيؤطوكية الإثنين</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{5AD56D85-2906-43FB-98E9-FB96F1B37293}</t>
+          <t>{5022D768-2E12-4BEA-8D76-E3896BD58932}</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1651</v>
+        <v>1611</v>
       </c>
       <c r="D88" t="n">
-        <v>1695</v>
+        <v>1655</v>
       </c>
       <c r="E88" t="n">
         <v>45</v>
@@ -28914,208 +29167,208 @@
     <row r="89" ht="18.75" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الخميس</t>
+          <t>مديح آدام على ثيئوطوكية يوم الثلاثاء</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{88249BFF-471A-47A1-B7BC-E5A5093EC8D7}</t>
+          <t>{91C639CD-0839-48C7-93C2-8702F0A3AC85}</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1696</v>
+        <v>1656</v>
       </c>
       <c r="D89" t="n">
-        <v>1791</v>
+        <v>1673</v>
       </c>
       <c r="E89" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ثيؤطوكية الجمعة</t>
+          <t>مديح ثانى آدام على ثيؤطوكية يوم الثلاثاء</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{6C9361D4-74F3-4201-B28D-7EB59C9D9A46}</t>
+          <t>{D3C67D5B-3D73-4555-B8F4-D8024A8D822D}</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1792</v>
+        <v>1674</v>
       </c>
       <c r="D90" t="n">
-        <v>1820</v>
+        <v>1691</v>
       </c>
       <c r="E90" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة الأولى</t>
+          <t>ثيؤطوكية الثلاثاء</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{25CBC7C4-A68C-4EBD-B127-98DA707B3413}</t>
+          <t>{D1BFEE47-99F3-4046-8C36-B6397205435B}</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1821</v>
+        <v>1692</v>
       </c>
       <c r="D91" t="n">
-        <v>1824</v>
+        <v>1739</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>تسبحة عشية - التفسير الأول من الرومي</t>
+          <t>ثيؤطوكية الأربعاء</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{36C13920-CFC8-484C-AC5D-4D48D9FF3140}</t>
+          <t>{5AD56D85-2906-43FB-98E9-FB96F1B37293}</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1825</v>
+        <v>1740</v>
       </c>
       <c r="D92" t="n">
-        <v>1831</v>
+        <v>1784</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>تسبحة عشية - التفسير الأول من القبطي المعقب</t>
+          <t>ثيؤطوكية الخميس</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{A4938238-103E-437B-88B4-7C77FC389030}</t>
+          <t>{88249BFF-471A-47A1-B7BC-E5A5093EC8D7}</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1832</v>
+        <v>1785</v>
       </c>
       <c r="D93" t="n">
-        <v>1840</v>
+        <v>1880</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>تسبحة عشية - المديح الأول لأبو السعد الأبوتيجي (من هي تدعى)</t>
+          <t>ثيؤطوكية الجمعة</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{B950C6F8-B998-4CA7-BD10-8101CD9332D8}</t>
+          <t>{6C9361D4-74F3-4201-B28D-7EB59C9D9A46}</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1841</v>
+        <v>1881</v>
       </c>
       <c r="D94" t="n">
-        <v>1843</v>
+        <v>1909</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> تسبحة عشية - المديح الأول للمعلم غبريال (ابدى باسم الله الآب)</t>
+          <t>ثيؤطوكية السبت – القطعة الأولى</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{A8E91968-A3B0-4108-BB66-21EBB72B90AB}</t>
+          <t>{25CBC7C4-A68C-4EBD-B127-98DA707B3413}</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1844</v>
+        <v>1910</v>
       </c>
       <c r="D95" t="n">
-        <v>1849</v>
+        <v>1913</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>تسبحة عشية - المديح الأول للبابا مرقس (أبدى باسم الله القدوس)</t>
+          <t>تسبحة عشية - التفسير الأول من الرومي</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{ADF1D3F0-D45B-4A96-A29B-39F83D7E9EB1}</t>
+          <t>{36C13920-CFC8-484C-AC5D-4D48D9FF3140}</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1850</v>
+        <v>1914</v>
       </c>
       <c r="D96" t="n">
-        <v>1853</v>
+        <v>1920</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة الثانية</t>
+          <t>تسبحة عشية - التفسير الأول من القبطي المعقب</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{8019C8C1-BEEC-40E4-968B-F5ED969AC113}</t>
+          <t>{A4938238-103E-437B-88B4-7C77FC389030}</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1854</v>
+        <v>1921</v>
       </c>
       <c r="D97" t="n">
-        <v>1856</v>
+        <v>1929</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة الثالثة</t>
+          <t>تسبحة عشية - المديح الأول لأبو السعد الأبوتيجي (من هي تدعى)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{CCF45E02-AA14-48CC-8886-031DF1780A0F}</t>
+          <t>{B950C6F8-B998-4CA7-BD10-8101CD9332D8}</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1857</v>
+        <v>1930</v>
       </c>
       <c r="D98" t="n">
-        <v>1859</v>
+        <v>1932</v>
       </c>
       <c r="E98" t="n">
         <v>3</v>
@@ -29124,40 +29377,40 @@
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة الرابعة</t>
+          <t xml:space="preserve"> تسبحة عشية - المديح الأول للمعلم غبريال (ابدى باسم الله الآب)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{19DD8226-67B0-4DB0-87AD-CDDB543FC5C6}</t>
+          <t>{A8E91968-A3B0-4108-BB66-21EBB72B90AB}</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1860</v>
+        <v>1933</v>
       </c>
       <c r="D99" t="n">
-        <v>1863</v>
+        <v>1938</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة الخامسة</t>
+          <t>تسبحة عشية - المديح الأول للبابا مرقس (أبدى باسم الله القدوس)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{3374DF62-0702-4B9C-9F9C-F3376F6F553C}</t>
+          <t>{ADF1D3F0-D45B-4A96-A29B-39F83D7E9EB1}</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1864</v>
+        <v>1939</v>
       </c>
       <c r="D100" t="n">
-        <v>1867</v>
+        <v>1942</v>
       </c>
       <c r="E100" t="n">
         <v>4</v>
@@ -29166,486 +29419,1495 @@
     <row r="101" ht="18.75" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة السادسة</t>
+          <t>ثيؤطوكية السبت – القطعة الثانية</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{99DFC09C-3E76-4286-A09B-64E0E29EFB55}</t>
+          <t>{8019C8C1-BEEC-40E4-968B-F5ED969AC113}</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1868</v>
+        <v>1943</v>
       </c>
       <c r="D101" t="n">
-        <v>1874</v>
+        <v>1945</v>
       </c>
       <c r="E101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" ht="18.75" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة السابعة</t>
+          <t>تسبحة عشية - التفسير الثاني من الرومي</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{84ED3472-EA03-4F72-BCB9-C4B4E3C3ACAB}</t>
+          <t>{9F9619E3-02E7-4C6C-9336-A15D581F2BB2}</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1875</v>
+        <v>1946</v>
       </c>
       <c r="D102" t="n">
-        <v>1877</v>
+        <v>1953</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" ht="18.75" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة الثامنة</t>
+          <t>تسبحة عشية - التفسير الثاني من القبطي المعقب</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{8EB0D94B-79DF-42B7-AB9C-7C2ECD0EE72D}</t>
+          <t>{C8646E49-D785-4E6C-9789-6F575016815F}</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1878</v>
+        <v>1954</v>
       </c>
       <c r="D103" t="n">
-        <v>1882</v>
+        <v>1963</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" ht="18.75" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ثيؤطوكية السبت – القطعة التاسعة</t>
+          <t>تسبحة عشية - المديح الثاني لأبو السعد الأبوتيجي (انا أفتح بالأمثال)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{B70FE0F4-C36A-4BB1-B317-D349CEE80ADE}</t>
+          <t>{FC6C8E4E-C009-4F2D-8755-1D6C3A6517C0}</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1883</v>
+        <v>1964</v>
       </c>
       <c r="D104" t="n">
-        <v>1886</v>
+        <v>1966</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" ht="18.75" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>لبش الإثنين</t>
+          <t xml:space="preserve"> تسبحة عشية - المديح الثاني للمعلم غبريال (تعظمك كل الطغمات)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{B08DAA27-DC93-470F-8EE4-DBA2CDED73FF}</t>
+          <t>{DEA60FC4-A401-48EC-AAA6-D362D85C0F33}</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1887</v>
+        <v>1967</v>
       </c>
       <c r="D105" t="n">
-        <v>1898</v>
+        <v>1972</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" ht="18.75" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>لبش الثلاثاء</t>
+          <t>تسبحة عشية - المديح الثاني للبابا مرقس (تعظمكِ كل الطغمات)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{EA64C1D5-8011-4ED1-AECA-ACA0D1D96925}</t>
+          <t>{21C5B8C3-2132-4D67-93A5-9D7EF7BEDB78}</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1899</v>
+        <v>1973</v>
       </c>
       <c r="D106" t="n">
-        <v>1907</v>
+        <v>1976</v>
       </c>
       <c r="E106" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" ht="18.75" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>لبش الأربعاء</t>
+          <t>ثيؤطوكية السبت – القطعة الثالثة</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{824D594F-C079-4552-882A-CC297F319D7D}</t>
+          <t>{CCF45E02-AA14-48CC-8886-031DF1780A0F}</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1908</v>
+        <v>1977</v>
       </c>
       <c r="D107" t="n">
-        <v>1922</v>
+        <v>1979</v>
       </c>
       <c r="E107" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" ht="18.75" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>لبش الخميس</t>
+          <t>تسبحة عشية - التفسير الثالث من الرومي</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{260E1FAC-A9F6-4E94-BAAB-EFD045CD242D}</t>
+          <t>{E0E9E346-0244-4A7C-B46F-9DF6C1596578}</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1923</v>
+        <v>1980</v>
       </c>
       <c r="D108" t="n">
-        <v>1939</v>
+        <v>1986</v>
       </c>
       <c r="E108" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>لبش الجمعة</t>
+          <t>تسبحة عشية - التفسير الثالث من القبطي المعقب</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{27A6E4EC-9C9A-4029-8EAF-A984FA647997}</t>
+          <t>{6644C05D-E826-4306-926C-DA6B46EDC3F5}</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1940</v>
+        <v>1987</v>
       </c>
       <c r="D109" t="n">
-        <v>1959</v>
+        <v>1994</v>
       </c>
       <c r="E109" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>شيرات السبت 1</t>
+          <t>تسبحة عشية - المديح الثالث لأبو السعد الأبوتيجي (مثل عروس بغير فساد)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{FA5AF629-FC64-4123-92EA-193DFE2229CC}</t>
+          <t>{BF9BA356-CCD2-4944-857F-0AD39CDDD702}</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1960</v>
+        <v>1995</v>
       </c>
       <c r="D110" t="n">
-        <v>1971</v>
+        <v>1997</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
+          <t>تسبحة عشية - المديح الثالث للمعلم غبريال (مثل عروس مختارة)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>{A0A64BE2-2FA2-4724-B72B-F2514028CE81}</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E111" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" ht="18.75" customHeight="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الثالث للبابا مرقس (صرت عروسة)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>{276FA185-6B86-460F-9D24-33C039B4056F}</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" ht="18.75" customHeight="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ثيؤطوكية السبت – القطعة الرابعة</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{19DD8226-67B0-4DB0-87AD-CDDB543FC5C6}</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" ht="18.75" customHeight="1">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير الرابع من الرومي</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>{8602D0D9-75CF-4EB8-9254-91151FE7FA72}</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E114" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" ht="18.75" customHeight="1">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير الرابع من القبطي المعقب</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>{85D9AB84-85AC-49F9-AE41-6E2DFA9C958F}</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E115" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" ht="18.75" customHeight="1">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الرابع لأبو السعد الأبوتيجي (أنت هي الجنس المعروف)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>{A7ACE94B-3F37-475C-BF03-F22718E4BF96}</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" ht="18.75" customHeight="1">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الرابع للمعلم غبريال (يا نسل مُكرم مختار)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>{E392047A-D471-4E1A-BF24-A626B29E3FA4}</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2031</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E117" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" ht="18.75" customHeight="1">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الرابع للبابا مرقس (أنت هي الجنس المختار)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>{278DE864-93F5-46B0-897D-A372B149AA0D}</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E118" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" ht="18.75" customHeight="1">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ثيؤطوكية السبت – القطعة الخامسة</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>{3374DF62-0702-4B9C-9F9C-F3376F6F553C}</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2042</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" ht="18.75" customHeight="1">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير الخامس من الرومي</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>{2A47E05F-7A8A-4EAE-868D-AD569618A18D}</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2046</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2052</v>
+      </c>
+      <c r="E120" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" ht="18.75" customHeight="1">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير الخامس من القبطي المعقب</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>{9223A262-9D6B-4995-A703-C5F20465AE57}</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2053</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2060</v>
+      </c>
+      <c r="E121" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" ht="18.75" customHeight="1">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الخامس لأبو السعد الأبوتيجي (السماء الثانية التي صارت)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>{230AA550-627E-452E-A6D8-161CA4934646}</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2061</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2063</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" ht="18.75" customHeight="1">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الخامس للمعلم غبريال (سماء ثانية جسدانية)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>{442C18F0-59B3-4BC2-A02C-AFBB93B810D1}</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2064</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2069</v>
+      </c>
+      <c r="E123" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" ht="18.75" customHeight="1">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الخامس للبابا مرقس (صرت سماء حقاً ثاني)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>{C16B2C70-B5AA-4D2B-A29B-14FEC378DE5B}</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2070</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2073</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" ht="18.75" customHeight="1">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ثيؤطوكية السبت – القطعة السادسة</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>{99DFC09C-3E76-4286-A09B-64E0E29EFB55}</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2074</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2080</v>
+      </c>
+      <c r="E125" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" ht="18.75" customHeight="1">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير السادس من الرومي</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>{4CC385F9-FD0B-442A-90BE-F003F9B58FE5}</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2081</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2087</v>
+      </c>
+      <c r="E126" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" ht="18.75" customHeight="1">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير السادس من القبطي المعقب</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>{D2951CB1-14A0-4C13-9BD8-17AFD996D685}</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2088</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2095</v>
+      </c>
+      <c r="E127" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" ht="18.75" customHeight="1">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح السادس لأبو السعد الأبوتيجي (القبة وأوانيها)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>{A0E4502F-9D07-43A2-A23B-D9AE4B6886BD}</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2096</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2098</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" ht="18.75" customHeight="1">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح السادس للمعلم غبريال (القبة المصنوعة)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>{440EF90E-601C-47D2-8F9B-41FA2D71A193}</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2099</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2104</v>
+      </c>
+      <c r="E129" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" ht="18.75" customHeight="1">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح السادس للبابا مرقس (القبة النبوية)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>{1228179F-A557-40AA-A2DC-82F35609F0DB}</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2105</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2108</v>
+      </c>
+      <c r="E130" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" ht="18.75" customHeight="1">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ثيؤطوكية السبت – القطعة السابعة</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>{84ED3472-EA03-4F72-BCB9-C4B4E3C3ACAB}</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2109</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2111</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" ht="18.75" customHeight="1">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير السابع من الرومي</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>{509AB624-F789-42CF-BBFF-85F10A8A2145}</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2112</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2118</v>
+      </c>
+      <c r="E132" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" ht="18.75" customHeight="1">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير السابع من القبطي المعقب</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>{EF820484-6F6F-4794-B620-50B5B695D73F}</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2119</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2126</v>
+      </c>
+      <c r="E133" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" ht="18.75" customHeight="1">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح السابع لأبو السعد الأبوتيجي (دُعيتِ أم الله وأي)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>{D32F0674-066D-4E24-9FDA-726924C66FEB}</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2127</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2129</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" ht="18.75" customHeight="1">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح السابع للمعلم غبريال (دُعيتِ أمًا لمن أنشاكِ)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>{A649486F-6A0C-4A3A-9107-929278AE24B5}</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2130</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2135</v>
+      </c>
+      <c r="E135" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" ht="18.75" customHeight="1">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح السابع للبابا مرقس (دُعيتِ أم الله خالقنا)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>{3DD40A56-AF52-4907-A428-A428C8731C76}</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2136</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2139</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" ht="18.75" customHeight="1">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ثيؤطوكية السبت – القطعة الثامنة</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>{8EB0D94B-79DF-42B7-AB9C-7C2ECD0EE72D}</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2144</v>
+      </c>
+      <c r="E137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" ht="18.75" customHeight="1">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير الثامن من الرومي</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>{3604EEB2-A087-46E9-8FA2-AEBF6D5EE0FB}</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2151</v>
+      </c>
+      <c r="E138" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" ht="18.75" customHeight="1">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير الثامن من القبطي المعقب</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>{8FD18F4B-9546-49F5-AA68-3A72BB2C5BE1}</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2152</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2160</v>
+      </c>
+      <c r="E139" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" ht="18.75" customHeight="1">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الثامن لأبو السعد الأبوتيجي (سلم رآه الآب يعقوب)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>{5E27A34A-8B77-42EC-A5D8-A8D7D7773FA5}</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2161</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2163</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" ht="18.75" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الثامن للمعلم غبريال (بمن أشبِّهكِ)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>{E2A803B1-215E-4DA7-B41B-872E7F05BD53}</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2164</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2169</v>
+      </c>
+      <c r="E141" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" ht="18.75" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح الثامن للبابا مرقس (سلم رآه الآب يعقوب)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>{F7F58D71-7B9A-4CBB-8252-99621A744687}</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2170</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2173</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" ht="18.75" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ثيؤطوكية السبت – القطعة التاسعة</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>{B70FE0F4-C36A-4BB1-B317-D349CEE80ADE}</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2174</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2177</v>
+      </c>
+      <c r="E143" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" ht="18.75" customHeight="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير التاسع من الرومي</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>{48506622-5B60-4368-BC4C-E9E7A0C4A544}</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2178</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2184</v>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" ht="18.75" customHeight="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - التفسير التاسع من القبطي المعقب</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>{8075DC79-158E-4D24-A697-B645ACEA5B9A}</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2191</v>
+      </c>
+      <c r="E145" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" ht="18.75" customHeight="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح التاسع لأبو السعد الأبوتيجي (هوذا الرب أتي منكِ)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>{FE11E60B-02A8-487F-BE56-B23920D75868}</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2192</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2194</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" ht="18.75" customHeight="1">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح التاسع للمعلم غبريال (هوذا الرب شاء وأحب)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>{A6B18C6E-604E-4D90-9664-3637DDF1DDF8}</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2201</v>
+      </c>
+      <c r="E147" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" ht="18.75" customHeight="1">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - المديح التاسع للبابا مرقس (هوذا الرب ظهر منك)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>{133CE765-593B-4B0F-8738-AC478CEBE541}</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2202</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2205</v>
+      </c>
+      <c r="E148" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" ht="18.75" customHeight="1">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>لبش الإثنين</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>{B08DAA27-DC93-470F-8EE4-DBA2CDED73FF}</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2206</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2217</v>
+      </c>
+      <c r="E149" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" ht="19.5" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>لبش الثلاثاء</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>{EA64C1D5-8011-4ED1-AECA-ACA0D1D96925}</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2218</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2226</v>
+      </c>
+      <c r="E150" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" ht="19.5" customHeight="1">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>لبش الأربعاء</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>{824D594F-C079-4552-882A-CC297F319D7D}</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2227</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2241</v>
+      </c>
+      <c r="E151" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" ht="19.5" customHeight="1">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>لبش الخميس</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>{260E1FAC-A9F6-4E94-BAAB-EFD045CD242D}</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2242</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2258</v>
+      </c>
+      <c r="E152" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>لبش الجمعة</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>{27A6E4EC-9C9A-4029-8EAF-A984FA647997}</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2259</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2278</v>
+      </c>
+      <c r="E153" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" ht="19.5" customHeight="1">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>شيرات السبت 1</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>{FA5AF629-FC64-4123-92EA-193DFE2229CC}</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2279</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2290</v>
+      </c>
+      <c r="E154" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" ht="19.5" customHeight="1">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>شيرات السبت 2</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>{2DF7B6FE-B056-4813-B72C-DFE470371815}</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>1972</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1987</v>
-      </c>
-      <c r="E111" t="n">
+      <c r="C155" t="n">
+        <v>2291</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2306</v>
+      </c>
+      <c r="E155" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="A156" t="inlineStr">
         <is>
           <t>طرح الفعلة القديسين</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>{2F0308A9-655B-409C-903E-7217C5A6FD57}</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>1988</v>
-      </c>
-      <c r="D112" t="n">
-        <v>1993</v>
-      </c>
-      <c r="E112" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="C156" t="n">
+        <v>2307</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2311</v>
+      </c>
+      <c r="E156" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" ht="19.5" customHeight="1">
+      <c r="A157" t="inlineStr">
         <is>
           <t>لحن ختام طرح الفعلة</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>{19A786C6-3975-4152-8E20-4A058B9E2BAA}</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>1994</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1994</v>
-      </c>
-      <c r="E113" t="n">
+      <c r="C157" t="n">
+        <v>2312</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2312</v>
+      </c>
+      <c r="E157" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>مقدمة الدفنار</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>{DBBEB49F-3396-41D0-81FF-0A028C3CB4DA}</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>1995</v>
-      </c>
-      <c r="D114" t="n">
-        <v>1995</v>
-      </c>
-      <c r="E114" t="n">
+    <row r="158" ht="19.5" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>مقدمة الدفنار والطرح الآدام</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>{0420AA0C-B21A-478D-88EA-8378E9539EDE}</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2313</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2316</v>
+      </c>
+      <c r="E158" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" ht="19.5" customHeight="1">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>مقدمة الدفنار والطرح الواطس</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>{F2541D73-C210-4196-BE50-DF6E6142A86C}</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2317</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E159" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" ht="19.5" customHeight="1">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>الدفنار</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>{A509B738-02BB-455A-944E-9E56D85C8942}</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>2321</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2321</v>
+      </c>
+      <c r="E160" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>مقدمة الدفنار الآدام</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>{0420AA0C-B21A-478D-88EA-8378E9539EDE}</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>1996</v>
-      </c>
-      <c r="D115" t="n">
-        <v>1999</v>
-      </c>
-      <c r="E115" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>مقدمة الدفنار الواطس</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>{F2541D73-C210-4196-BE50-DF6E6142A86C}</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D116" t="n">
-        <v>2003</v>
-      </c>
-      <c r="E116" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>الدفنار</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>{A509B738-02BB-455A-944E-9E56D85C8942}</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>2004</v>
-      </c>
-      <c r="D117" t="n">
-        <v>2005</v>
-      </c>
-      <c r="E117" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="161" ht="19.5" customHeight="1">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ختام الثيؤطوكيات</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>{1B7589F7-B83E-4575-B202-AFD46AB5081F}</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2322</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2322</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
+      <c r="A162" t="inlineStr">
         <is>
           <t>مديح مراحمك يا إلهي</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>{B589BFA4-6FB5-43EB-90E4-CCBE0D4ADF21}</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>2006</v>
-      </c>
-      <c r="D118" t="n">
-        <v>2013</v>
-      </c>
-      <c r="E118" t="n">
+      <c r="C162" t="n">
+        <v>2323</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E162" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="163" ht="19.5" customHeight="1">
+      <c r="A163" t="inlineStr">
         <is>
           <t>ختام الثؤطوكيات الادام</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>{14A3A43C-A9F7-45A8-A510-EE3F33D99572}</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>2014</v>
-      </c>
-      <c r="D119" t="n">
-        <v>2030</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="C163" t="n">
+        <v>2331</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2347</v>
+      </c>
+      <c r="E163" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="164" ht="19.5" customHeight="1">
+      <c r="A164" t="inlineStr">
         <is>
           <t>ختام الثيؤطوكيات الواطس</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>{BF439D71-64D1-4376-8E4A-812437425EBB}</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D120" t="n">
-        <v>2050</v>
-      </c>
-      <c r="E120" t="n">
+      <c r="C164" t="n">
+        <v>2348</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2367</v>
+      </c>
+      <c r="E164" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="A165" t="inlineStr">
         <is>
           <t>قانون الايمان</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>{A12368B5-4E89-4682-AF79-DC1979BA120B}</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>2051</v>
-      </c>
-      <c r="D121" t="n">
-        <v>2059</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="C165" t="n">
+        <v>2368</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2376</v>
+      </c>
+      <c r="E165" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="166" ht="19.5" customHeight="1">
+      <c r="A166" t="inlineStr">
         <is>
           <t>ختام التسبحة</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>{BABBF91F-DC4B-4DBC-A6C1-054AEA7290F3}</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>2060</v>
-      </c>
-      <c r="D122" t="n">
-        <v>2074</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="C166" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2391</v>
+      </c>
+      <c r="E166" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="167" ht="19.5" customHeight="1">
+      <c r="A167" t="inlineStr">
         <is>
           <t>قدوس قدوس قدوس</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>{F2F363F3-5DD8-474B-94A0-6895758AB76D}</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>2075</v>
-      </c>
-      <c r="D123" t="n">
-        <v>2079</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="C167" t="n">
+        <v>2392</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E167" t="n">
         <v>5</v>
       </c>
     </row>
+    <row r="168" ht="19.5" customHeight="1">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - طرح الأحد الأول</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>{61D3DBD3-6C8F-47D9-AD64-BC1E7C227747}</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2397</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2410</v>
+      </c>
+      <c r="E168" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" ht="19.5" customHeight="1">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - طرح الأحد الثاني</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>{E547F89F-E66E-4E8C-9F82-10A0896D784A}</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2411</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2423</v>
+      </c>
+      <c r="E169" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" ht="19.5" customHeight="1">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - طرح الأحد الثالث</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>{A7C1A333-7A01-4371-849F-C187F9577916}</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>2424</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2434</v>
+      </c>
+      <c r="E170" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>تسبحة عشية - طرح الأحد الرابع</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>{D60C22F6-03D6-428B-A7F9-EFF9C3530875}</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2447</v>
+      </c>
+      <c r="E171" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" ht="19.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Files Data.xlsx
+++ b/Files Data.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E484"/>
+  <dimension ref="A1:E485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="59.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -10119,10 +10119,10 @@
         <v>2998</v>
       </c>
       <c r="D459" t="n">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="E459" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="460" ht="18.75" customHeight="1">
@@ -10137,115 +10137,115 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="D460" t="n">
-        <v>3049</v>
+        <v>3051</v>
       </c>
       <c r="E460" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="461" ht="18.75" customHeight="1">
       <c r="A461" t="inlineStr">
         <is>
-          <t>يونا بى ابروفيتيس</t>
+          <t>استر ماجي</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>{859D33B0-D7E3-4EDC-8AB9-E56533A2D980}</t>
+          <t>{224CCBC0-10D1-4FE6-900A-04D5BF9A2756}</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>3050</v>
+        <v>3052</v>
       </c>
       <c r="D461" t="n">
-        <v>3065</v>
+        <v>3055</v>
       </c>
       <c r="E461" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="462" ht="18.75" customHeight="1">
       <c r="A462" t="inlineStr">
         <is>
-          <t>بي ماي رومي</t>
+          <t>يونا بى ابروفيتيس</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>{315091E2-E367-43B7-A35E-4175DF947038}</t>
+          <t>{859D33B0-D7E3-4EDC-8AB9-E56533A2D980}</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>3066</v>
+        <v>3056</v>
       </c>
       <c r="D462" t="n">
-        <v>3080</v>
+        <v>3071</v>
       </c>
       <c r="E462" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="463" ht="18.75" customHeight="1">
       <c r="A463" t="inlineStr">
         <is>
-          <t>اونيشتي اميستيريون</t>
+          <t>بي ماي رومي</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>{DB680029-4B05-4C3F-98B3-FB5469AADBD7}</t>
+          <t>{315091E2-E367-43B7-A35E-4175DF947038}</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>3081</v>
+        <v>3072</v>
       </c>
       <c r="D463" t="n">
-        <v>3100</v>
+        <v>3086</v>
       </c>
       <c r="E463" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="464" ht="18.75" customHeight="1">
       <c r="A464" t="inlineStr">
         <is>
-          <t>مدائح سنوي</t>
+          <t>اونيشتي اميستيريون</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>{07298C47-E831-4285-ACB7-25BB3772C6A2}</t>
+          <t>{DB680029-4B05-4C3F-98B3-FB5469AADBD7}</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>3101</v>
+        <v>3087</v>
       </c>
       <c r="D464" t="n">
-        <v>3101</v>
+        <v>3106</v>
       </c>
       <c r="E464" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="465" ht="18.75" customHeight="1">
       <c r="A465" t="inlineStr">
         <is>
-          <t>مدائح النيروز</t>
+          <t>مدائح سنوي</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>{61C536ED-3B9E-4448-A01E-0EE67B371A03}</t>
+          <t>{07298C47-E831-4285-ACB7-25BB3772C6A2}</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>3102</v>
+        <v>3107</v>
       </c>
       <c r="D465" t="n">
-        <v>3102</v>
+        <v>3107</v>
       </c>
       <c r="E465" t="n">
         <v>1</v>
@@ -10254,19 +10254,19 @@
     <row r="466" ht="18.75" customHeight="1">
       <c r="A466" t="inlineStr">
         <is>
-          <t>مدائح كيهك</t>
+          <t>مدائح النيروز</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>{DCEAD1F4-0405-4EE6-9905-219FC8E85798}</t>
+          <t>{61C536ED-3B9E-4448-A01E-0EE67B371A03}</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>3103</v>
+        <v>3108</v>
       </c>
       <c r="D466" t="n">
-        <v>3103</v>
+        <v>3108</v>
       </c>
       <c r="E466" t="n">
         <v>1</v>
@@ -10275,19 +10275,19 @@
     <row r="467" ht="18.75" customHeight="1">
       <c r="A467" t="inlineStr">
         <is>
-          <t>مدائح الميلاد</t>
+          <t>مدائح كيهك</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>{42181297-997B-4C4C-B43B-4E9D8A23858D}</t>
+          <t>{DCEAD1F4-0405-4EE6-9905-219FC8E85798}</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>3104</v>
+        <v>3109</v>
       </c>
       <c r="D467" t="n">
-        <v>3104</v>
+        <v>3109</v>
       </c>
       <c r="E467" t="n">
         <v>1</v>
@@ -10296,19 +10296,19 @@
     <row r="468" ht="18.75" customHeight="1">
       <c r="A468" t="inlineStr">
         <is>
-          <t>مدائح صوم نينوى</t>
+          <t>مدائح الميلاد</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>{43C9AE43-EC80-4A72-97F0-F38A712DDA09}</t>
+          <t>{42181297-997B-4C4C-B43B-4E9D8A23858D}</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>3105</v>
+        <v>3110</v>
       </c>
       <c r="D468" t="n">
-        <v>3105</v>
+        <v>3110</v>
       </c>
       <c r="E468" t="n">
         <v>1</v>
@@ -10317,19 +10317,19 @@
     <row r="469" ht="18.75" customHeight="1">
       <c r="A469" t="inlineStr">
         <is>
-          <t>مدائح الصوم الكبير</t>
+          <t>مدائح صوم نينوى</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>{6C210ECD-CC91-4984-B251-46939B2A0039}</t>
+          <t>{43C9AE43-EC80-4A72-97F0-F38A712DDA09}</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>3106</v>
+        <v>3111</v>
       </c>
       <c r="D469" t="n">
-        <v>3106</v>
+        <v>3111</v>
       </c>
       <c r="E469" t="n">
         <v>1</v>
@@ -10338,19 +10338,19 @@
     <row r="470" ht="18.75" customHeight="1">
       <c r="A470" t="inlineStr">
         <is>
-          <t>مدائح سبت لعازر</t>
+          <t>مدائح الصوم الكبير</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>{DB6B4ECA-F770-40E7-A7BA-46A8B5B46C3B}</t>
+          <t>{6C210ECD-CC91-4984-B251-46939B2A0039}</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>3107</v>
+        <v>3112</v>
       </c>
       <c r="D470" t="n">
-        <v>3107</v>
+        <v>3112</v>
       </c>
       <c r="E470" t="n">
         <v>1</v>
@@ -10359,19 +10359,19 @@
     <row r="471" ht="18.75" customHeight="1">
       <c r="A471" t="inlineStr">
         <is>
-          <t>مدائح احد الشعانين</t>
+          <t>مدائح سبت لعازر</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>{37DC4920-98DA-477A-A6F7-6D252B149A22}</t>
+          <t>{DB6B4ECA-F770-40E7-A7BA-46A8B5B46C3B}</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>3108</v>
+        <v>3113</v>
       </c>
       <c r="D471" t="n">
-        <v>3108</v>
+        <v>3113</v>
       </c>
       <c r="E471" t="n">
         <v>1</v>
@@ -10380,19 +10380,19 @@
     <row r="472" ht="18.75" customHeight="1">
       <c r="A472" t="inlineStr">
         <is>
-          <t>مدائح القيامة</t>
+          <t>مدائح احد الشعانين</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>{1D781881-AD2E-41FE-97D4-458A86F892F1}</t>
+          <t>{37DC4920-98DA-477A-A6F7-6D252B149A22}</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>3109</v>
+        <v>3114</v>
       </c>
       <c r="D472" t="n">
-        <v>3109</v>
+        <v>3114</v>
       </c>
       <c r="E472" t="n">
         <v>1</v>
@@ -10401,19 +10401,19 @@
     <row r="473" ht="18.75" customHeight="1">
       <c r="A473" t="inlineStr">
         <is>
-          <t>مدائح الخماسين من 2 الى 39</t>
+          <t>مدائح القيامة</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>{F74608AC-8E8B-460A-97E7-1E6B86D50B5B}</t>
+          <t>{1D781881-AD2E-41FE-97D4-458A86F892F1}</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>3110</v>
+        <v>3115</v>
       </c>
       <c r="D473" t="n">
-        <v>3110</v>
+        <v>3115</v>
       </c>
       <c r="E473" t="n">
         <v>1</v>
@@ -10422,19 +10422,19 @@
     <row r="474" ht="18.75" customHeight="1">
       <c r="A474" t="inlineStr">
         <is>
-          <t>مدائح الصعود الى العنصرة</t>
+          <t>مدائح الخماسين من 2 الى 39</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>{BAAC56F0-C9A0-4321-AB43-D79F5FCE37C9}</t>
+          <t>{F74608AC-8E8B-460A-97E7-1E6B86D50B5B}</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>3111</v>
+        <v>3116</v>
       </c>
       <c r="D474" t="n">
-        <v>3111</v>
+        <v>3116</v>
       </c>
       <c r="E474" t="n">
         <v>1</v>
@@ -10443,19 +10443,19 @@
     <row r="475" ht="18.75" customHeight="1">
       <c r="A475" t="inlineStr">
         <is>
-          <t>مدائح صوم الرسل</t>
+          <t>مدائح الصعود الى العنصرة</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>{5F05D018-CCA5-41B9-A869-A1F64A0C2BCC}</t>
+          <t>{BAAC56F0-C9A0-4321-AB43-D79F5FCE37C9}</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>3112</v>
+        <v>3117</v>
       </c>
       <c r="D475" t="n">
-        <v>3112</v>
+        <v>3117</v>
       </c>
       <c r="E475" t="n">
         <v>1</v>
@@ -10464,19 +10464,19 @@
     <row r="476" ht="18.75" customHeight="1">
       <c r="A476" t="inlineStr">
         <is>
-          <t>مدائح الاعياد السيدية</t>
+          <t>مدائح صوم الرسل</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>{147FD013-1F73-40AC-92A0-5544B48FA888}</t>
+          <t>{5F05D018-CCA5-41B9-A869-A1F64A0C2BCC}</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>3113</v>
+        <v>3118</v>
       </c>
       <c r="D476" t="n">
-        <v>3113</v>
+        <v>3118</v>
       </c>
       <c r="E476" t="n">
         <v>1</v>
@@ -10485,19 +10485,19 @@
     <row r="477" ht="18.75" customHeight="1">
       <c r="A477" t="inlineStr">
         <is>
-          <t>مدائح ال29 من الشهر</t>
+          <t>مدائح الاعياد السيدية</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>{3BE1A381-B11E-4562-921A-ECB2221D0A43}</t>
+          <t>{147FD013-1F73-40AC-92A0-5544B48FA888}</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>3114</v>
+        <v>3119</v>
       </c>
       <c r="D477" t="n">
-        <v>3114</v>
+        <v>3119</v>
       </c>
       <c r="E477" t="n">
         <v>1</v>
@@ -10506,147 +10506,168 @@
     <row r="478" ht="18.75" customHeight="1">
       <c r="A478" t="inlineStr">
         <is>
-          <t>ابؤرو للتوزيع</t>
+          <t>مدائح ال29 من الشهر</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>{7007E16E-5DD0-4268-A326-25AF88EA4DE9}</t>
+          <t>{3BE1A381-B11E-4562-921A-ECB2221D0A43}</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>3115</v>
+        <v>3120</v>
       </c>
       <c r="D478" t="n">
-        <v>3125</v>
+        <v>3120</v>
       </c>
       <c r="E478" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479" ht="18.75" customHeight="1">
       <c r="A479" t="inlineStr">
         <is>
-          <t>الختام</t>
+          <t>ابؤرو للتوزيع</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>{90F50AB7-3911-445D-9C45-41866ECCCED0}</t>
+          <t>{7007E16E-5DD0-4268-A326-25AF88EA4DE9}</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>3126</v>
+        <v>3121</v>
       </c>
       <c r="D479" t="n">
-        <v>3126</v>
+        <v>3131</v>
       </c>
       <c r="E479" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="480" ht="18.75" customHeight="1">
       <c r="A480" t="inlineStr">
         <is>
-          <t>الختام السنوي</t>
+          <t>الختام</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>{0D2A50D9-F484-4E60-922B-66FF81444E2C}</t>
+          <t>{90F50AB7-3911-445D-9C45-41866ECCCED0}</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>3127</v>
+        <v>3132</v>
       </c>
       <c r="D480" t="n">
-        <v>3129</v>
+        <v>3132</v>
       </c>
       <c r="E480" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481" ht="18.75" customHeight="1">
       <c r="A481" t="inlineStr">
         <is>
-          <t>الختام في الصوم المقدس</t>
+          <t>الختام السنوي</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>{4A3AE26D-6D71-4143-8C05-7618E08EF248}</t>
+          <t>{0D2A50D9-F484-4E60-922B-66FF81444E2C}</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>3130</v>
+        <v>3133</v>
       </c>
       <c r="D481" t="n">
         <v>3135</v>
       </c>
       <c r="E481" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482" ht="18.75" customHeight="1">
       <c r="A482" t="inlineStr">
         <is>
-          <t>تكملة على حسب المناسبة</t>
+          <t>الختام في الصوم المقدس</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>{A18EDC94-F257-4FAC-99C7-0A8EA70F0FAF}</t>
+          <t>{4A3AE26D-6D71-4143-8C05-7618E08EF248}</t>
         </is>
       </c>
       <c r="C482" t="n">
         <v>3136</v>
       </c>
       <c r="D482" t="n">
-        <v>3160</v>
+        <v>3141</v>
       </c>
       <c r="E482" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="483" ht="18.75" customHeight="1">
       <c r="A483" t="inlineStr">
         <is>
-          <t>في حضور الاسقف</t>
+          <t>تكملة على حسب المناسبة</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>{A9183893-7B7E-459F-8547-F7A8F7D2D521}</t>
+          <t>{A18EDC94-F257-4FAC-99C7-0A8EA70F0FAF}</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>3161</v>
+        <v>3142</v>
       </c>
       <c r="D483" t="n">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="E483" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="484" ht="18.75" customHeight="1">
       <c r="A484" t="inlineStr">
         <is>
+          <t>في حضور الاسقف</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>{A9183893-7B7E-459F-8547-F7A8F7D2D521}</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>3167</v>
+      </c>
+      <c r="D484" t="n">
+        <v>3175</v>
+      </c>
+      <c r="E484" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
           <t>الختام 2</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>{A3DED752-5159-4F64-86F6-7B95F37A8327}</t>
         </is>
       </c>
-      <c r="C484" t="n">
-        <v>3170</v>
-      </c>
-      <c r="D484" t="n">
-        <v>3174</v>
-      </c>
-      <c r="E484" t="n">
+      <c r="C485" t="n">
+        <v>3176</v>
+      </c>
+      <c r="D485" t="n">
+        <v>3180</v>
+      </c>
+      <c r="E485" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10661,7 +10682,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="41.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -11016,12 +11037,12 @@
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>(الميلاد) أنا افتح فاي بمجد الله</t>
+          <t>(الميلاد) مديح عشية - أبدأ باسم الله القدوس</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{99CFF969-C99E-48F8-A8E9-E208BA5E4210}</t>
+          <t>{27A6321C-5645-4ABC-BC4F-6253849FA217}</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -11037,796 +11058,796 @@
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>(تذكار الاعياد السيدية) المجد للآب خالقنا</t>
+          <t>(الميلاد) قطع باكر - الله الحي المتعالى</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{A11F2970-128A-421A-92A7-78C73AEA4270}</t>
+          <t>{D04503D9-2941-4E17-A74A-8D581A1CCF25}</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>438</v>
       </c>
       <c r="D18" t="n">
-        <v>453</v>
+        <v>499</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(صوم نينوى) الصوم الصوم للنفس ثبات</t>
+          <t>(الميلاد) أنا افتح فاي بمجد الله</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{22B730C4-9A84-4D38-B8FD-3409EF83C4BD}</t>
+          <t>{99CFF969-C99E-48F8-A8E9-E208BA5E4210}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="D19" t="n">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="E19" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الاول - الصوم الصوم للنفس ثبات</t>
+          <t>(تذكار الاعياد السيدية) المجد للآب خالقنا</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{19C963C1-49D7-4905-842B-977245127917}</t>
+          <t>{A11F2970-128A-421A-92A7-78C73AEA4270}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D20" t="n">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الثاني - سر عجيب هو سر المسيح</t>
+          <t>(صوم نينوى) الصوم الصوم للنفس ثبات</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{4A2CC73C-A3C7-45E5-9BFE-FBC538653C4B}</t>
+          <t>{22B730C4-9A84-4D38-B8FD-3409EF83C4BD}</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="D21" t="n">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الثالث - الصوم هو حصن غير مهدوم</t>
+          <t>(الصوم الكبير) الاسبوع الاول - الصوم الصوم للنفس ثبات</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{4CDA093F-DDF6-4FED-8316-8CFC4A383925}</t>
+          <t>{19C963C1-49D7-4905-842B-977245127917}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="D22" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع الرابع - الصوم هو حصن غير مهدوم</t>
+          <t>(الصوم الكبير) الاسبوع الثاني - سر عجيب هو سر المسيح</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{FE32734F-5C08-4A79-BCCD-16672ABB653D}</t>
+          <t>{4A2CC73C-A3C7-45E5-9BFE-FBC538653C4B}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D23" t="n">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(الصوم الكبير) الاسبوع السابع و ختام الصوم ـ الصوم الصوم يا شعب يسوع</t>
+          <t>(الصوم الكبير) الاسبوع الثالث - الصوم هو حصن غير مهدوم</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{3DD0F949-75DE-4846-840E-7878908DF90E}</t>
+          <t>{4CDA093F-DDF6-4FED-8316-8CFC4A383925}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="D24" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E24" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(احد الشعانين) اليومَ تمت الأقوال</t>
+          <t>(الصوم الكبير) الاسبوع الرابع - الصوم هو حصن غير مهدوم</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{51A8EA9C-25BB-445D-B0EF-E66FBADDBE1A}</t>
+          <t>{FE32734F-5C08-4A79-BCCD-16672ABB653D}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D25" t="n">
-        <v>732</v>
+        <v>759</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(احد الشعانين) الجالس فوق الشاروبيم</t>
+          <t>(الصوم الكبير) الاسبوع السابع و ختام الصوم ـ الصوم الصوم يا شعب يسوع</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{2E674F43-188F-46C4-B421-E7ADF4DB57C7}</t>
+          <t>{3DD0F949-75DE-4846-840E-7878908DF90E}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="D26" t="n">
-        <v>749</v>
+        <v>810</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>(احد الشعانين) المجد لله الأوحد</t>
+          <t>(احد الشعانين) اليومَ تمت الأقوال</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{D5D7C4B4-CC66-4076-8A09-DFD723D50F03}</t>
+          <t>{51A8EA9C-25BB-445D-B0EF-E66FBADDBE1A}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>750</v>
+        <v>811</v>
       </c>
       <c r="D27" t="n">
-        <v>792</v>
+        <v>825</v>
       </c>
       <c r="E27" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>(احد الشعانين) أوصنا يا ابن داود</t>
+          <t>(احد الشعانين) الجالس فوق الشاروبيم</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{FC1EEFC2-F019-4CD5-BD5A-23F9E734E63A}</t>
+          <t>{2E674F43-188F-46C4-B421-E7ADF4DB57C7}</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>793</v>
+        <v>826</v>
       </c>
       <c r="D28" t="n">
-        <v>803</v>
+        <v>842</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>(خميس العهد) ليل العشاء السري</t>
+          <t>(احد الشعانين) المجد لله الأوحد</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{F55CB762-4A57-49B3-A691-C8660FCFC634}</t>
+          <t>{D5D7C4B4-CC66-4076-8A09-DFD723D50F03}</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>804</v>
+        <v>843</v>
       </c>
       <c r="D29" t="n">
-        <v>828</v>
+        <v>885</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (خميس العهد) إن فادينا دعانا</t>
+          <t>(احد الشعانين) أوصنا يا ابن داود</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{1A183E7B-87A1-4C2F-841E-DFEC3B4A7D2F}</t>
+          <t>{FC1EEFC2-F019-4CD5-BD5A-23F9E734E63A}</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>829</v>
+        <v>886</v>
       </c>
       <c r="D30" t="n">
-        <v>844</v>
+        <v>896</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>(خميس العهد) أوصنا يا إبن داود</t>
+          <t>(خميس العهد) ليل العشاء السري</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{59DFCA58-6399-41A0-AB3D-6A5B0D8DDFBC}</t>
+          <t>{F55CB762-4A57-49B3-A691-C8660FCFC634}</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>845</v>
+        <v>897</v>
       </c>
       <c r="D31" t="n">
-        <v>854</v>
+        <v>921</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>(القيامة) مديح واطس لعشية - الله الأزلي قبل الأوقات</t>
+          <t xml:space="preserve"> (خميس العهد) إن فادينا دعانا</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{A72E6126-0320-4081-9967-7CDEDE602A51}</t>
+          <t>{1A183E7B-87A1-4C2F-841E-DFEC3B4A7D2F}</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>855</v>
+        <v>922</v>
       </c>
       <c r="D32" t="n">
-        <v>884</v>
+        <v>937</v>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>(القيامة) سبع قطع لباكر - المجد والعظمة للإله</t>
+          <t>(خميس العهد) أوصنا يا إبن داود</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{0D4A51F9-2CBC-4DB3-8764-00D5D185E9D3}</t>
+          <t>{59DFCA58-6399-41A0-AB3D-6A5B0D8DDFBC}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>885</v>
+        <v>938</v>
       </c>
       <c r="D33" t="n">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="E33" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>(القيامة) أنا افتح فمي وأتكلم</t>
+          <t>(القيامة) مديح واطس لعشية - الله الأزلي قبل الأوقات</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{05FB6036-013E-4B49-AF1F-F51A76197290}</t>
+          <t>{A72E6126-0320-4081-9967-7CDEDE602A51}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="D34" t="n">
-        <v>964</v>
+        <v>977</v>
       </c>
       <c r="E34" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الأول - أبدأ باسم الله القدوس</t>
+          <t>(القيامة) سبع قطع لباكر - المجد والعظمة للإله</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{E652151D-56BC-4E03-935C-6CB473E64AC9}</t>
+          <t>{0D4A51F9-2CBC-4DB3-8764-00D5D185E9D3}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>965</v>
+        <v>978</v>
       </c>
       <c r="D35" t="n">
-        <v>978</v>
+        <v>1028</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الثاني - أنا أفتح فمي بمجد الله</t>
+          <t>(القيامة) أنا افتح فمي وأتكلم</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{12A7A1D0-EC34-4F91-93B4-77F40C22A4E0}</t>
+          <t>{05FB6036-013E-4B49-AF1F-F51A76197290}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>979</v>
+        <v>1029</v>
       </c>
       <c r="D36" t="n">
-        <v>998</v>
+        <v>1057</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الثالث - المجد يليق والأكرام</t>
+          <t>(الخماسين) الاسبوع الأول - أبدأ باسم الله القدوس</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{CCFAA7F8-17F8-4620-BE25-841890829953}</t>
+          <t>{E652151D-56BC-4E03-935C-6CB473E64AC9}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>999</v>
+        <v>1058</v>
       </c>
       <c r="D37" t="n">
-        <v>1027</v>
+        <v>1071</v>
       </c>
       <c r="E37" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الرابع - أنا أفتح فمي واتكلم</t>
+          <t>(الخماسين) الاسبوع الثاني - أنا أفتح فمي بمجد الله</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{6896F5AC-12DD-450D-A6A9-E7A0FC24A7D1}</t>
+          <t>{12A7A1D0-EC34-4F91-93B4-77F40C22A4E0}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1028</v>
+        <v>1072</v>
       </c>
       <c r="D38" t="n">
-        <v>1056</v>
+        <v>1091</v>
       </c>
       <c r="E38" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع الخامس - أبدى باسم الله القدوس</t>
+          <t>(الخماسين) الاسبوع الثالث - المجد يليق والأكرام</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{F0F8F790-9F1B-48CC-B4CF-E7411C57B0C8}</t>
+          <t>{CCFAA7F8-17F8-4620-BE25-841890829953}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1057</v>
+        <v>1092</v>
       </c>
       <c r="D39" t="n">
-        <v>1086</v>
+        <v>1120</v>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>(الخماسين) الاسبوع السادس - أنا أفتح فاي وأخبركم</t>
+          <t>(الخماسين) الاسبوع الرابع - أنا أفتح فمي واتكلم</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{852F6F54-9767-4FF5-B8C5-8BE0B6729F8D}</t>
+          <t>{6896F5AC-12DD-450D-A6A9-E7A0FC24A7D1}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1087</v>
+        <v>1121</v>
       </c>
       <c r="D40" t="n">
-        <v>1102</v>
+        <v>1149</v>
       </c>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>(الخماسين) عيد الصعود - المجد لله والأكرام</t>
+          <t>(الخماسين) الاسبوع الخامس - أبدى باسم الله القدوس</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{0B00A682-598E-42FA-9F88-D72EAFF6E783}</t>
+          <t>{F0F8F790-9F1B-48CC-B4CF-E7411C57B0C8}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="D41" t="n">
-        <v>1119</v>
+        <v>1179</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>(الخماسين) عيد العنصرة - المجد لله القدوس</t>
+          <t>(الخماسين) الاسبوع السادس - أنا أفتح فاي وأخبركم</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{C028FF9B-09C1-42E1-90E0-2C45A634BAF0}</t>
+          <t>{852F6F54-9767-4FF5-B8C5-8BE0B6729F8D}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1120</v>
+        <v>1180</v>
       </c>
       <c r="D42" t="n">
-        <v>1137</v>
+        <v>1195</v>
       </c>
       <c r="E42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>(صوم وعيد الرسل) الفاعل الأمين لا يخزى</t>
+          <t>(الخماسين) عيد الصعود - المجد لله والأكرام</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{B9A8D07C-0514-491C-A91B-A5BD0B14C556}</t>
+          <t>{0B00A682-598E-42FA-9F88-D72EAFF6E783}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1138</v>
+        <v>1196</v>
       </c>
       <c r="D43" t="n">
-        <v>1167</v>
+        <v>1212</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>(صوم و عيد الرسل) فلنسبح إلهنا القـدوس</t>
+          <t>(الخماسين) عيد العنصرة - المجد لله القدوس</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{FFAC3DB8-CD69-4363-AEEE-0A77AFA5C14C}</t>
+          <t>{C028FF9B-09C1-42E1-90E0-2C45A634BAF0}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1168</v>
+        <v>1213</v>
       </c>
       <c r="D44" t="n">
-        <v>1197</v>
+        <v>1230</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>(التجلي) المجد لله ذي الرحمة</t>
+          <t>(صوم وعيد الرسل) الفاعل الأمين لا يخزى</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{72B6A886-BE5B-444C-ADB8-80108ED1C462}</t>
+          <t>{B9A8D07C-0514-491C-A91B-A5BD0B14C556}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1198</v>
+        <v>1231</v>
       </c>
       <c r="D45" t="n">
-        <v>1214</v>
+        <v>1260</v>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>(سنوي) ابانا الذي في السموات</t>
+          <t>(صوم و عيد الرسل) فلنسبح إلهنا القـدوس</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{55AD0713-7619-4F4A-BBF7-CBEC78E9D2B6}</t>
+          <t>{FFAC3DB8-CD69-4363-AEEE-0A77AFA5C14C}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1215</v>
+        <v>1261</v>
       </c>
       <c r="D46" t="n">
-        <v>1228</v>
+        <v>1290</v>
       </c>
       <c r="E46" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>(سنوي) اسمعوا يا شعب المسيح</t>
+          <t>(التجلي) المجد لله ذي الرحمة</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{FBABEA1B-1917-427E-BD5E-EB2368CB6293}</t>
+          <t>{72B6A886-BE5B-444C-ADB8-80108ED1C462}</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1229</v>
+        <v>1291</v>
       </c>
       <c r="D47" t="n">
-        <v>1257</v>
+        <v>1307</v>
       </c>
       <c r="E47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>(سنوي) المجد لمن رفع السموات</t>
+          <t>(سنوي) ابانا الذي في السموات</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{12A69F25-ED75-4850-8C2A-4864364C2131}</t>
+          <t>{55AD0713-7619-4F4A-BBF7-CBEC78E9D2B6}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1258</v>
+        <v>1308</v>
       </c>
       <c r="D48" t="n">
-        <v>1288</v>
+        <v>1321</v>
       </c>
       <c r="E48" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>(سنوي) أول ما أبدي أسبح الإله</t>
+          <t>(سنوي) اسمعوا يا شعب المسيح</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{BA707332-FF09-40ED-BD05-0F3CE5931805}</t>
+          <t>{FBABEA1B-1917-427E-BD5E-EB2368CB6293}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1289</v>
+        <v>1322</v>
       </c>
       <c r="D49" t="n">
-        <v>1318</v>
+        <v>1350</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>الباب الثاني</t>
+          <t>(سنوي) المجد لمن رفع السموات</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{E9ED8CBA-74AF-4903-9BE7-83949A2E6042}</t>
+          <t>{12A69F25-ED75-4850-8C2A-4864364C2131}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1319</v>
+        <v>1351</v>
       </c>
       <c r="D50" t="n">
-        <v>1319</v>
+        <v>1381</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>أبادير وإيرائي اخته</t>
+          <t>(سنوي) أول ما أبدي أسبح الإله</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{418E980F-1BC4-40C4-AED7-1DE2566AF0A8}</t>
+          <t>{BA707332-FF09-40ED-BD05-0F3CE5931805}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1320</v>
+        <v>1382</v>
       </c>
       <c r="D51" t="n">
-        <v>1344</v>
+        <v>1411</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>أبسخيرون القليني</t>
+          <t>الباب الثاني</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{21D2DCA4-5857-4F13-886C-A79FCE9F45CF}</t>
+          <t>{E9ED8CBA-74AF-4903-9BE7-83949A2E6042}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1345</v>
+        <v>1412</v>
       </c>
       <c r="D52" t="n">
-        <v>1356</v>
+        <v>1412</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>أباكراجون البتانوني</t>
+          <t>أبادير وإيرائي اخته</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{C6670786-A976-4B52-868E-171137C94BF0}</t>
+          <t>{418E980F-1BC4-40C4-AED7-1DE2566AF0A8}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1357</v>
+        <v>1413</v>
       </c>
       <c r="D53" t="n">
-        <v>1372</v>
+        <v>1437</v>
       </c>
       <c r="E53" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>اباكير و يوحنا</t>
+          <t>أبسخيرون القليني</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{94B1CF6F-400F-4EBB-BEB3-7561B8B79E22}</t>
+          <t>{21D2DCA4-5857-4F13-886C-A79FCE9F45CF}</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1373</v>
+        <v>1438</v>
       </c>
       <c r="D54" t="n">
-        <v>1389</v>
+        <v>1449</v>
       </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>أبانوب النهيسي</t>
+          <t>أباكراجون البتانوني</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{B7505EB8-9095-443D-8AB4-76B429FB6882}</t>
+          <t>{C6670786-A976-4B52-868E-171137C94BF0}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1390</v>
+        <v>1450</v>
       </c>
       <c r="D55" t="n">
-        <v>1405</v>
+        <v>1465</v>
       </c>
       <c r="E55" t="n">
         <v>16</v>
@@ -11835,229 +11856,229 @@
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>الأنبا إبرآم أسقف الفيوم</t>
+          <t>اباكير و يوحنا</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{76A5C39E-E378-49E4-A1B3-3C3C6AD0FC45}</t>
+          <t>{94B1CF6F-400F-4EBB-BEB3-7561B8B79E22}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1406</v>
+        <v>1466</v>
       </c>
       <c r="D56" t="n">
-        <v>1425</v>
+        <v>1482</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>الأنبا أبوللو والأنبا أبيب</t>
+          <t>أبانوب النهيسي</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{15F37CDF-162E-4235-B0CD-3EC560293C8F}</t>
+          <t>{B7505EB8-9095-443D-8AB4-76B429FB6882}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1426</v>
+        <v>1483</v>
       </c>
       <c r="D57" t="n">
-        <v>1444</v>
+        <v>1498</v>
       </c>
       <c r="E57" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>الأنبا بيشوي</t>
+          <t>الأنبا إبرآم أسقف الفيوم</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{A7827B46-8853-4630-8C57-25D12D4BB0CC}</t>
+          <t>{76A5C39E-E378-49E4-A1B3-3C3C6AD0FC45}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1445</v>
+        <v>1499</v>
       </c>
       <c r="D58" t="n">
-        <v>1463</v>
+        <v>1518</v>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>الأنبا أنطونيوس</t>
+          <t>الأنبا أبوللو والأنبا أبيب</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{AE159095-D310-4A30-980A-0B3122A27E47}</t>
+          <t>{15F37CDF-162E-4235-B0CD-3EC560293C8F}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1464</v>
+        <v>1519</v>
       </c>
       <c r="D59" t="n">
-        <v>1478</v>
+        <v>1537</v>
       </c>
       <c r="E59" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>القديس أبو مقار الكبير</t>
+          <t>الأنبا بيشوي</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{D1D7B229-E53D-4C04-AC77-B8E34223EEAF}</t>
+          <t>{A7827B46-8853-4630-8C57-25D12D4BB0CC}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1479</v>
+        <v>1538</v>
       </c>
       <c r="D60" t="n">
-        <v>1494</v>
+        <v>1556</v>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>الأنبا ساويرس الأنطاكي</t>
+          <t>الأنبا أنطونيوس</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{9BAA7FB0-F8B8-4E53-A01A-F247E651EA5F}</t>
+          <t>{AE159095-D310-4A30-980A-0B3122A27E47}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1495</v>
+        <v>1557</v>
       </c>
       <c r="D61" t="n">
-        <v>1510</v>
+        <v>1571</v>
       </c>
       <c r="E61" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>الأنبا أرسانيوس</t>
+          <t>القديس أبو مقار الكبير</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{C7297DB4-629F-4E57-809D-A2D2D80CBC90}</t>
+          <t>{D1D7B229-E53D-4C04-AC77-B8E34223EEAF}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1511</v>
+        <v>1572</v>
       </c>
       <c r="D62" t="n">
-        <v>1521</v>
+        <v>1587</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>الأنبا رويس (أفتح فاي باسم الله)</t>
+          <t>الأنبا ساويرس الأنطاكي</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{6DD4328F-B2A2-4D8E-B789-5A48B3861347}</t>
+          <t>{9BAA7FB0-F8B8-4E53-A01A-F247E651EA5F}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1522</v>
+        <v>1588</v>
       </c>
       <c r="D63" t="n">
-        <v>1540</v>
+        <v>1603</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>الأنبا رويس (السلام للأنبا فريج)</t>
+          <t>الأنبا أرسانيوس</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{E747FAEF-A32D-48E7-9745-27FFACBBF45C}</t>
+          <t>{C7297DB4-629F-4E57-809D-A2D2D80CBC90}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1541</v>
+        <v>1604</v>
       </c>
       <c r="D64" t="n">
-        <v>1557</v>
+        <v>1614</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>البابا بطرس خاتم الشهداء (أفتح فاى بالتمجيد)</t>
+          <t>الأنبا رويس (أفتح فاي باسم الله)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{713E38EC-7043-46DD-9D08-0B816BE65A07}</t>
+          <t>{6DD4328F-B2A2-4D8E-B789-5A48B3861347}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1558</v>
+        <v>1615</v>
       </c>
       <c r="D65" t="n">
-        <v>1572</v>
+        <v>1633</v>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>البابا بطرس خاتم الشهداء (افتح فاي بالتسبيح)</t>
+          <t>الأنبا رويس (السلام للأنبا فريج)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{0A2C786B-9166-4B00-8893-BDBFED3B96C5}</t>
+          <t>{E747FAEF-A32D-48E7-9745-27FFACBBF45C}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1573</v>
+        <v>1634</v>
       </c>
       <c r="D66" t="n">
-        <v>1589</v>
+        <v>1650</v>
       </c>
       <c r="E66" t="n">
         <v>17</v>
@@ -12066,483 +12087,525 @@
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>الشهيد مارجرجس الروماني</t>
+          <t>البابا بطرس خاتم الشهداء (أفتح فاى بالتمجيد)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{FFF1B9FE-C89C-4F56-85B7-F375461AEA62}</t>
+          <t>{713E38EC-7043-46DD-9D08-0B816BE65A07}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1590</v>
+        <v>1651</v>
       </c>
       <c r="D67" t="n">
-        <v>1601</v>
+        <v>1665</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (تعالوا نتهلل بالالحان)</t>
+          <t>البابا بطرس خاتم الشهداء (افتح فاي بالتسبيح)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{1CB7C0A9-70EC-46E1-9942-6BB8469F3452}</t>
+          <t>{0A2C786B-9166-4B00-8893-BDBFED3B96C5}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1602</v>
+        <v>1666</v>
       </c>
       <c r="D68" t="n">
-        <v>1625</v>
+        <v>1682</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (افتح فاى بالتسبيح)</t>
+          <t>الشهيد مارجرجس الروماني</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{A09196A5-E8C6-4842-A208-B0D3C60A9650}</t>
+          <t>{FFF1B9FE-C89C-4F56-85B7-F375461AEA62}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1626</v>
+        <v>1683</v>
       </c>
       <c r="D69" t="n">
-        <v>1639</v>
+        <v>1694</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>الشهيد مارمينا العجائبي</t>
+          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (تعالوا نتهلل بالالحان)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{FEF9FE36-19EB-47C1-B153-89D4179D816D}</t>
+          <t>{1CB7C0A9-70EC-46E1-9942-6BB8469F3452}</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1640</v>
+        <v>1695</v>
       </c>
       <c r="D70" t="n">
-        <v>1652</v>
+        <v>1718</v>
       </c>
       <c r="E70" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>الشهيد اسطفانوس</t>
+          <t>الشهيد فيلوباتير ميرقوريوس أبو سيفين (افتح فاى بالتسبيح)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{B37BED38-74B5-4E20-9C68-02F0B138FB76}</t>
+          <t>{A09196A5-E8C6-4842-A208-B0D3C60A9650}</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1653</v>
+        <v>1719</v>
       </c>
       <c r="D71" t="n">
-        <v>1665</v>
+        <v>1732</v>
       </c>
       <c r="E71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>القديس لوقا الانجيلي</t>
+          <t>الشهيد مارمينا العجائبي</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{50EEB170-6F56-438C-943C-B8B3136DBB6A}</t>
+          <t>{FEF9FE36-19EB-47C1-B153-89D4179D816D}</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1666</v>
+        <v>1733</v>
       </c>
       <c r="D72" t="n">
-        <v>1683</v>
+        <v>1745</v>
       </c>
       <c r="E72" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>القديس مارمرقس الرسول</t>
+          <t>الشهيد اسطفانوس</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{D4872368-E5CE-4B87-A314-70582CB26D33}</t>
+          <t>{B37BED38-74B5-4E20-9C68-02F0B138FB76}</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1684</v>
+        <v>1746</v>
       </c>
       <c r="D73" t="n">
-        <v>1702</v>
+        <v>1758</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>شهداء اخميم</t>
+          <t>القديس لوقا الانجيلي</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{BCD6DB0F-7899-4280-8F26-43D95DAD6C10}</t>
+          <t>{50EEB170-6F56-438C-943C-B8B3136DBB6A}</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1703</v>
+        <v>1759</v>
       </c>
       <c r="D74" t="n">
-        <v>1715</v>
+        <v>1776</v>
       </c>
       <c r="E74" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>القديسة ڤيرينا</t>
+          <t>القديس مارمرقس الرسول</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{97AE3AB0-0AA8-460A-9F07-02DB0D944E28}</t>
+          <t>{D4872368-E5CE-4B87-A314-70582CB26D33}</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1716</v>
+        <v>1777</v>
       </c>
       <c r="D75" t="n">
-        <v>1729</v>
+        <v>1795</v>
       </c>
       <c r="E75" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>العذراء مريم .. يا أم الله القدوس</t>
+          <t>شهداء اخميم</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{BC31EDAD-70A8-41AD-8F09-30FB6E612B63}</t>
+          <t>{BCD6DB0F-7899-4280-8F26-43D95DAD6C10}</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1730</v>
+        <v>1796</v>
       </c>
       <c r="D76" t="n">
-        <v>1740</v>
+        <v>1808</v>
       </c>
       <c r="E76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>العذراء مريم .. يا يمامة جليلة تصيح</t>
+          <t>القديسة ڤيرينا</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{CA9FFDD9-E5B0-41CC-901F-6882250D1D1A}</t>
+          <t>{97AE3AB0-0AA8-460A-9F07-02DB0D944E28}</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1741</v>
+        <v>1809</v>
       </c>
       <c r="D77" t="n">
-        <v>1755</v>
+        <v>1822</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>الملاك ميخائيل</t>
+          <t>العذراء مريم .. يا أم الله القدوس</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{12793581-7FD0-4EE7-B903-2943F410A5D2}</t>
+          <t>{BC31EDAD-70A8-41AD-8F09-30FB6E612B63}</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1756</v>
+        <v>1823</v>
       </c>
       <c r="D78" t="n">
-        <v>1767</v>
+        <v>1833</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>الملاك غبريال</t>
+          <t>العذراء مريم .. يا يمامة جليلة تصيح</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{FFD2036A-0F2D-47E3-B5B9-AC167E3F6FF3}</t>
+          <t>{CA9FFDD9-E5B0-41CC-901F-6882250D1D1A}</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1768</v>
+        <v>1834</v>
       </c>
       <c r="D79" t="n">
-        <v>1779</v>
+        <v>1848</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>الباب الثالث</t>
+          <t>الملاك ميخائيل</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{E5B98BC1-9C9D-42EC-BB16-E848179FB9DC}</t>
+          <t>{12793581-7FD0-4EE7-B903-2943F410A5D2}</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1780</v>
+        <v>1849</v>
       </c>
       <c r="D80" t="n">
-        <v>1780</v>
+        <v>1860</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>أعروس الفادي القبطية</t>
+          <t>الملاك غبريال</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{3CBD5E49-3BE4-475A-A6D3-2858A4DB1030}</t>
+          <t>{FFD2036A-0F2D-47E3-B5B9-AC167E3F6FF3}</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1781</v>
+        <v>1861</v>
       </c>
       <c r="D81" t="n">
-        <v>1809</v>
+        <v>1872</v>
       </c>
       <c r="E81" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>انظروا يديه تأملوا رجليه</t>
+          <t>الباب الثالث</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{E1A31474-7F00-4B7D-90FD-A67415E32872}</t>
+          <t>{E5B98BC1-9C9D-42EC-BB16-E848179FB9DC}</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1810</v>
+        <v>1873</v>
       </c>
       <c r="D82" t="n">
-        <v>1824</v>
+        <v>1873</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>رحلة الصوم الكبير</t>
+          <t>أعروس الفادي القبطية</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{11755A37-6BDF-4E72-9537-F39867C5BB7D}</t>
+          <t>{3CBD5E49-3BE4-475A-A6D3-2858A4DB1030}</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1825</v>
+        <v>1874</v>
       </c>
       <c r="D83" t="n">
-        <v>1831</v>
+        <v>1902</v>
       </c>
       <c r="E83" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" ht="18.75" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>عند شق الفجر باكر</t>
+          <t>انظروا يديه تأملوا رجليه</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{D4859CD1-25CE-465C-846E-A0311D24DB66}</t>
+          <t>{E1A31474-7F00-4B7D-90FD-A67415E32872}</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1832</v>
+        <v>1903</v>
       </c>
       <c r="D84" t="n">
-        <v>1864</v>
+        <v>1917</v>
       </c>
       <c r="E84" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>قام حقا</t>
+          <t>رحلة الصوم الكبير</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{4615B620-F94D-4CAD-843A-EB32E8369AAB}</t>
+          <t>{11755A37-6BDF-4E72-9537-F39867C5BB7D}</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1865</v>
+        <v>1918</v>
       </c>
       <c r="D85" t="n">
-        <v>1878</v>
+        <v>1924</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>كنيستي أرجو لك</t>
+          <t>عند شق الفجر باكر</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{8A08F2A7-DAF4-4998-9EF9-8221744F0038}</t>
+          <t>{D4859CD1-25CE-465C-846E-A0311D24DB66}</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1879</v>
+        <v>1925</v>
       </c>
       <c r="D86" t="n">
-        <v>1889</v>
+        <v>1957</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" ht="18.75" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>كنيستي القبطية كنيسة الإله</t>
+          <t>قام حقا</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{B1A30565-0CDB-40D5-8B05-21F68D5C9160}</t>
+          <t>{4615B620-F94D-4CAD-843A-EB32E8369AAB}</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1890</v>
+        <v>1958</v>
       </c>
       <c r="D87" t="n">
-        <v>1916</v>
+        <v>1971</v>
       </c>
       <c r="E87" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" ht="18.75" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>كنيستي القبطية نشرت المسيحية</t>
+          <t>كنيستي أرجو لك</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{AB60D02D-F80E-4E53-B0A0-3A54593EB31B}</t>
+          <t>{8A08F2A7-DAF4-4998-9EF9-8221744F0038}</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1917</v>
+        <v>1972</v>
       </c>
       <c r="D88" t="n">
-        <v>1929</v>
+        <v>1982</v>
       </c>
       <c r="E88" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>كنيستي القبطية كنيسة الإله</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>{B1A30565-0CDB-40D5-8B05-21F68D5C9160}</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E89" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>كنيستي القبطية نشرت المسيحية</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>{AB60D02D-F80E-4E53-B0A0-3A54593EB31B}</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E90" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>يا ربنا مولى السلام</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>{325B4DE6-FA63-4B6D-827F-BCC78EF1FEC9}</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>1930</v>
-      </c>
-      <c r="D89" t="n">
-        <v>1973</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="C91" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E91" t="n">
         <v>44</v>
       </c>
     </row>
@@ -27300,7 +27363,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="53.86214285714286" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -30907,7 +30970,1266 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" ht="19.5" customHeight="1"/>
+    <row r="172" ht="19.5" customHeight="1">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>دفنار 1 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>{E42EBDBB-169A-4744-9780-1F93398B5016}</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>2448</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2451</v>
+      </c>
+      <c r="E172" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>دفنار 1 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>{D6E545D7-F6D6-49C7-8EC4-9B1AEC83F880}</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2452</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2457</v>
+      </c>
+      <c r="E173" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>دفنار 2 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>{C435A074-E166-46E6-A184-34598107738B}</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2458</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2462</v>
+      </c>
+      <c r="E174" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>دفنار 2 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>{9E05E867-107F-4104-8B32-23D6F46FAFA4}</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2463</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2468</v>
+      </c>
+      <c r="E175" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>دفنار 3 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>{48B75380-64B7-4DFD-8837-537BB9C6F227}</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2469</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2480</v>
+      </c>
+      <c r="E176" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>دفنار 3 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>{FDF9CA83-D3F9-4FB7-9ED4-9FA4112D7035}</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2481</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2508</v>
+      </c>
+      <c r="E177" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>دفنار 4 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>{DD19F10A-416A-4FC9-B3B6-DCFDF25BB1BA}</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2509</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2513</v>
+      </c>
+      <c r="E178" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>دفنار 4 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>{63C445C3-C7D3-4259-8F62-1C86B6991D2E}</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2514</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2519</v>
+      </c>
+      <c r="E179" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>دفنار 5 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>{028FE138-F61F-4B84-B51D-BA3D2EB4C532}</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2520</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2523</v>
+      </c>
+      <c r="E180" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>دفنار 5 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>{01CAEE5F-097A-4D3C-99D1-4316E64C7B1C}</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2524</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2526</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>دفنار 6 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>{DB85702F-96F2-4C3E-A598-7E144D488361}</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2527</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2530</v>
+      </c>
+      <c r="E182" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>دفنار 6 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>{E41788C7-A663-46E2-A01B-31386C539A43}</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2531</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E183" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>دفنار 7 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>{8938239B-2EB5-4903-AF1D-E9568B734DC7}</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2537</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E184" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>دفنار 7 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>{1E2C5C71-2981-452F-801D-CA45C4B29993}</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2541</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2546</v>
+      </c>
+      <c r="E185" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>دفنار 8 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>{4BF476AB-EB4C-4D76-BBFB-C979AE042D76}</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2547</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2560</v>
+      </c>
+      <c r="E186" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>دفنار 8 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>{23A26D23-3DDD-4D55-BD14-8D8D790BCE55}</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2561</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2571</v>
+      </c>
+      <c r="E187" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>دفنار 9 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>{E193355A-967B-4E1C-BE04-236B7CD8F0BB}</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2572</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2576</v>
+      </c>
+      <c r="E188" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>دفنار 9 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>{25A9CB9E-22CE-4550-81C3-6C760EF0E8DE}</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2577</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2582</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>دفنار 10 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>{3C2E00F7-3B7B-4F64-B43B-2FA029483CDF}</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2583</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2585</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>دفنار 10 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>{66F036BB-932C-4672-A931-1C6159696B7A}</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2586</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2588</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>دفنار 11 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>{055DEBBE-9431-42E9-B923-FF0BE05D668B}</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2589</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2591</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>دفنار 11 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>{0737DFD5-A83D-4EC6-9ED5-D1070780C427}</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2592</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2594</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>دفنار 12 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>{E54BB253-F6AB-4567-BDA4-A38D4152F8FB}</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2595</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2598</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>دفنار 12 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>{D0E79F3F-B5B7-468F-896B-A6F41EFA4982}</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2599</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2603</v>
+      </c>
+      <c r="E195" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>دفنار 13 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>{E1040604-D5BD-4CDB-8E2C-069A886CB764}</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2604</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2605</v>
+      </c>
+      <c r="E196" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>دفنار 13 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>{E3CF320F-D2F7-4EDA-B7DE-FE4DFFEDFBAA}</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2606</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2608</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>دفنار 14 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>{024F3287-B2B3-473E-9342-47CB1B1689EE}</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2609</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2617</v>
+      </c>
+      <c r="E198" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>دفنار 14 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>{21F16C91-FFC7-438F-BE72-CDFE39B45895}</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2618</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2620</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>دفنار 15 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>{EB47167D-2C70-42FE-9ABD-20A8D6F528A9}</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2621</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2623</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>دفنار 15 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>{F8C4C951-86F3-46E1-8FF2-88FB5C12FAA2}</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2624</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2626</v>
+      </c>
+      <c r="E201" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>دفنار 16 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>{B9EC7658-6362-481A-8C69-7156BF45C05B}</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2627</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2629</v>
+      </c>
+      <c r="E202" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>دفنار 16 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>{64805263-785C-419B-93D7-8C9439FAB0D1}</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2630</v>
+      </c>
+      <c r="D203" t="n">
+        <v>2632</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>دفنار 17 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>{573A71EC-D2EF-4B8A-B334-3F85B728B6C1}</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2633</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2634</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>دفنار 17 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>{4978928A-9F76-4E06-8802-C73727171BF6}</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2635</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2637</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>دفنار 18 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>{D4158BDB-7EE4-41CA-8E5A-43B42C195384}</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2638</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2640</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>دفنار 18 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>{FF69615A-C9B2-4BCF-9D41-A0121147F676}</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2641</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2643</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>دفنار 19 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>{77C019E6-B29C-4F3F-9770-B5EE1359AA04}</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2644</v>
+      </c>
+      <c r="D208" t="n">
+        <v>2648</v>
+      </c>
+      <c r="E208" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>دفنار 19 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>{5E1C9FF2-E6E6-4541-99C8-D0A85623EE65}</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2649</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2653</v>
+      </c>
+      <c r="E209" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>دفنار 20 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>{FF982FD1-1C92-43E2-908D-C38681CB14CB}</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2654</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2656</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>دفنار 20 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>{5F9DFE32-8305-4673-9706-15986AA1DF0C}</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2657</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2658</v>
+      </c>
+      <c r="E211" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>دفنار 21 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>{480A6C5E-2702-4204-A191-DA133EBD19B9}</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2659</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E212" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>دفنار 21 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>{23967870-2312-42F5-B7A3-63162E0BAA8A}</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2664</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2666</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>دفنار 22 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>{B872450F-1979-4377-B9F6-4DE5D7C3B803}</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2667</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2671</v>
+      </c>
+      <c r="E214" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>دفنار 22 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>{9622CABE-6EAD-4349-BB9C-EE0881C21C25}</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2672</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E215" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>دفنار 23 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>{292DC64C-E523-4775-9C3F-72EB4506357B}</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2675</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2678</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>دفنار 23 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>{63EF58B3-5273-4D22-80E3-C0EF9672EE86}</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2679</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>دفنار 24 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>{E0E2666F-D3ED-4483-B187-633C8B568C06}</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2681</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2683</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>دفنار 24 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>{4F7B613C-B064-4226-BAF1-02C96F343983}</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2684</v>
+      </c>
+      <c r="D219" t="n">
+        <v>2686</v>
+      </c>
+      <c r="E219" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>دفنار 25 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>{63C9C39E-E518-4A66-8E27-5C6D631BFF35}</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2687</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2689</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>دفنار 25 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>{8B3B81C9-1409-46C7-B3E4-9E970358F6DE}</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2690</v>
+      </c>
+      <c r="D221" t="n">
+        <v>2692</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>دفنار 26 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>{94682183-6030-4B14-B37E-6A8DB50546CD}</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2693</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2697</v>
+      </c>
+      <c r="E222" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>دفنار 26 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>{9016BCE0-6B9D-448D-BC74-BAA9EB1AA324}</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2698</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2703</v>
+      </c>
+      <c r="E223" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>دفنار 27 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>{9973F098-4000-4E69-B862-970209F7EFBD}</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2704</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2706</v>
+      </c>
+      <c r="E224" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>دفنار 27 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>{14399DE1-9205-44E9-9319-A519ECEFF1A8}</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2707</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E225" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>دفنار 28 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>{D268969B-7FAA-455D-BB9F-1A2DDAD2BEF8}</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2710</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2713</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>دفنار 28 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>{FAAC854F-53F0-467F-A5EF-0E10F086D9FC}</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2714</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2717</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>دفنار 29 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>{8A845694-5190-4527-8F13-9F9392305625}</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2718</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2722</v>
+      </c>
+      <c r="E228" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>دفنار 29 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>{E75FE5D3-84D1-498B-ACEE-9428CA6E23BB}</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2723</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2726</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>دفنار 30 كيهك ادام</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>{E46B383C-BD35-4B99-8396-6007419FCF66}</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2727</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2729</v>
+      </c>
+      <c r="E230" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>دفنار 30 كيهك واطس</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>{CEB4ACB5-D656-42DE-846D-782604E342DE}</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2730</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2732</v>
+      </c>
+      <c r="E231" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
